--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,4980 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124800303</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>440909</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7001374</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124800334</v>
+      </c>
+      <c r="B4" t="n">
+        <v>77753</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>314</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vitskaftad svartspik</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis viridialba</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>440624</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7001080</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124740817</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>440684</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7001254</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124800329</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>440658</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7001354</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124800315</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78889</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>864</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>440782</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7001494</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124800296</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>440939</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7001309</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124800300</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>440915</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7001296</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124800293</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>441111</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7001333</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124800306</v>
+      </c>
+      <c r="B11" t="n">
+        <v>88359</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>510</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>440872</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7001384</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124800325</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>440674</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7001385</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124800307</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>440872</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7001280</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124800313</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>440791</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7001239</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124800324</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91361</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>440680</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7001258</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124800336</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91026</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>440616</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7001215</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124800320</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>440720</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7001206</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124800318</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96354</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>53</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>440721</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7001216</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124800310</v>
+      </c>
+      <c r="B19" t="n">
+        <v>74901</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>440799</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7001243</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124800304</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>440902</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7001332</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124800299</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78889</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>864</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>440915</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7001377</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>124800297</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91026</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>440921</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7001295</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>124800302</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78889</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>864</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>440910</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7001371</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>124800327</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>440672</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7001361</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>124740889</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>440684</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7001254</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>124800328</v>
+      </c>
+      <c r="B26" t="n">
+        <v>95335</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>440661</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7001244</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>124800326</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>440672</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7001335</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>124801009</v>
+      </c>
+      <c r="B28" t="n">
+        <v>94769</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2411</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Nordlig källmossa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Philonotis tomentella</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Molendo</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>440900</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7001371</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>124800319</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97185</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>440720</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7001201</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>124800294</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79851</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>441028</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7001364</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>124800316</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>440773</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7001489</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>124800309</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>440821</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7001261</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>124800340</v>
+      </c>
+      <c r="B33" t="n">
+        <v>74901</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>440590</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7001362</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>124800330</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>440646</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7001158</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>124800323</v>
+      </c>
+      <c r="B35" t="n">
+        <v>74901</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>440681</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7001285</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>124800335</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78889</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>864</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>440621</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7001181</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>124800322</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>440696</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7001259</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>124800305</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>658</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>440874</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7001281</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>124800308</v>
+      </c>
+      <c r="B39" t="n">
+        <v>88359</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>510</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>440850</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7001393</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>124800295</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>440940</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7001369</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>124800321</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91008</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>440709</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7001238</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>124800314</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>440785</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7001501</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>124800333</v>
+      </c>
+      <c r="B43" t="n">
+        <v>82597</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>440628</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7001081</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>124800338</v>
+      </c>
+      <c r="B44" t="n">
+        <v>96776</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2389</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Purpurmylia</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Mylia taylorii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Hook.) Gray</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>440604</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7001240</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>124800311</v>
+      </c>
+      <c r="B45" t="n">
+        <v>77753</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>314</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vitskaftad svartspik</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis viridialba</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>440798</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7001239</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>124800331</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>440637</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7001171</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>124738082</v>
+      </c>
+      <c r="B47" t="n">
+        <v>88359</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>510</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>440684</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7001254</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>124800298</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>440916</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7001320</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>124800332</v>
+      </c>
+      <c r="B49" t="n">
+        <v>74906</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>440630</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7001086</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800303</v>
+        <v>124800325</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440909</v>
+        <v>440674</v>
       </c>
       <c r="R3" t="n">
-        <v>7001374</v>
+        <v>7001385</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800334</v>
+        <v>124800307</v>
       </c>
       <c r="B4" t="n">
-        <v>77753</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>314</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440624</v>
+        <v>440872</v>
       </c>
       <c r="R4" t="n">
-        <v>7001080</v>
+        <v>7001280</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124740817</v>
+        <v>124800300</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,34 +1015,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440684</v>
+        <v>440915</v>
       </c>
       <c r="R5" t="n">
-        <v>7001254</v>
+        <v>7001296</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,12 +1073,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800329</v>
+        <v>124800340</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1121,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1145,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440658</v>
+        <v>440590</v>
       </c>
       <c r="R6" t="n">
-        <v>7001354</v>
+        <v>7001362</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800315</v>
+        <v>124800305</v>
       </c>
       <c r="B7" t="n">
-        <v>78889</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,21 +1227,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1251,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440782</v>
+        <v>440874</v>
       </c>
       <c r="R7" t="n">
-        <v>7001494</v>
+        <v>7001281</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800296</v>
+        <v>124800322</v>
       </c>
       <c r="B8" t="n">
         <v>91012</v>
@@ -1357,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440939</v>
+        <v>440696</v>
       </c>
       <c r="R8" t="n">
-        <v>7001309</v>
+        <v>7001259</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800300</v>
+        <v>124800332</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>74906</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1439,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1463,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440915</v>
+        <v>440630</v>
       </c>
       <c r="R9" t="n">
-        <v>7001296</v>
+        <v>7001086</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800293</v>
+        <v>124800316</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,21 +1545,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1569,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441111</v>
+        <v>440773</v>
       </c>
       <c r="R10" t="n">
-        <v>7001333</v>
+        <v>7001489</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,10 +1635,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800306</v>
+        <v>124800321</v>
       </c>
       <c r="B11" t="n">
-        <v>88359</v>
+        <v>91008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,21 +1651,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1675,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440872</v>
+        <v>440709</v>
       </c>
       <c r="R11" t="n">
-        <v>7001384</v>
+        <v>7001238</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800325</v>
+        <v>124800335</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,21 +1757,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1781,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440674</v>
+        <v>440621</v>
       </c>
       <c r="R12" t="n">
-        <v>7001385</v>
+        <v>7001181</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800307</v>
+        <v>124740889</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,38 +1863,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440872</v>
+        <v>440684</v>
       </c>
       <c r="R13" t="n">
-        <v>7001280</v>
+        <v>7001254</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,12 +1917,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800313</v>
+        <v>124800327</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1993,10 +1993,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440791</v>
+        <v>440672</v>
       </c>
       <c r="R14" t="n">
-        <v>7001239</v>
+        <v>7001361</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800324</v>
+        <v>124800314</v>
       </c>
       <c r="B15" t="n">
-        <v>91361</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,25 +2067,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2093,19 +2093,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440680</v>
+        <v>440785</v>
       </c>
       <c r="R15" t="n">
-        <v>7001258</v>
+        <v>7001501</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,12 +2129,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2146,7 +2143,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2165,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800336</v>
+        <v>124800311</v>
       </c>
       <c r="B16" t="n">
-        <v>91026</v>
+        <v>77753</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,21 +2177,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2209,10 +2205,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440616</v>
+        <v>440798</v>
       </c>
       <c r="R16" t="n">
-        <v>7001215</v>
+        <v>7001239</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,7 +2267,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800320</v>
+        <v>124740817</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2304,21 +2300,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440720</v>
+        <v>440684</v>
       </c>
       <c r="R17" t="n">
-        <v>7001206</v>
+        <v>7001254</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,12 +2337,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2369,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800318</v>
+        <v>124801009</v>
       </c>
       <c r="B18" t="n">
-        <v>96354</v>
+        <v>94769</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2389,25 +2381,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>2411</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Nordlig källmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Philonotis tomentella</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Molendo</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2421,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440721</v>
+        <v>440900</v>
       </c>
       <c r="R18" t="n">
-        <v>7001216</v>
+        <v>7001371</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800310</v>
+        <v>124800319</v>
       </c>
       <c r="B19" t="n">
-        <v>74901</v>
+        <v>97185</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,25 +2487,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>220686</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2527,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440799</v>
+        <v>440720</v>
       </c>
       <c r="R19" t="n">
-        <v>7001243</v>
+        <v>7001201</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800304</v>
+        <v>124800313</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2605,21 +2597,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2633,10 +2625,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440902</v>
+        <v>440791</v>
       </c>
       <c r="R20" t="n">
-        <v>7001332</v>
+        <v>7001239</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800299</v>
+        <v>124800323</v>
       </c>
       <c r="B21" t="n">
-        <v>78889</v>
+        <v>74901</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2711,21 +2703,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2739,10 +2731,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440915</v>
+        <v>440681</v>
       </c>
       <c r="R21" t="n">
-        <v>7001377</v>
+        <v>7001285</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2801,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800297</v>
+        <v>124800295</v>
       </c>
       <c r="B22" t="n">
-        <v>91026</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2817,21 +2809,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2845,10 +2837,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440921</v>
+        <v>440940</v>
       </c>
       <c r="R22" t="n">
-        <v>7001295</v>
+        <v>7001369</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,10 +2899,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800302</v>
+        <v>124800296</v>
       </c>
       <c r="B23" t="n">
-        <v>78889</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,21 +2915,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2951,10 +2943,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440910</v>
+        <v>440939</v>
       </c>
       <c r="R23" t="n">
-        <v>7001371</v>
+        <v>7001309</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3013,7 +3005,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800327</v>
+        <v>124800329</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3057,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440672</v>
+        <v>440658</v>
       </c>
       <c r="R24" t="n">
-        <v>7001361</v>
+        <v>7001354</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3119,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124740889</v>
+        <v>124800306</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>88359</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3135,34 +3127,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440684</v>
+        <v>440872</v>
       </c>
       <c r="R25" t="n">
-        <v>7001254</v>
+        <v>7001384</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3189,12 +3185,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3221,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800328</v>
+        <v>124738082</v>
       </c>
       <c r="B26" t="n">
-        <v>95335</v>
+        <v>88359</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3233,42 +3229,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2809</v>
+        <v>510</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440661</v>
+        <v>440684</v>
       </c>
       <c r="R26" t="n">
-        <v>7001244</v>
+        <v>7001254</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3295,12 +3287,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3327,10 +3319,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800326</v>
+        <v>124800304</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3343,21 +3335,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3371,10 +3363,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440672</v>
+        <v>440902</v>
       </c>
       <c r="R27" t="n">
-        <v>7001335</v>
+        <v>7001332</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3433,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124801009</v>
+        <v>124800336</v>
       </c>
       <c r="B28" t="n">
-        <v>94769</v>
+        <v>91026</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3445,25 +3437,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2411</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordlig källmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Philonotis tomentella</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Molendo</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3477,10 +3469,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440900</v>
+        <v>440616</v>
       </c>
       <c r="R28" t="n">
-        <v>7001371</v>
+        <v>7001215</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3539,10 +3531,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800319</v>
+        <v>124800326</v>
       </c>
       <c r="B29" t="n">
-        <v>97185</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3551,25 +3543,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220686</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3583,10 +3575,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440720</v>
+        <v>440672</v>
       </c>
       <c r="R29" t="n">
-        <v>7001201</v>
+        <v>7001335</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3645,10 +3637,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800294</v>
+        <v>124800333</v>
       </c>
       <c r="B30" t="n">
-        <v>79851</v>
+        <v>82597</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3657,25 +3649,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3689,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441028</v>
+        <v>440628</v>
       </c>
       <c r="R30" t="n">
-        <v>7001364</v>
+        <v>7001081</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3751,10 +3743,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800316</v>
+        <v>124800328</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>95335</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3763,25 +3755,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3795,10 +3787,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440773</v>
+        <v>440661</v>
       </c>
       <c r="R31" t="n">
-        <v>7001489</v>
+        <v>7001244</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,10 +3849,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124800309</v>
+        <v>124800303</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3873,21 +3865,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3901,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440821</v>
+        <v>440909</v>
       </c>
       <c r="R32" t="n">
-        <v>7001261</v>
+        <v>7001374</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3963,10 +3955,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124800340</v>
+        <v>124800299</v>
       </c>
       <c r="B33" t="n">
-        <v>74901</v>
+        <v>78889</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3979,21 +3971,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4007,10 +3999,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440590</v>
+        <v>440915</v>
       </c>
       <c r="R33" t="n">
-        <v>7001362</v>
+        <v>7001377</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4069,7 +4061,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124800330</v>
+        <v>124800331</v>
       </c>
       <c r="B34" t="n">
         <v>78810</v>
@@ -4113,10 +4105,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440646</v>
+        <v>440637</v>
       </c>
       <c r="R34" t="n">
-        <v>7001158</v>
+        <v>7001171</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4175,10 +4167,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124800323</v>
+        <v>124800338</v>
       </c>
       <c r="B35" t="n">
-        <v>74901</v>
+        <v>96776</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4187,25 +4179,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>2389</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4219,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440681</v>
+        <v>440604</v>
       </c>
       <c r="R35" t="n">
-        <v>7001285</v>
+        <v>7001240</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4281,10 +4273,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124800335</v>
+        <v>124800324</v>
       </c>
       <c r="B36" t="n">
-        <v>78889</v>
+        <v>91361</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4293,25 +4285,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>864</v>
+        <v>2062</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4319,16 +4311,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440621</v>
+        <v>440680</v>
       </c>
       <c r="R36" t="n">
-        <v>7001181</v>
+        <v>7001258</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4369,6 +4364,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4387,10 +4383,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124800322</v>
+        <v>124800302</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>78889</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4403,21 +4399,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4431,10 +4427,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440696</v>
+        <v>440910</v>
       </c>
       <c r="R37" t="n">
-        <v>7001259</v>
+        <v>7001371</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4493,10 +4489,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124800305</v>
+        <v>124800294</v>
       </c>
       <c r="B38" t="n">
-        <v>91299</v>
+        <v>79851</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4505,25 +4501,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4537,10 +4533,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440874</v>
+        <v>441028</v>
       </c>
       <c r="R38" t="n">
-        <v>7001281</v>
+        <v>7001364</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4599,10 +4595,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124800308</v>
+        <v>124800330</v>
       </c>
       <c r="B39" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4615,21 +4611,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4643,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440850</v>
+        <v>440646</v>
       </c>
       <c r="R39" t="n">
-        <v>7001393</v>
+        <v>7001158</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4705,10 +4701,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124800295</v>
+        <v>124800308</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4721,21 +4717,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4749,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440940</v>
+        <v>440850</v>
       </c>
       <c r="R40" t="n">
-        <v>7001369</v>
+        <v>7001393</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,10 +4807,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124800321</v>
+        <v>124800309</v>
       </c>
       <c r="B41" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4827,21 +4823,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4855,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440709</v>
+        <v>440821</v>
       </c>
       <c r="R41" t="n">
-        <v>7001238</v>
+        <v>7001261</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4917,10 +4913,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124800314</v>
+        <v>124800297</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4933,21 +4929,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4961,10 +4957,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440785</v>
+        <v>440921</v>
       </c>
       <c r="R42" t="n">
-        <v>7001501</v>
+        <v>7001295</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4991,12 +4987,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5023,10 +5019,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124800333</v>
+        <v>124800320</v>
       </c>
       <c r="B43" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5039,21 +5035,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5067,10 +5063,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440628</v>
+        <v>440720</v>
       </c>
       <c r="R43" t="n">
-        <v>7001081</v>
+        <v>7001206</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5129,10 +5125,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124800338</v>
+        <v>124800298</v>
       </c>
       <c r="B44" t="n">
-        <v>96776</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5141,25 +5137,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2389</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5173,10 +5169,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440604</v>
+        <v>440916</v>
       </c>
       <c r="R44" t="n">
-        <v>7001240</v>
+        <v>7001320</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5235,10 +5231,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124800311</v>
+        <v>124800318</v>
       </c>
       <c r="B45" t="n">
-        <v>77753</v>
+        <v>96354</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5251,21 +5247,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>314</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5279,10 +5275,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440798</v>
+        <v>440721</v>
       </c>
       <c r="R45" t="n">
-        <v>7001239</v>
+        <v>7001216</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,10 +5337,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124800331</v>
+        <v>124800334</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>77753</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5357,21 +5353,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5385,10 +5381,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440637</v>
+        <v>440624</v>
       </c>
       <c r="R46" t="n">
-        <v>7001171</v>
+        <v>7001080</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5447,10 +5443,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124738082</v>
+        <v>124800293</v>
       </c>
       <c r="B47" t="n">
-        <v>88359</v>
+        <v>57529</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5463,34 +5459,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440684</v>
+        <v>441111</v>
       </c>
       <c r="R47" t="n">
-        <v>7001254</v>
+        <v>7001333</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5549,10 +5549,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124800298</v>
+        <v>124800315</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5565,21 +5565,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440916</v>
+        <v>440782</v>
       </c>
       <c r="R48" t="n">
-        <v>7001320</v>
+        <v>7001494</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5655,10 +5655,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124800332</v>
+        <v>124800310</v>
       </c>
       <c r="B49" t="n">
-        <v>74906</v>
+        <v>74901</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440630</v>
+        <v>440799</v>
       </c>
       <c r="R49" t="n">
-        <v>7001086</v>
+        <v>7001243</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -3319,10 +3319,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800304</v>
+        <v>124800336</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>91026</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3335,21 +3335,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3363,10 +3363,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440902</v>
+        <v>440616</v>
       </c>
       <c r="R27" t="n">
-        <v>7001332</v>
+        <v>7001215</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800336</v>
+        <v>124800304</v>
       </c>
       <c r="B28" t="n">
-        <v>91026</v>
+        <v>91012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3441,21 +3441,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440616</v>
+        <v>440902</v>
       </c>
       <c r="R28" t="n">
-        <v>7001215</v>
+        <v>7001332</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124800293</v>
+        <v>124800315</v>
       </c>
       <c r="B47" t="n">
-        <v>57529</v>
+        <v>78889</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>864</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>441111</v>
+        <v>440782</v>
       </c>
       <c r="R47" t="n">
-        <v>7001333</v>
+        <v>7001494</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124800315</v>
+        <v>124800293</v>
       </c>
       <c r="B48" t="n">
-        <v>78889</v>
+        <v>57529</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5565,21 +5565,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440782</v>
+        <v>441111</v>
       </c>
       <c r="R48" t="n">
-        <v>7001494</v>
+        <v>7001333</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800325</v>
+        <v>124800311</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>77753</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440674</v>
+        <v>440798</v>
       </c>
       <c r="R3" t="n">
-        <v>7001385</v>
+        <v>7001239</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800307</v>
+        <v>124800334</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>77753</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440872</v>
+        <v>440624</v>
       </c>
       <c r="R4" t="n">
-        <v>7001280</v>
+        <v>7001080</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800300</v>
+        <v>124800332</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>74906</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440915</v>
+        <v>440630</v>
       </c>
       <c r="R5" t="n">
-        <v>7001296</v>
+        <v>7001086</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800340</v>
+        <v>124800307</v>
       </c>
       <c r="B6" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,21 +1121,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440590</v>
+        <v>440872</v>
       </c>
       <c r="R6" t="n">
-        <v>7001362</v>
+        <v>7001280</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800305</v>
+        <v>124800338</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>96776</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,25 +1223,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>2389</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440874</v>
+        <v>440604</v>
       </c>
       <c r="R7" t="n">
-        <v>7001281</v>
+        <v>7001240</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800322</v>
+        <v>124800302</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>78889</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440696</v>
+        <v>440910</v>
       </c>
       <c r="R8" t="n">
-        <v>7001259</v>
+        <v>7001371</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800332</v>
+        <v>124800323</v>
       </c>
       <c r="B9" t="n">
-        <v>74906</v>
+        <v>74901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,21 +1439,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440630</v>
+        <v>440681</v>
       </c>
       <c r="R9" t="n">
-        <v>7001086</v>
+        <v>7001285</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800316</v>
+        <v>124800320</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440773</v>
+        <v>440720</v>
       </c>
       <c r="R10" t="n">
-        <v>7001489</v>
+        <v>7001206</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,10 +1635,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800321</v>
+        <v>124801009</v>
       </c>
       <c r="B11" t="n">
-        <v>91008</v>
+        <v>94769</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,25 +1647,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>2411</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Nordlig källmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Philonotis tomentella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Molendo</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440709</v>
+        <v>440900</v>
       </c>
       <c r="R11" t="n">
-        <v>7001238</v>
+        <v>7001371</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800335</v>
+        <v>124800295</v>
       </c>
       <c r="B12" t="n">
-        <v>78889</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,21 +1757,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440621</v>
+        <v>440940</v>
       </c>
       <c r="R12" t="n">
-        <v>7001181</v>
+        <v>7001369</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124740889</v>
+        <v>124800335</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>78889</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,34 +1863,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440684</v>
+        <v>440621</v>
       </c>
       <c r="R13" t="n">
-        <v>7001254</v>
+        <v>7001181</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,12 +1921,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1953,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800327</v>
+        <v>124740817</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1982,21 +1986,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440672</v>
+        <v>440684</v>
       </c>
       <c r="R14" t="n">
-        <v>7001361</v>
+        <v>7001254</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,12 +2023,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2055,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800314</v>
+        <v>124738082</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2071,38 +2071,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440785</v>
+        <v>440684</v>
       </c>
       <c r="R15" t="n">
-        <v>7001501</v>
+        <v>7001254</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,10 +2157,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800311</v>
+        <v>124800321</v>
       </c>
       <c r="B16" t="n">
-        <v>77753</v>
+        <v>91008</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2177,21 +2173,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>314</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2205,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440798</v>
+        <v>440709</v>
       </c>
       <c r="R16" t="n">
-        <v>7001239</v>
+        <v>7001238</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2267,7 +2263,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124740817</v>
+        <v>124800326</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2300,17 +2296,21 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440684</v>
+        <v>440672</v>
       </c>
       <c r="R17" t="n">
-        <v>7001254</v>
+        <v>7001335</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,12 +2337,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2369,10 +2369,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124801009</v>
+        <v>124800306</v>
       </c>
       <c r="B18" t="n">
-        <v>94769</v>
+        <v>88359</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2381,25 +2381,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2411</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordlig källmossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Philonotis tomentella</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Molendo</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440900</v>
+        <v>440872</v>
       </c>
       <c r="R18" t="n">
-        <v>7001371</v>
+        <v>7001384</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2475,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800319</v>
+        <v>124800327</v>
       </c>
       <c r="B19" t="n">
-        <v>97185</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2487,25 +2487,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220686</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440720</v>
+        <v>440672</v>
       </c>
       <c r="R19" t="n">
-        <v>7001201</v>
+        <v>7001361</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2581,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800313</v>
+        <v>124800314</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440791</v>
+        <v>440785</v>
       </c>
       <c r="R20" t="n">
-        <v>7001239</v>
+        <v>7001501</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2687,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800323</v>
+        <v>124800316</v>
       </c>
       <c r="B21" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,21 +2703,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440681</v>
+        <v>440773</v>
       </c>
       <c r="R21" t="n">
-        <v>7001285</v>
+        <v>7001489</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800295</v>
+        <v>124800300</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2809,21 +2809,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440940</v>
+        <v>440915</v>
       </c>
       <c r="R22" t="n">
-        <v>7001369</v>
+        <v>7001296</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800296</v>
+        <v>124800298</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2915,21 +2915,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440939</v>
+        <v>440916</v>
       </c>
       <c r="R23" t="n">
-        <v>7001309</v>
+        <v>7001320</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,10 +3005,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800329</v>
+        <v>124800297</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3021,21 +3021,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440658</v>
+        <v>440921</v>
       </c>
       <c r="R24" t="n">
-        <v>7001354</v>
+        <v>7001295</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800306</v>
+        <v>124800309</v>
       </c>
       <c r="B25" t="n">
-        <v>88359</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3127,21 +3127,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440872</v>
+        <v>440821</v>
       </c>
       <c r="R25" t="n">
-        <v>7001384</v>
+        <v>7001261</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124738082</v>
+        <v>124800304</v>
       </c>
       <c r="B26" t="n">
-        <v>88359</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3233,34 +3233,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440684</v>
+        <v>440902</v>
       </c>
       <c r="R26" t="n">
-        <v>7001254</v>
+        <v>7001332</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3287,12 +3291,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3319,10 +3323,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800336</v>
+        <v>124800328</v>
       </c>
       <c r="B27" t="n">
-        <v>91026</v>
+        <v>95335</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3331,25 +3335,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>2809</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3363,10 +3367,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440616</v>
+        <v>440661</v>
       </c>
       <c r="R27" t="n">
-        <v>7001215</v>
+        <v>7001244</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,10 +3429,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800304</v>
+        <v>124800308</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3441,21 +3445,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3469,10 +3473,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440902</v>
+        <v>440850</v>
       </c>
       <c r="R28" t="n">
-        <v>7001332</v>
+        <v>7001393</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,10 +3535,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800326</v>
+        <v>124800294</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>79851</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3543,25 +3547,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3575,10 +3579,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440672</v>
+        <v>441028</v>
       </c>
       <c r="R29" t="n">
-        <v>7001335</v>
+        <v>7001364</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3637,10 +3641,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800333</v>
+        <v>124800336</v>
       </c>
       <c r="B30" t="n">
-        <v>82597</v>
+        <v>91026</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3653,21 +3657,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3681,10 +3685,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440628</v>
+        <v>440616</v>
       </c>
       <c r="R30" t="n">
-        <v>7001081</v>
+        <v>7001215</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3743,10 +3747,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800328</v>
+        <v>124800310</v>
       </c>
       <c r="B31" t="n">
-        <v>95335</v>
+        <v>74901</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3755,25 +3759,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3787,10 +3791,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440661</v>
+        <v>440799</v>
       </c>
       <c r="R31" t="n">
-        <v>7001244</v>
+        <v>7001243</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3849,10 +3853,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124800303</v>
+        <v>124800305</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3865,21 +3869,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3893,10 +3897,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440909</v>
+        <v>440874</v>
       </c>
       <c r="R32" t="n">
-        <v>7001374</v>
+        <v>7001281</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,10 +3959,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124800299</v>
+        <v>124800324</v>
       </c>
       <c r="B33" t="n">
-        <v>78889</v>
+        <v>91361</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3967,25 +3971,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>2062</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3993,16 +3997,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440915</v>
+        <v>440680</v>
       </c>
       <c r="R33" t="n">
-        <v>7001377</v>
+        <v>7001258</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4043,6 +4050,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4061,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124800331</v>
+        <v>124800318</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4077,21 +4085,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4105,10 +4113,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440637</v>
+        <v>440721</v>
       </c>
       <c r="R34" t="n">
-        <v>7001171</v>
+        <v>7001216</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,10 +4175,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124800338</v>
+        <v>124800330</v>
       </c>
       <c r="B35" t="n">
-        <v>96776</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4179,25 +4187,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2389</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4211,10 +4219,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440604</v>
+        <v>440646</v>
       </c>
       <c r="R35" t="n">
-        <v>7001240</v>
+        <v>7001158</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4273,10 +4281,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124800324</v>
+        <v>124800329</v>
       </c>
       <c r="B36" t="n">
-        <v>91361</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4285,25 +4293,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4311,19 +4319,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440680</v>
+        <v>440658</v>
       </c>
       <c r="R36" t="n">
-        <v>7001258</v>
+        <v>7001354</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4364,7 +4369,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4383,10 +4387,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124800302</v>
+        <v>124800322</v>
       </c>
       <c r="B37" t="n">
-        <v>78889</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4399,21 +4403,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4427,10 +4431,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440910</v>
+        <v>440696</v>
       </c>
       <c r="R37" t="n">
-        <v>7001371</v>
+        <v>7001259</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4489,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124800294</v>
+        <v>124800293</v>
       </c>
       <c r="B38" t="n">
-        <v>79851</v>
+        <v>57529</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4501,25 +4505,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4533,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441028</v>
+        <v>441111</v>
       </c>
       <c r="R38" t="n">
-        <v>7001364</v>
+        <v>7001333</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4599,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124800330</v>
+        <v>124800325</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -4639,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440646</v>
+        <v>440674</v>
       </c>
       <c r="R39" t="n">
-        <v>7001158</v>
+        <v>7001385</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4701,10 +4705,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124800308</v>
+        <v>124800296</v>
       </c>
       <c r="B40" t="n">
-        <v>88359</v>
+        <v>91012</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4717,21 +4721,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4745,10 +4749,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440850</v>
+        <v>440939</v>
       </c>
       <c r="R40" t="n">
-        <v>7001393</v>
+        <v>7001309</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4807,10 +4811,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124800309</v>
+        <v>124800315</v>
       </c>
       <c r="B41" t="n">
-        <v>91012</v>
+        <v>78889</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4823,21 +4827,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4851,10 +4855,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440821</v>
+        <v>440782</v>
       </c>
       <c r="R41" t="n">
-        <v>7001261</v>
+        <v>7001494</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4913,10 +4917,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124800297</v>
+        <v>124800299</v>
       </c>
       <c r="B42" t="n">
-        <v>91026</v>
+        <v>78889</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4929,21 +4933,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4957,10 +4961,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440921</v>
+        <v>440915</v>
       </c>
       <c r="R42" t="n">
-        <v>7001295</v>
+        <v>7001377</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5019,7 +5023,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124800320</v>
+        <v>124800313</v>
       </c>
       <c r="B43" t="n">
         <v>78810</v>
@@ -5063,10 +5067,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440720</v>
+        <v>440791</v>
       </c>
       <c r="R43" t="n">
-        <v>7001206</v>
+        <v>7001239</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5125,7 +5129,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124800298</v>
+        <v>124800331</v>
       </c>
       <c r="B44" t="n">
         <v>78810</v>
@@ -5169,10 +5173,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440916</v>
+        <v>440637</v>
       </c>
       <c r="R44" t="n">
-        <v>7001320</v>
+        <v>7001171</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5231,10 +5235,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124800318</v>
+        <v>124800303</v>
       </c>
       <c r="B45" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5247,21 +5251,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5275,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440721</v>
+        <v>440909</v>
       </c>
       <c r="R45" t="n">
-        <v>7001216</v>
+        <v>7001374</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5337,10 +5341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124800334</v>
+        <v>124800340</v>
       </c>
       <c r="B46" t="n">
-        <v>77753</v>
+        <v>74901</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5353,21 +5357,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>314</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5381,10 +5385,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440624</v>
+        <v>440590</v>
       </c>
       <c r="R46" t="n">
-        <v>7001080</v>
+        <v>7001362</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5443,10 +5447,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124800315</v>
+        <v>124800319</v>
       </c>
       <c r="B47" t="n">
-        <v>78889</v>
+        <v>97185</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5455,25 +5459,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>864</v>
+        <v>220686</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5487,10 +5491,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440782</v>
+        <v>440720</v>
       </c>
       <c r="R47" t="n">
-        <v>7001494</v>
+        <v>7001201</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5549,10 +5553,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124800293</v>
+        <v>124740889</v>
       </c>
       <c r="B48" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5565,38 +5569,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>441111</v>
+        <v>440684</v>
       </c>
       <c r="R48" t="n">
-        <v>7001333</v>
+        <v>7001254</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5655,10 +5655,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124800310</v>
+        <v>124800333</v>
       </c>
       <c r="B49" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440799</v>
+        <v>440628</v>
       </c>
       <c r="R49" t="n">
-        <v>7001243</v>
+        <v>7001081</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800302</v>
+        <v>124800323</v>
       </c>
       <c r="B8" t="n">
-        <v>78889</v>
+        <v>74901</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440910</v>
+        <v>440681</v>
       </c>
       <c r="R8" t="n">
-        <v>7001371</v>
+        <v>7001285</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800323</v>
+        <v>124800302</v>
       </c>
       <c r="B9" t="n">
-        <v>74901</v>
+        <v>78889</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,21 +1439,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440681</v>
+        <v>440910</v>
       </c>
       <c r="R9" t="n">
-        <v>7001285</v>
+        <v>7001371</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124738082</v>
+        <v>124800321</v>
       </c>
       <c r="B15" t="n">
-        <v>88359</v>
+        <v>91008</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2071,34 +2071,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440684</v>
+        <v>440709</v>
       </c>
       <c r="R15" t="n">
-        <v>7001254</v>
+        <v>7001238</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2125,12 +2129,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2157,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800321</v>
+        <v>124738082</v>
       </c>
       <c r="B16" t="n">
-        <v>91008</v>
+        <v>88359</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2173,38 +2177,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440709</v>
+        <v>440684</v>
       </c>
       <c r="R16" t="n">
-        <v>7001238</v>
+        <v>7001254</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2231,12 +2231,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800323</v>
+        <v>124800302</v>
       </c>
       <c r="B8" t="n">
-        <v>74901</v>
+        <v>78889</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440681</v>
+        <v>440910</v>
       </c>
       <c r="R8" t="n">
-        <v>7001285</v>
+        <v>7001371</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800302</v>
+        <v>124800323</v>
       </c>
       <c r="B9" t="n">
-        <v>78889</v>
+        <v>74901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,21 +1439,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440910</v>
+        <v>440681</v>
       </c>
       <c r="R9" t="n">
-        <v>7001371</v>
+        <v>7001285</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124800293</v>
+        <v>124800325</v>
       </c>
       <c r="B38" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4509,21 +4509,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441111</v>
+        <v>440674</v>
       </c>
       <c r="R38" t="n">
-        <v>7001333</v>
+        <v>7001385</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4599,10 +4599,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124800325</v>
+        <v>124800293</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4615,21 +4615,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440674</v>
+        <v>441111</v>
       </c>
       <c r="R39" t="n">
-        <v>7001385</v>
+        <v>7001333</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800311</v>
+        <v>124800306</v>
       </c>
       <c r="B3" t="n">
-        <v>77753</v>
+        <v>88359</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>314</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440798</v>
+        <v>440872</v>
       </c>
       <c r="R3" t="n">
-        <v>7001239</v>
+        <v>7001384</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800334</v>
+        <v>124800321</v>
       </c>
       <c r="B4" t="n">
-        <v>77753</v>
+        <v>91008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>314</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440624</v>
+        <v>440709</v>
       </c>
       <c r="R4" t="n">
-        <v>7001080</v>
+        <v>7001238</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800332</v>
+        <v>124800328</v>
       </c>
       <c r="B5" t="n">
-        <v>74906</v>
+        <v>95335</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1011,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1467</v>
+        <v>2809</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440630</v>
+        <v>440661</v>
       </c>
       <c r="R5" t="n">
-        <v>7001086</v>
+        <v>7001244</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800307</v>
+        <v>124800329</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,21 +1121,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440872</v>
+        <v>440658</v>
       </c>
       <c r="R6" t="n">
-        <v>7001280</v>
+        <v>7001354</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800338</v>
+        <v>124800303</v>
       </c>
       <c r="B7" t="n">
-        <v>96776</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,25 +1223,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2389</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440604</v>
+        <v>440909</v>
       </c>
       <c r="R7" t="n">
-        <v>7001240</v>
+        <v>7001374</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800302</v>
+        <v>124800340</v>
       </c>
       <c r="B8" t="n">
-        <v>78889</v>
+        <v>74901</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440910</v>
+        <v>440590</v>
       </c>
       <c r="R8" t="n">
-        <v>7001371</v>
+        <v>7001362</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800323</v>
+        <v>124800307</v>
       </c>
       <c r="B9" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,21 +1439,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440681</v>
+        <v>440872</v>
       </c>
       <c r="R9" t="n">
-        <v>7001285</v>
+        <v>7001280</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800320</v>
+        <v>124800326</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440720</v>
+        <v>440672</v>
       </c>
       <c r="R10" t="n">
-        <v>7001206</v>
+        <v>7001335</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,10 +1635,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124801009</v>
+        <v>124800299</v>
       </c>
       <c r="B11" t="n">
-        <v>94769</v>
+        <v>78889</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,25 +1647,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2411</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordlig källmossa</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Philonotis tomentella</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Molendo</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440900</v>
+        <v>440915</v>
       </c>
       <c r="R11" t="n">
-        <v>7001371</v>
+        <v>7001377</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800295</v>
+        <v>124801009</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>94769</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,25 +1753,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>2411</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordlig källmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Philonotis tomentella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Molendo</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440940</v>
+        <v>440900</v>
       </c>
       <c r="R12" t="n">
-        <v>7001369</v>
+        <v>7001371</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800335</v>
+        <v>124800313</v>
       </c>
       <c r="B13" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440621</v>
+        <v>440791</v>
       </c>
       <c r="R13" t="n">
-        <v>7001181</v>
+        <v>7001239</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,7 +1953,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124740817</v>
+        <v>124800331</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1986,17 +1986,21 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440684</v>
+        <v>440637</v>
       </c>
       <c r="R14" t="n">
-        <v>7001254</v>
+        <v>7001171</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,12 +2027,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2055,10 +2059,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800321</v>
+        <v>124800300</v>
       </c>
       <c r="B15" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2071,21 +2075,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2099,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440709</v>
+        <v>440915</v>
       </c>
       <c r="R15" t="n">
-        <v>7001238</v>
+        <v>7001296</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,10 +2165,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124738082</v>
+        <v>124800295</v>
       </c>
       <c r="B16" t="n">
-        <v>88359</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2177,34 +2181,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440684</v>
+        <v>440940</v>
       </c>
       <c r="R16" t="n">
-        <v>7001254</v>
+        <v>7001369</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2231,12 +2239,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800326</v>
+        <v>124800304</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2279,21 +2287,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2307,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440672</v>
+        <v>440902</v>
       </c>
       <c r="R17" t="n">
-        <v>7001335</v>
+        <v>7001332</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800306</v>
+        <v>124800332</v>
       </c>
       <c r="B18" t="n">
-        <v>88359</v>
+        <v>74906</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2385,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>1467</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2413,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440872</v>
+        <v>440630</v>
       </c>
       <c r="R18" t="n">
-        <v>7001384</v>
+        <v>7001086</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2475,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800327</v>
+        <v>124800293</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2491,21 +2499,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2519,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440672</v>
+        <v>441111</v>
       </c>
       <c r="R19" t="n">
-        <v>7001361</v>
+        <v>7001333</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2581,10 +2589,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800314</v>
+        <v>124800319</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>97185</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2593,25 +2601,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220686</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2625,10 +2633,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440785</v>
+        <v>440720</v>
       </c>
       <c r="R20" t="n">
-        <v>7001501</v>
+        <v>7001201</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2655,12 +2663,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2687,10 +2695,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800316</v>
+        <v>124740889</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,38 +2711,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440773</v>
+        <v>440684</v>
       </c>
       <c r="R21" t="n">
-        <v>7001489</v>
+        <v>7001254</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2761,12 +2765,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2793,10 +2797,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800300</v>
+        <v>124800336</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>91026</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2809,21 +2813,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2837,10 +2841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440915</v>
+        <v>440616</v>
       </c>
       <c r="R22" t="n">
-        <v>7001296</v>
+        <v>7001215</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2899,10 +2903,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800298</v>
+        <v>124800324</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>91361</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2911,25 +2915,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2937,16 +2941,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440916</v>
+        <v>440680</v>
       </c>
       <c r="R23" t="n">
-        <v>7001320</v>
+        <v>7001258</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,6 +2994,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3005,10 +3013,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800297</v>
+        <v>124800338</v>
       </c>
       <c r="B24" t="n">
-        <v>91026</v>
+        <v>96776</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3017,25 +3025,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>2389</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3049,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440921</v>
+        <v>440604</v>
       </c>
       <c r="R24" t="n">
-        <v>7001295</v>
+        <v>7001240</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3217,10 +3225,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800304</v>
+        <v>124800335</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>78889</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3233,21 +3241,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3261,10 +3269,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440902</v>
+        <v>440621</v>
       </c>
       <c r="R26" t="n">
-        <v>7001332</v>
+        <v>7001181</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,10 +3331,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800328</v>
+        <v>124800308</v>
       </c>
       <c r="B27" t="n">
-        <v>95335</v>
+        <v>88359</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3335,25 +3343,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2809</v>
+        <v>510</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3367,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440661</v>
+        <v>440850</v>
       </c>
       <c r="R27" t="n">
-        <v>7001244</v>
+        <v>7001393</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,10 +3437,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800308</v>
+        <v>124800297</v>
       </c>
       <c r="B28" t="n">
-        <v>88359</v>
+        <v>91026</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3445,21 +3453,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3473,10 +3481,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440850</v>
+        <v>440921</v>
       </c>
       <c r="R28" t="n">
-        <v>7001393</v>
+        <v>7001295</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3535,10 +3543,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800294</v>
+        <v>124800327</v>
       </c>
       <c r="B29" t="n">
-        <v>79851</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3547,25 +3555,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3579,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441028</v>
+        <v>440672</v>
       </c>
       <c r="R29" t="n">
-        <v>7001364</v>
+        <v>7001361</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3641,10 +3649,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800336</v>
+        <v>124800320</v>
       </c>
       <c r="B30" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3657,21 +3665,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3685,10 +3693,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440616</v>
+        <v>440720</v>
       </c>
       <c r="R30" t="n">
-        <v>7001215</v>
+        <v>7001206</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3747,10 +3755,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800310</v>
+        <v>124800305</v>
       </c>
       <c r="B31" t="n">
-        <v>74901</v>
+        <v>91299</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3763,21 +3771,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3791,10 +3799,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440799</v>
+        <v>440874</v>
       </c>
       <c r="R31" t="n">
-        <v>7001243</v>
+        <v>7001281</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,10 +3861,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124800305</v>
+        <v>124800315</v>
       </c>
       <c r="B32" t="n">
-        <v>91299</v>
+        <v>78889</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3869,21 +3877,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3897,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440874</v>
+        <v>440782</v>
       </c>
       <c r="R32" t="n">
-        <v>7001281</v>
+        <v>7001494</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3959,10 +3967,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124800324</v>
+        <v>124800330</v>
       </c>
       <c r="B33" t="n">
-        <v>91361</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3971,25 +3979,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3997,19 +4005,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440680</v>
+        <v>440646</v>
       </c>
       <c r="R33" t="n">
-        <v>7001258</v>
+        <v>7001158</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4050,7 +4055,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4069,10 +4073,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124800318</v>
+        <v>124800323</v>
       </c>
       <c r="B34" t="n">
-        <v>96354</v>
+        <v>74901</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4085,21 +4089,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4113,10 +4117,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440721</v>
+        <v>440681</v>
       </c>
       <c r="R34" t="n">
-        <v>7001216</v>
+        <v>7001285</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4175,7 +4179,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124800330</v>
+        <v>124800325</v>
       </c>
       <c r="B35" t="n">
         <v>78810</v>
@@ -4219,10 +4223,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440646</v>
+        <v>440674</v>
       </c>
       <c r="R35" t="n">
-        <v>7001158</v>
+        <v>7001385</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4281,10 +4285,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124800329</v>
+        <v>124800296</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4297,21 +4301,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4325,10 +4329,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440658</v>
+        <v>440939</v>
       </c>
       <c r="R36" t="n">
-        <v>7001354</v>
+        <v>7001309</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4387,10 +4391,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124800322</v>
+        <v>124800311</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>77753</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4403,21 +4407,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4431,10 +4435,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440696</v>
+        <v>440798</v>
       </c>
       <c r="R37" t="n">
-        <v>7001259</v>
+        <v>7001239</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4493,10 +4497,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124800325</v>
+        <v>124800294</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>79851</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4505,25 +4509,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4537,10 +4541,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440674</v>
+        <v>441028</v>
       </c>
       <c r="R38" t="n">
-        <v>7001385</v>
+        <v>7001364</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4599,10 +4603,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124800293</v>
+        <v>124800333</v>
       </c>
       <c r="B39" t="n">
-        <v>57529</v>
+        <v>82597</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4615,21 +4619,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4643,10 +4647,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>441111</v>
+        <v>440628</v>
       </c>
       <c r="R39" t="n">
-        <v>7001333</v>
+        <v>7001081</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4705,10 +4709,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124800296</v>
+        <v>124800316</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4721,21 +4725,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4749,10 +4753,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440939</v>
+        <v>440773</v>
       </c>
       <c r="R40" t="n">
-        <v>7001309</v>
+        <v>7001489</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,10 +4815,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124800315</v>
+        <v>124800334</v>
       </c>
       <c r="B41" t="n">
-        <v>78889</v>
+        <v>77753</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4827,21 +4831,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>864</v>
+        <v>314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4855,10 +4859,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440782</v>
+        <v>440624</v>
       </c>
       <c r="R41" t="n">
-        <v>7001494</v>
+        <v>7001080</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4917,10 +4921,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124800299</v>
+        <v>124800314</v>
       </c>
       <c r="B42" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4933,21 +4937,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4961,10 +4965,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440915</v>
+        <v>440785</v>
       </c>
       <c r="R42" t="n">
-        <v>7001377</v>
+        <v>7001501</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4991,12 +4995,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5023,10 +5027,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124800313</v>
+        <v>124738082</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5039,38 +5043,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440791</v>
+        <v>440684</v>
       </c>
       <c r="R43" t="n">
-        <v>7001239</v>
+        <v>7001254</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5129,7 +5129,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124800331</v>
+        <v>124740817</v>
       </c>
       <c r="B44" t="n">
         <v>78810</v>
@@ -5162,21 +5162,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440637</v>
+        <v>440684</v>
       </c>
       <c r="R44" t="n">
-        <v>7001171</v>
+        <v>7001254</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5203,12 +5199,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5235,10 +5231,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124800303</v>
+        <v>124800310</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5251,21 +5247,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5279,10 +5275,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440909</v>
+        <v>440799</v>
       </c>
       <c r="R45" t="n">
-        <v>7001374</v>
+        <v>7001243</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,10 +5337,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124800340</v>
+        <v>124800318</v>
       </c>
       <c r="B46" t="n">
-        <v>74901</v>
+        <v>96354</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5357,21 +5353,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5385,10 +5381,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440590</v>
+        <v>440721</v>
       </c>
       <c r="R46" t="n">
-        <v>7001362</v>
+        <v>7001216</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5447,10 +5443,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124800319</v>
+        <v>124800322</v>
       </c>
       <c r="B47" t="n">
-        <v>97185</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5459,25 +5455,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220686</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5491,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440720</v>
+        <v>440696</v>
       </c>
       <c r="R47" t="n">
-        <v>7001201</v>
+        <v>7001259</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5553,10 +5549,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124740889</v>
+        <v>124800302</v>
       </c>
       <c r="B48" t="n">
-        <v>91030</v>
+        <v>78889</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5569,34 +5565,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440684</v>
+        <v>440910</v>
       </c>
       <c r="R48" t="n">
-        <v>7001254</v>
+        <v>7001371</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5655,10 +5655,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124800333</v>
+        <v>124800298</v>
       </c>
       <c r="B49" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440628</v>
+        <v>440916</v>
       </c>
       <c r="R49" t="n">
-        <v>7001081</v>
+        <v>7001320</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800306</v>
+        <v>124800322</v>
       </c>
       <c r="B3" t="n">
-        <v>88359</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440872</v>
+        <v>440696</v>
       </c>
       <c r="R3" t="n">
-        <v>7001384</v>
+        <v>7001259</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800321</v>
+        <v>124800325</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440709</v>
+        <v>440674</v>
       </c>
       <c r="R4" t="n">
-        <v>7001238</v>
+        <v>7001385</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800328</v>
+        <v>124800307</v>
       </c>
       <c r="B5" t="n">
-        <v>95335</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1011,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440661</v>
+        <v>440872</v>
       </c>
       <c r="R5" t="n">
-        <v>7001244</v>
+        <v>7001280</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800329</v>
+        <v>124800303</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440658</v>
+        <v>440909</v>
       </c>
       <c r="R6" t="n">
-        <v>7001354</v>
+        <v>7001374</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800303</v>
+        <v>124800319</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>97185</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,25 +1223,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220686</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440909</v>
+        <v>440720</v>
       </c>
       <c r="R7" t="n">
-        <v>7001374</v>
+        <v>7001201</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800340</v>
+        <v>124800338</v>
       </c>
       <c r="B8" t="n">
-        <v>74901</v>
+        <v>96776</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,25 +1329,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>2389</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440590</v>
+        <v>440604</v>
       </c>
       <c r="R8" t="n">
-        <v>7001362</v>
+        <v>7001240</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800307</v>
+        <v>124800308</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,21 +1439,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440872</v>
+        <v>440850</v>
       </c>
       <c r="R9" t="n">
-        <v>7001280</v>
+        <v>7001393</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800326</v>
+        <v>124800329</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440672</v>
+        <v>440658</v>
       </c>
       <c r="R10" t="n">
-        <v>7001335</v>
+        <v>7001354</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,10 +1635,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800299</v>
+        <v>124800330</v>
       </c>
       <c r="B11" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,21 +1651,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440915</v>
+        <v>440646</v>
       </c>
       <c r="R11" t="n">
-        <v>7001377</v>
+        <v>7001158</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124801009</v>
+        <v>124800326</v>
       </c>
       <c r="B12" t="n">
-        <v>94769</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,25 +1753,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2411</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordlig källmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Philonotis tomentella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Molendo</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440900</v>
+        <v>440672</v>
       </c>
       <c r="R12" t="n">
-        <v>7001371</v>
+        <v>7001335</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1953,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800331</v>
+        <v>124800305</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1969,21 +1969,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440637</v>
+        <v>440874</v>
       </c>
       <c r="R14" t="n">
-        <v>7001171</v>
+        <v>7001281</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,10 +2059,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800300</v>
+        <v>124800294</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>79851</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2071,25 +2071,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440915</v>
+        <v>441028</v>
       </c>
       <c r="R15" t="n">
-        <v>7001296</v>
+        <v>7001364</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,10 +2165,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800295</v>
+        <v>124800318</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>96354</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440940</v>
+        <v>440721</v>
       </c>
       <c r="R16" t="n">
-        <v>7001369</v>
+        <v>7001216</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800304</v>
+        <v>124800315</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>78889</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,21 +2287,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440902</v>
+        <v>440782</v>
       </c>
       <c r="R17" t="n">
-        <v>7001332</v>
+        <v>7001494</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800332</v>
+        <v>124800297</v>
       </c>
       <c r="B18" t="n">
-        <v>74906</v>
+        <v>91026</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440630</v>
+        <v>440921</v>
       </c>
       <c r="R18" t="n">
-        <v>7001086</v>
+        <v>7001295</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800293</v>
+        <v>124800323</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2499,21 +2499,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441111</v>
+        <v>440681</v>
       </c>
       <c r="R19" t="n">
-        <v>7001333</v>
+        <v>7001285</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,10 +2589,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800319</v>
+        <v>124800331</v>
       </c>
       <c r="B20" t="n">
-        <v>97185</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2601,25 +2601,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220686</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440720</v>
+        <v>440637</v>
       </c>
       <c r="R20" t="n">
-        <v>7001201</v>
+        <v>7001171</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,10 +2695,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124740889</v>
+        <v>124800340</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2711,34 +2711,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440684</v>
+        <v>440590</v>
       </c>
       <c r="R21" t="n">
-        <v>7001254</v>
+        <v>7001362</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,12 +2769,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2797,10 +2801,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800336</v>
+        <v>124800299</v>
       </c>
       <c r="B22" t="n">
-        <v>91026</v>
+        <v>78889</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2813,21 +2817,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2841,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440616</v>
+        <v>440915</v>
       </c>
       <c r="R22" t="n">
-        <v>7001215</v>
+        <v>7001377</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2903,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800324</v>
+        <v>124800304</v>
       </c>
       <c r="B23" t="n">
-        <v>91361</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2915,25 +2919,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2941,19 +2945,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440680</v>
+        <v>440902</v>
       </c>
       <c r="R23" t="n">
-        <v>7001258</v>
+        <v>7001332</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2994,7 +2995,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800338</v>
+        <v>124800302</v>
       </c>
       <c r="B24" t="n">
-        <v>96776</v>
+        <v>78889</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3025,25 +3025,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2389</v>
+        <v>864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440604</v>
+        <v>440910</v>
       </c>
       <c r="R24" t="n">
-        <v>7001240</v>
+        <v>7001371</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800309</v>
+        <v>124800332</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>74906</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3135,21 +3135,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440821</v>
+        <v>440630</v>
       </c>
       <c r="R25" t="n">
-        <v>7001261</v>
+        <v>7001086</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800335</v>
+        <v>124740889</v>
       </c>
       <c r="B26" t="n">
-        <v>78889</v>
+        <v>91030</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3241,38 +3241,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440621</v>
+        <v>440684</v>
       </c>
       <c r="R26" t="n">
-        <v>7001181</v>
+        <v>7001254</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3299,12 +3295,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3331,10 +3327,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800308</v>
+        <v>124800334</v>
       </c>
       <c r="B27" t="n">
-        <v>88359</v>
+        <v>77753</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3347,21 +3343,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>510</v>
+        <v>314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3375,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440850</v>
+        <v>440624</v>
       </c>
       <c r="R27" t="n">
-        <v>7001393</v>
+        <v>7001080</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3437,10 +3433,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800297</v>
+        <v>124800328</v>
       </c>
       <c r="B28" t="n">
-        <v>91026</v>
+        <v>95335</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3449,25 +3445,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>2809</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3481,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440921</v>
+        <v>440661</v>
       </c>
       <c r="R28" t="n">
-        <v>7001295</v>
+        <v>7001244</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3543,7 +3539,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800327</v>
+        <v>124800316</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3587,10 +3583,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440672</v>
+        <v>440773</v>
       </c>
       <c r="R29" t="n">
-        <v>7001361</v>
+        <v>7001489</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3649,10 +3645,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800320</v>
+        <v>124800311</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>77753</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3665,21 +3661,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3693,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440720</v>
+        <v>440798</v>
       </c>
       <c r="R30" t="n">
-        <v>7001206</v>
+        <v>7001239</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3755,10 +3751,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800305</v>
+        <v>124800321</v>
       </c>
       <c r="B31" t="n">
-        <v>91299</v>
+        <v>91008</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3771,21 +3767,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3799,10 +3795,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440874</v>
+        <v>440709</v>
       </c>
       <c r="R31" t="n">
-        <v>7001281</v>
+        <v>7001238</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3861,10 +3857,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124800315</v>
+        <v>124800310</v>
       </c>
       <c r="B32" t="n">
-        <v>78889</v>
+        <v>74901</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3877,21 +3873,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3905,10 +3901,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440782</v>
+        <v>440799</v>
       </c>
       <c r="R32" t="n">
-        <v>7001494</v>
+        <v>7001243</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3967,10 +3963,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124800330</v>
+        <v>124800324</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>91361</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3979,25 +3975,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4005,16 +4001,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440646</v>
+        <v>440680</v>
       </c>
       <c r="R33" t="n">
-        <v>7001158</v>
+        <v>7001258</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4055,6 +4054,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4073,10 +4073,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124800323</v>
+        <v>124801009</v>
       </c>
       <c r="B34" t="n">
-        <v>74901</v>
+        <v>94769</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4085,25 +4085,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>2411</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Nordlig källmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Philonotis tomentella</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Molendo</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440681</v>
+        <v>440900</v>
       </c>
       <c r="R34" t="n">
-        <v>7001285</v>
+        <v>7001371</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124800325</v>
+        <v>124800293</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4195,21 +4195,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440674</v>
+        <v>441111</v>
       </c>
       <c r="R35" t="n">
-        <v>7001385</v>
+        <v>7001333</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4285,7 +4285,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124800296</v>
+        <v>124800295</v>
       </c>
       <c r="B36" t="n">
         <v>91012</v>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440939</v>
+        <v>440940</v>
       </c>
       <c r="R36" t="n">
-        <v>7001309</v>
+        <v>7001369</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4391,10 +4391,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124800311</v>
+        <v>124800335</v>
       </c>
       <c r="B37" t="n">
-        <v>77753</v>
+        <v>78889</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4407,21 +4407,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>314</v>
+        <v>864</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440798</v>
+        <v>440621</v>
       </c>
       <c r="R37" t="n">
-        <v>7001239</v>
+        <v>7001181</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4497,10 +4497,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124800294</v>
+        <v>124800309</v>
       </c>
       <c r="B38" t="n">
-        <v>79851</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4509,25 +4509,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441028</v>
+        <v>440821</v>
       </c>
       <c r="R38" t="n">
-        <v>7001364</v>
+        <v>7001261</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4603,10 +4603,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124800333</v>
+        <v>124800327</v>
       </c>
       <c r="B39" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4619,21 +4619,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440628</v>
+        <v>440672</v>
       </c>
       <c r="R39" t="n">
-        <v>7001081</v>
+        <v>7001361</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4709,10 +4709,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124800316</v>
+        <v>124800296</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4725,21 +4725,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440773</v>
+        <v>440939</v>
       </c>
       <c r="R40" t="n">
-        <v>7001489</v>
+        <v>7001309</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4815,10 +4815,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124800334</v>
+        <v>124800314</v>
       </c>
       <c r="B41" t="n">
-        <v>77753</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4831,21 +4831,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4859,10 +4859,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440624</v>
+        <v>440785</v>
       </c>
       <c r="R41" t="n">
-        <v>7001080</v>
+        <v>7001501</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4889,12 +4889,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4921,7 +4921,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124800314</v>
+        <v>124800320</v>
       </c>
       <c r="B42" t="n">
         <v>78810</v>
@@ -4965,10 +4965,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440785</v>
+        <v>440720</v>
       </c>
       <c r="R42" t="n">
-        <v>7001501</v>
+        <v>7001206</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4995,12 +4995,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5027,10 +5027,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124738082</v>
+        <v>124800336</v>
       </c>
       <c r="B43" t="n">
-        <v>88359</v>
+        <v>91026</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5043,34 +5043,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440684</v>
+        <v>440616</v>
       </c>
       <c r="R43" t="n">
-        <v>7001254</v>
+        <v>7001215</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5097,12 +5101,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5129,10 +5133,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124740817</v>
+        <v>124800306</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5145,34 +5149,38 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440684</v>
+        <v>440872</v>
       </c>
       <c r="R44" t="n">
-        <v>7001254</v>
+        <v>7001384</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5199,12 +5207,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5231,10 +5239,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124800310</v>
+        <v>124800333</v>
       </c>
       <c r="B45" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5247,21 +5255,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5275,10 +5283,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440799</v>
+        <v>440628</v>
       </c>
       <c r="R45" t="n">
-        <v>7001243</v>
+        <v>7001081</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5337,10 +5345,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124800318</v>
+        <v>124738082</v>
       </c>
       <c r="B46" t="n">
-        <v>96354</v>
+        <v>88359</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5353,38 +5361,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>510</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440721</v>
+        <v>440684</v>
       </c>
       <c r="R46" t="n">
-        <v>7001216</v>
+        <v>7001254</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5411,12 +5415,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5443,10 +5447,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124800322</v>
+        <v>124800300</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5459,21 +5463,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5487,10 +5491,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440696</v>
+        <v>440915</v>
       </c>
       <c r="R47" t="n">
-        <v>7001259</v>
+        <v>7001296</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5549,10 +5553,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124800302</v>
+        <v>124800298</v>
       </c>
       <c r="B48" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5565,21 +5569,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5593,10 +5597,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440910</v>
+        <v>440916</v>
       </c>
       <c r="R48" t="n">
-        <v>7001371</v>
+        <v>7001320</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5655,7 +5659,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124800298</v>
+        <v>124740817</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -5688,21 +5692,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440916</v>
+        <v>440684</v>
       </c>
       <c r="R49" t="n">
-        <v>7001320</v>
+        <v>7001254</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800308</v>
+        <v>124800305</v>
       </c>
       <c r="B9" t="n">
-        <v>88359</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,21 +1439,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440850</v>
+        <v>440874</v>
       </c>
       <c r="R9" t="n">
-        <v>7001393</v>
+        <v>7001281</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800329</v>
+        <v>124800308</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,21 +1545,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440658</v>
+        <v>440850</v>
       </c>
       <c r="R10" t="n">
-        <v>7001354</v>
+        <v>7001393</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,7 +1635,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800330</v>
+        <v>124800329</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440646</v>
+        <v>440658</v>
       </c>
       <c r="R11" t="n">
-        <v>7001158</v>
+        <v>7001354</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1847,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800313</v>
+        <v>124800330</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440791</v>
+        <v>440646</v>
       </c>
       <c r="R13" t="n">
-        <v>7001239</v>
+        <v>7001158</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800305</v>
+        <v>124800313</v>
       </c>
       <c r="B14" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1969,21 +1969,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440874</v>
+        <v>440791</v>
       </c>
       <c r="R14" t="n">
-        <v>7001281</v>
+        <v>7001239</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800315</v>
+        <v>124800297</v>
       </c>
       <c r="B17" t="n">
-        <v>78889</v>
+        <v>91026</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,21 +2287,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440782</v>
+        <v>440921</v>
       </c>
       <c r="R17" t="n">
-        <v>7001494</v>
+        <v>7001295</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800297</v>
+        <v>124800315</v>
       </c>
       <c r="B18" t="n">
-        <v>91026</v>
+        <v>78889</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440921</v>
+        <v>440782</v>
       </c>
       <c r="R18" t="n">
-        <v>7001295</v>
+        <v>7001494</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800321</v>
+        <v>124801009</v>
       </c>
       <c r="B31" t="n">
-        <v>91008</v>
+        <v>94769</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3763,25 +3763,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>2411</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Nordlig källmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Philonotis tomentella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Molendo</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440709</v>
+        <v>440900</v>
       </c>
       <c r="R31" t="n">
-        <v>7001238</v>
+        <v>7001371</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124800324</v>
+        <v>124800321</v>
       </c>
       <c r="B33" t="n">
-        <v>91361</v>
+        <v>91008</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3975,25 +3975,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2062</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4001,19 +4001,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440680</v>
+        <v>440709</v>
       </c>
       <c r="R33" t="n">
-        <v>7001258</v>
+        <v>7001238</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4054,7 +4051,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4073,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124801009</v>
+        <v>124800324</v>
       </c>
       <c r="B34" t="n">
-        <v>94769</v>
+        <v>91361</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4085,25 +4081,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2411</v>
+        <v>2062</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nordlig källmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Philonotis tomentella</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Molendo</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4111,16 +4107,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440900</v>
+        <v>440680</v>
       </c>
       <c r="R34" t="n">
-        <v>7001371</v>
+        <v>7001258</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4161,6 +4160,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5239,10 +5239,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124800333</v>
+        <v>124738082</v>
       </c>
       <c r="B45" t="n">
-        <v>82597</v>
+        <v>88359</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5255,38 +5255,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440628</v>
+        <v>440684</v>
       </c>
       <c r="R45" t="n">
-        <v>7001081</v>
+        <v>7001254</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5313,12 +5309,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5345,10 +5341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124738082</v>
+        <v>124800333</v>
       </c>
       <c r="B46" t="n">
-        <v>88359</v>
+        <v>82597</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5361,34 +5357,38 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440684</v>
+        <v>440628</v>
       </c>
       <c r="R46" t="n">
-        <v>7001254</v>
+        <v>7001081</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5415,12 +5415,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800322</v>
+        <v>124800295</v>
       </c>
       <c r="B3" t="n">
         <v>91012</v>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440696</v>
+        <v>440940</v>
       </c>
       <c r="R3" t="n">
-        <v>7001259</v>
+        <v>7001369</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800325</v>
+        <v>124800332</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>74906</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440674</v>
+        <v>440630</v>
       </c>
       <c r="R4" t="n">
-        <v>7001385</v>
+        <v>7001086</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800307</v>
+        <v>124800323</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440872</v>
+        <v>440681</v>
       </c>
       <c r="R5" t="n">
-        <v>7001280</v>
+        <v>7001285</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800303</v>
+        <v>124800306</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,21 +1121,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440909</v>
+        <v>440872</v>
       </c>
       <c r="R6" t="n">
-        <v>7001374</v>
+        <v>7001384</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800319</v>
+        <v>124800331</v>
       </c>
       <c r="B7" t="n">
-        <v>97185</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,25 +1223,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220686</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440720</v>
+        <v>440637</v>
       </c>
       <c r="R7" t="n">
-        <v>7001201</v>
+        <v>7001171</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800338</v>
+        <v>124800335</v>
       </c>
       <c r="B8" t="n">
-        <v>96776</v>
+        <v>78889</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,25 +1329,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2389</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440604</v>
+        <v>440621</v>
       </c>
       <c r="R8" t="n">
-        <v>7001240</v>
+        <v>7001181</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800305</v>
+        <v>124740889</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,38 +1439,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440874</v>
+        <v>440684</v>
       </c>
       <c r="R9" t="n">
-        <v>7001281</v>
+        <v>7001254</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,12 +1493,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800308</v>
+        <v>124800338</v>
       </c>
       <c r="B10" t="n">
-        <v>88359</v>
+        <v>96776</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,25 +1537,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>2389</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1573,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440850</v>
+        <v>440604</v>
       </c>
       <c r="R10" t="n">
-        <v>7001393</v>
+        <v>7001240</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,7 +1631,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800329</v>
+        <v>124740817</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1668,21 +1664,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440658</v>
+        <v>440684</v>
       </c>
       <c r="R11" t="n">
-        <v>7001354</v>
+        <v>7001254</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,12 +1701,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,10 +1733,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800326</v>
+        <v>124800309</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,21 +1749,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1785,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440672</v>
+        <v>440821</v>
       </c>
       <c r="R12" t="n">
-        <v>7001335</v>
+        <v>7001261</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,10 +1839,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800330</v>
+        <v>124800296</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,21 +1855,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1891,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440646</v>
+        <v>440939</v>
       </c>
       <c r="R13" t="n">
-        <v>7001158</v>
+        <v>7001309</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800313</v>
+        <v>124801009</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>94769</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,25 +1957,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2411</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig källmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Philonotis tomentella</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Molendo</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1997,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440791</v>
+        <v>440900</v>
       </c>
       <c r="R14" t="n">
-        <v>7001239</v>
+        <v>7001371</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800294</v>
+        <v>124800311</v>
       </c>
       <c r="B15" t="n">
-        <v>79851</v>
+        <v>77753</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2071,25 +2063,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2103,10 +2095,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441028</v>
+        <v>440798</v>
       </c>
       <c r="R15" t="n">
-        <v>7001364</v>
+        <v>7001239</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,10 +2157,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800318</v>
+        <v>124800310</v>
       </c>
       <c r="B16" t="n">
-        <v>96354</v>
+        <v>74901</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,21 +2173,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2209,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440721</v>
+        <v>440799</v>
       </c>
       <c r="R16" t="n">
-        <v>7001216</v>
+        <v>7001243</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,10 +2263,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800297</v>
+        <v>124800325</v>
       </c>
       <c r="B17" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,21 +2279,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2315,10 +2307,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440921</v>
+        <v>440674</v>
       </c>
       <c r="R17" t="n">
-        <v>7001295</v>
+        <v>7001385</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,10 +2369,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800315</v>
+        <v>124800314</v>
       </c>
       <c r="B18" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,21 +2385,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2421,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440782</v>
+        <v>440785</v>
       </c>
       <c r="R18" t="n">
-        <v>7001494</v>
+        <v>7001501</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2451,12 +2443,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2483,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800323</v>
+        <v>124800333</v>
       </c>
       <c r="B19" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2499,21 +2491,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2527,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440681</v>
+        <v>440628</v>
       </c>
       <c r="R19" t="n">
-        <v>7001285</v>
+        <v>7001081</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800331</v>
+        <v>124800293</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2605,21 +2597,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2633,10 +2625,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440637</v>
+        <v>441111</v>
       </c>
       <c r="R20" t="n">
-        <v>7001171</v>
+        <v>7001333</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800340</v>
+        <v>124800302</v>
       </c>
       <c r="B21" t="n">
-        <v>74901</v>
+        <v>78889</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2711,21 +2703,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2739,10 +2731,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440590</v>
+        <v>440910</v>
       </c>
       <c r="R21" t="n">
-        <v>7001362</v>
+        <v>7001371</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2801,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800299</v>
+        <v>124800308</v>
       </c>
       <c r="B22" t="n">
-        <v>78889</v>
+        <v>88359</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2817,21 +2809,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>864</v>
+        <v>510</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2845,10 +2837,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440915</v>
+        <v>440850</v>
       </c>
       <c r="R22" t="n">
-        <v>7001377</v>
+        <v>7001393</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,10 +2899,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800304</v>
+        <v>124800316</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,21 +2915,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2951,10 +2943,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440902</v>
+        <v>440773</v>
       </c>
       <c r="R23" t="n">
-        <v>7001332</v>
+        <v>7001489</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3013,10 +3005,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800302</v>
+        <v>124800324</v>
       </c>
       <c r="B24" t="n">
-        <v>78889</v>
+        <v>91361</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3025,25 +3017,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>864</v>
+        <v>2062</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3051,16 +3043,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440910</v>
+        <v>440680</v>
       </c>
       <c r="R24" t="n">
-        <v>7001371</v>
+        <v>7001258</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3101,6 +3096,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3119,10 +3115,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800332</v>
+        <v>124800334</v>
       </c>
       <c r="B25" t="n">
-        <v>74906</v>
+        <v>77753</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3135,21 +3131,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1467</v>
+        <v>314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3163,10 +3159,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440630</v>
+        <v>440624</v>
       </c>
       <c r="R25" t="n">
-        <v>7001086</v>
+        <v>7001080</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3225,10 +3221,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124740889</v>
+        <v>124800305</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3241,34 +3237,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440684</v>
+        <v>440874</v>
       </c>
       <c r="R26" t="n">
-        <v>7001254</v>
+        <v>7001281</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3295,12 +3295,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3327,10 +3327,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800334</v>
+        <v>124800303</v>
       </c>
       <c r="B27" t="n">
-        <v>77753</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440624</v>
+        <v>440909</v>
       </c>
       <c r="R27" t="n">
-        <v>7001080</v>
+        <v>7001374</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3433,10 +3433,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800328</v>
+        <v>124800300</v>
       </c>
       <c r="B28" t="n">
-        <v>95335</v>
+        <v>91030</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3445,25 +3445,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440661</v>
+        <v>440915</v>
       </c>
       <c r="R28" t="n">
-        <v>7001244</v>
+        <v>7001296</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3539,10 +3539,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800316</v>
+        <v>124800304</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3555,21 +3555,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440773</v>
+        <v>440902</v>
       </c>
       <c r="R29" t="n">
-        <v>7001489</v>
+        <v>7001332</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3645,10 +3645,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800311</v>
+        <v>124800319</v>
       </c>
       <c r="B30" t="n">
-        <v>77753</v>
+        <v>97185</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3657,25 +3657,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>314</v>
+        <v>220686</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440798</v>
+        <v>440720</v>
       </c>
       <c r="R30" t="n">
-        <v>7001239</v>
+        <v>7001201</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124801009</v>
+        <v>124800298</v>
       </c>
       <c r="B31" t="n">
-        <v>94769</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3763,25 +3763,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2411</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nordlig källmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Philonotis tomentella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Molendo</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440900</v>
+        <v>440916</v>
       </c>
       <c r="R31" t="n">
-        <v>7001371</v>
+        <v>7001320</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,10 +3857,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124800310</v>
+        <v>124800322</v>
       </c>
       <c r="B32" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3873,21 +3873,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440799</v>
+        <v>440696</v>
       </c>
       <c r="R32" t="n">
-        <v>7001243</v>
+        <v>7001259</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124800321</v>
+        <v>124800315</v>
       </c>
       <c r="B33" t="n">
-        <v>91008</v>
+        <v>78889</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3979,21 +3979,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440709</v>
+        <v>440782</v>
       </c>
       <c r="R33" t="n">
-        <v>7001238</v>
+        <v>7001494</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4069,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124800324</v>
+        <v>124800307</v>
       </c>
       <c r="B34" t="n">
-        <v>91361</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4081,25 +4081,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4107,19 +4107,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440680</v>
+        <v>440872</v>
       </c>
       <c r="R34" t="n">
-        <v>7001258</v>
+        <v>7001280</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4160,7 +4157,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4179,10 +4175,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124800293</v>
+        <v>124800318</v>
       </c>
       <c r="B35" t="n">
-        <v>57529</v>
+        <v>96354</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4195,21 +4191,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4223,10 +4219,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>441111</v>
+        <v>440721</v>
       </c>
       <c r="R35" t="n">
-        <v>7001333</v>
+        <v>7001216</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4285,10 +4281,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124800295</v>
+        <v>124800329</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4301,21 +4297,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4329,10 +4325,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440940</v>
+        <v>440658</v>
       </c>
       <c r="R36" t="n">
-        <v>7001369</v>
+        <v>7001354</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4391,10 +4387,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124800335</v>
+        <v>124800313</v>
       </c>
       <c r="B37" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4407,21 +4403,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4435,10 +4431,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440621</v>
+        <v>440791</v>
       </c>
       <c r="R37" t="n">
-        <v>7001181</v>
+        <v>7001239</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4497,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124800309</v>
+        <v>124800321</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4513,21 +4509,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4541,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440821</v>
+        <v>440709</v>
       </c>
       <c r="R38" t="n">
-        <v>7001261</v>
+        <v>7001238</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4709,10 +4705,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124800296</v>
+        <v>124738082</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4725,38 +4721,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440939</v>
+        <v>440684</v>
       </c>
       <c r="R40" t="n">
-        <v>7001309</v>
+        <v>7001254</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4783,12 +4775,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4815,10 +4807,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124800314</v>
+        <v>124800340</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4831,21 +4823,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4859,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440785</v>
+        <v>440590</v>
       </c>
       <c r="R41" t="n">
-        <v>7001501</v>
+        <v>7001362</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4889,12 +4881,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4921,10 +4913,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124800320</v>
+        <v>124800297</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4937,21 +4929,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4965,10 +4957,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440720</v>
+        <v>440921</v>
       </c>
       <c r="R42" t="n">
-        <v>7001206</v>
+        <v>7001295</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5027,10 +5019,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124800336</v>
+        <v>124800328</v>
       </c>
       <c r="B43" t="n">
-        <v>91026</v>
+        <v>95335</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5039,25 +5031,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>2809</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5071,10 +5063,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440616</v>
+        <v>440661</v>
       </c>
       <c r="R43" t="n">
-        <v>7001215</v>
+        <v>7001244</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5133,10 +5125,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124800306</v>
+        <v>124800294</v>
       </c>
       <c r="B44" t="n">
-        <v>88359</v>
+        <v>79851</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5145,25 +5137,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>510</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5177,10 +5169,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440872</v>
+        <v>441028</v>
       </c>
       <c r="R44" t="n">
-        <v>7001384</v>
+        <v>7001364</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5239,10 +5231,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124738082</v>
+        <v>124800326</v>
       </c>
       <c r="B45" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5255,34 +5247,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440684</v>
+        <v>440672</v>
       </c>
       <c r="R45" t="n">
-        <v>7001254</v>
+        <v>7001335</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5309,12 +5305,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5341,10 +5337,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124800333</v>
+        <v>124800330</v>
       </c>
       <c r="B46" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5357,21 +5353,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5385,10 +5381,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440628</v>
+        <v>440646</v>
       </c>
       <c r="R46" t="n">
-        <v>7001081</v>
+        <v>7001158</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5447,10 +5443,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124800300</v>
+        <v>124800320</v>
       </c>
       <c r="B47" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5463,21 +5459,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5491,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440915</v>
+        <v>440720</v>
       </c>
       <c r="R47" t="n">
-        <v>7001296</v>
+        <v>7001206</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5553,10 +5549,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124800298</v>
+        <v>124800336</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5569,21 +5565,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5597,10 +5593,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440916</v>
+        <v>440616</v>
       </c>
       <c r="R48" t="n">
-        <v>7001320</v>
+        <v>7001215</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5659,10 +5655,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124740817</v>
+        <v>124800299</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5675,34 +5671,38 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440684</v>
+        <v>440915</v>
       </c>
       <c r="R49" t="n">
-        <v>7001254</v>
+        <v>7001377</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -4705,10 +4705,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124738082</v>
+        <v>124800340</v>
       </c>
       <c r="B40" t="n">
-        <v>88359</v>
+        <v>74901</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4721,34 +4721,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440684</v>
+        <v>440590</v>
       </c>
       <c r="R40" t="n">
-        <v>7001254</v>
+        <v>7001362</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4775,12 +4779,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4807,10 +4811,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124800340</v>
+        <v>124738082</v>
       </c>
       <c r="B41" t="n">
-        <v>74901</v>
+        <v>88359</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4823,38 +4827,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440590</v>
+        <v>440684</v>
       </c>
       <c r="R41" t="n">
-        <v>7001362</v>
+        <v>7001254</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4881,12 +4881,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800295</v>
+        <v>124800293</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440940</v>
+        <v>441111</v>
       </c>
       <c r="R3" t="n">
-        <v>7001369</v>
+        <v>7001333</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800332</v>
+        <v>124738082</v>
       </c>
       <c r="B4" t="n">
-        <v>74906</v>
+        <v>88359</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +909,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1467</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440630</v>
+        <v>440684</v>
       </c>
       <c r="R4" t="n">
-        <v>7001086</v>
+        <v>7001254</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,12 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +995,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800323</v>
+        <v>124800310</v>
       </c>
       <c r="B5" t="n">
         <v>74901</v>
@@ -1043,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440681</v>
+        <v>440799</v>
       </c>
       <c r="R5" t="n">
-        <v>7001285</v>
+        <v>7001243</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800306</v>
+        <v>124800295</v>
       </c>
       <c r="B6" t="n">
-        <v>88359</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1149,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440872</v>
+        <v>440940</v>
       </c>
       <c r="R6" t="n">
-        <v>7001384</v>
+        <v>7001369</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1207,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800331</v>
+        <v>124800298</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1255,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440637</v>
+        <v>440916</v>
       </c>
       <c r="R7" t="n">
-        <v>7001171</v>
+        <v>7001320</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800335</v>
+        <v>124800330</v>
       </c>
       <c r="B8" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1329,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1361,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440621</v>
+        <v>440646</v>
       </c>
       <c r="R8" t="n">
-        <v>7001181</v>
+        <v>7001158</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124740889</v>
+        <v>124800327</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,34 +1435,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440684</v>
+        <v>440672</v>
       </c>
       <c r="R9" t="n">
-        <v>7001254</v>
+        <v>7001361</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800338</v>
+        <v>124800296</v>
       </c>
       <c r="B10" t="n">
-        <v>96776</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,25 +1537,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2389</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440604</v>
+        <v>440939</v>
       </c>
       <c r="R10" t="n">
-        <v>7001240</v>
+        <v>7001309</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124740817</v>
+        <v>124800311</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>77753</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,34 +1647,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440684</v>
+        <v>440798</v>
       </c>
       <c r="R11" t="n">
-        <v>7001254</v>
+        <v>7001239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,12 +1705,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800309</v>
+        <v>124801009</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>94769</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1745,25 +1749,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>2411</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordlig källmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Philonotis tomentella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Molendo</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1777,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440821</v>
+        <v>440900</v>
       </c>
       <c r="R12" t="n">
-        <v>7001261</v>
+        <v>7001371</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800296</v>
+        <v>124800324</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>91361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1851,25 +1855,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1877,16 +1881,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440939</v>
+        <v>440680</v>
       </c>
       <c r="R13" t="n">
-        <v>7001309</v>
+        <v>7001258</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,6 +1934,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1945,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124801009</v>
+        <v>124800338</v>
       </c>
       <c r="B14" t="n">
-        <v>94769</v>
+        <v>96776</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1961,21 +1969,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2411</v>
+        <v>2389</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordlig källmossa</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Philonotis tomentella</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Molendo</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1989,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440900</v>
+        <v>440604</v>
       </c>
       <c r="R14" t="n">
-        <v>7001371</v>
+        <v>7001240</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,10 +2059,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800311</v>
+        <v>124800315</v>
       </c>
       <c r="B15" t="n">
-        <v>77753</v>
+        <v>78889</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,21 +2075,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>314</v>
+        <v>864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2095,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440798</v>
+        <v>440782</v>
       </c>
       <c r="R15" t="n">
-        <v>7001239</v>
+        <v>7001494</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,10 +2165,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800310</v>
+        <v>124800329</v>
       </c>
       <c r="B16" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2173,21 +2181,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2201,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440799</v>
+        <v>440658</v>
       </c>
       <c r="R16" t="n">
-        <v>7001243</v>
+        <v>7001354</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2271,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800325</v>
+        <v>124800303</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2307,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440674</v>
+        <v>440909</v>
       </c>
       <c r="R17" t="n">
-        <v>7001385</v>
+        <v>7001374</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800314</v>
+        <v>124740817</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2402,21 +2410,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440785</v>
+        <v>440684</v>
       </c>
       <c r="R18" t="n">
-        <v>7001501</v>
+        <v>7001254</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2475,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800333</v>
+        <v>124740889</v>
       </c>
       <c r="B19" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2491,38 +2495,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440628</v>
+        <v>440684</v>
       </c>
       <c r="R19" t="n">
-        <v>7001081</v>
+        <v>7001254</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800293</v>
+        <v>124800332</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>74906</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,21 +2597,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441111</v>
+        <v>440630</v>
       </c>
       <c r="R20" t="n">
-        <v>7001333</v>
+        <v>7001086</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800302</v>
+        <v>124800314</v>
       </c>
       <c r="B21" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,21 +2703,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440910</v>
+        <v>440785</v>
       </c>
       <c r="R21" t="n">
-        <v>7001371</v>
+        <v>7001501</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2761,12 +2761,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2793,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800308</v>
+        <v>124800333</v>
       </c>
       <c r="B22" t="n">
-        <v>88359</v>
+        <v>82597</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2809,21 +2809,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440850</v>
+        <v>440628</v>
       </c>
       <c r="R22" t="n">
-        <v>7001393</v>
+        <v>7001081</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800316</v>
+        <v>124800306</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2915,21 +2915,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440773</v>
+        <v>440872</v>
       </c>
       <c r="R23" t="n">
-        <v>7001489</v>
+        <v>7001384</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,10 +3005,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800324</v>
+        <v>124800331</v>
       </c>
       <c r="B24" t="n">
-        <v>91361</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3017,25 +3017,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3043,19 +3043,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440680</v>
+        <v>440637</v>
       </c>
       <c r="R24" t="n">
-        <v>7001258</v>
+        <v>7001171</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3096,7 +3093,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3115,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800334</v>
+        <v>124800328</v>
       </c>
       <c r="B25" t="n">
-        <v>77753</v>
+        <v>95335</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3127,25 +3123,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>314</v>
+        <v>2809</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3159,10 +3155,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440624</v>
+        <v>440661</v>
       </c>
       <c r="R25" t="n">
-        <v>7001080</v>
+        <v>7001244</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3221,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800305</v>
+        <v>124800334</v>
       </c>
       <c r="B26" t="n">
-        <v>91299</v>
+        <v>77753</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3237,21 +3233,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3265,10 +3261,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440874</v>
+        <v>440624</v>
       </c>
       <c r="R26" t="n">
-        <v>7001281</v>
+        <v>7001080</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3327,10 +3323,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800303</v>
+        <v>124800294</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>79851</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3339,25 +3335,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3371,10 +3367,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440909</v>
+        <v>441028</v>
       </c>
       <c r="R27" t="n">
-        <v>7001374</v>
+        <v>7001364</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3433,10 +3429,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800300</v>
+        <v>124800335</v>
       </c>
       <c r="B28" t="n">
-        <v>91030</v>
+        <v>78889</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3449,21 +3445,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3477,10 +3473,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440915</v>
+        <v>440621</v>
       </c>
       <c r="R28" t="n">
-        <v>7001296</v>
+        <v>7001181</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3539,10 +3535,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800304</v>
+        <v>124800326</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3555,21 +3551,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3583,10 +3579,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440902</v>
+        <v>440672</v>
       </c>
       <c r="R29" t="n">
-        <v>7001332</v>
+        <v>7001335</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3645,10 +3641,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800319</v>
+        <v>124800313</v>
       </c>
       <c r="B30" t="n">
-        <v>97185</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3657,25 +3653,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220686</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3689,10 +3685,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440720</v>
+        <v>440791</v>
       </c>
       <c r="R30" t="n">
-        <v>7001201</v>
+        <v>7001239</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3751,7 +3747,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800298</v>
+        <v>124800316</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3795,10 +3791,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440916</v>
+        <v>440773</v>
       </c>
       <c r="R31" t="n">
-        <v>7001320</v>
+        <v>7001489</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,7 +3853,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124800322</v>
+        <v>124800309</v>
       </c>
       <c r="B32" t="n">
         <v>91012</v>
@@ -3901,10 +3897,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440696</v>
+        <v>440821</v>
       </c>
       <c r="R32" t="n">
-        <v>7001259</v>
+        <v>7001261</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3963,10 +3959,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124800315</v>
+        <v>124800297</v>
       </c>
       <c r="B33" t="n">
-        <v>78889</v>
+        <v>91026</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3979,21 +3975,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4007,10 +4003,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440782</v>
+        <v>440921</v>
       </c>
       <c r="R33" t="n">
-        <v>7001494</v>
+        <v>7001295</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4175,10 +4171,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124800318</v>
+        <v>124800320</v>
       </c>
       <c r="B35" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4191,21 +4187,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4219,10 +4215,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440721</v>
+        <v>440720</v>
       </c>
       <c r="R35" t="n">
-        <v>7001216</v>
+        <v>7001206</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4281,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124800329</v>
+        <v>124800319</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>97185</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4293,25 +4289,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220686</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4325,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440658</v>
+        <v>440720</v>
       </c>
       <c r="R36" t="n">
-        <v>7001354</v>
+        <v>7001201</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4387,10 +4383,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124800313</v>
+        <v>124800308</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4403,21 +4399,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4431,10 +4427,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440791</v>
+        <v>440850</v>
       </c>
       <c r="R37" t="n">
-        <v>7001239</v>
+        <v>7001393</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4493,10 +4489,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124800321</v>
+        <v>124800336</v>
       </c>
       <c r="B38" t="n">
-        <v>91008</v>
+        <v>91026</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4509,21 +4505,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4537,10 +4533,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440709</v>
+        <v>440616</v>
       </c>
       <c r="R38" t="n">
-        <v>7001238</v>
+        <v>7001215</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4599,10 +4595,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124800327</v>
+        <v>124800299</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4615,21 +4611,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4643,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440672</v>
+        <v>440915</v>
       </c>
       <c r="R39" t="n">
-        <v>7001361</v>
+        <v>7001377</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4705,7 +4701,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124800340</v>
+        <v>124800323</v>
       </c>
       <c r="B40" t="n">
         <v>74901</v>
@@ -4749,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440590</v>
+        <v>440681</v>
       </c>
       <c r="R40" t="n">
-        <v>7001362</v>
+        <v>7001285</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,10 +4807,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124738082</v>
+        <v>124800318</v>
       </c>
       <c r="B41" t="n">
-        <v>88359</v>
+        <v>96354</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4827,34 +4823,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>510</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440684</v>
+        <v>440721</v>
       </c>
       <c r="R41" t="n">
-        <v>7001254</v>
+        <v>7001216</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4881,12 +4881,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4913,10 +4913,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124800297</v>
+        <v>124800340</v>
       </c>
       <c r="B42" t="n">
-        <v>91026</v>
+        <v>74901</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4929,21 +4929,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440921</v>
+        <v>440590</v>
       </c>
       <c r="R42" t="n">
-        <v>7001295</v>
+        <v>7001362</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124800328</v>
+        <v>124800322</v>
       </c>
       <c r="B43" t="n">
-        <v>95335</v>
+        <v>91012</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5031,25 +5031,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5063,10 +5063,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440661</v>
+        <v>440696</v>
       </c>
       <c r="R43" t="n">
-        <v>7001244</v>
+        <v>7001259</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5125,10 +5125,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124800294</v>
+        <v>124800325</v>
       </c>
       <c r="B44" t="n">
-        <v>79851</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5137,25 +5137,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5169,10 +5169,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441028</v>
+        <v>440674</v>
       </c>
       <c r="R44" t="n">
-        <v>7001364</v>
+        <v>7001385</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5231,10 +5231,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124800326</v>
+        <v>124800300</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5247,21 +5247,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440672</v>
+        <v>440915</v>
       </c>
       <c r="R45" t="n">
-        <v>7001335</v>
+        <v>7001296</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124800330</v>
+        <v>124800304</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5353,21 +5353,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440646</v>
+        <v>440902</v>
       </c>
       <c r="R46" t="n">
-        <v>7001158</v>
+        <v>7001332</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124800320</v>
+        <v>124800305</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440720</v>
+        <v>440874</v>
       </c>
       <c r="R47" t="n">
-        <v>7001206</v>
+        <v>7001281</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124800336</v>
+        <v>124800302</v>
       </c>
       <c r="B48" t="n">
-        <v>91026</v>
+        <v>78889</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5565,21 +5565,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440616</v>
+        <v>440910</v>
       </c>
       <c r="R48" t="n">
-        <v>7001215</v>
+        <v>7001371</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5655,10 +5655,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124800299</v>
+        <v>124800321</v>
       </c>
       <c r="B49" t="n">
-        <v>78889</v>
+        <v>91008</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440915</v>
+        <v>440709</v>
       </c>
       <c r="R49" t="n">
-        <v>7001377</v>
+        <v>7001238</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800293</v>
+        <v>124738082</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>88359</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,38 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441111</v>
+        <v>440684</v>
       </c>
       <c r="R3" t="n">
-        <v>7001333</v>
+        <v>7001254</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124738082</v>
+        <v>124800318</v>
       </c>
       <c r="B4" t="n">
-        <v>88359</v>
+        <v>96354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,34 +905,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440684</v>
+        <v>440721</v>
       </c>
       <c r="R4" t="n">
-        <v>7001254</v>
+        <v>7001216</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,12 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800310</v>
+        <v>124800297</v>
       </c>
       <c r="B5" t="n">
-        <v>74901</v>
+        <v>91026</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440799</v>
+        <v>440921</v>
       </c>
       <c r="R5" t="n">
-        <v>7001243</v>
+        <v>7001295</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800295</v>
+        <v>124800313</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440940</v>
+        <v>440791</v>
       </c>
       <c r="R6" t="n">
-        <v>7001369</v>
+        <v>7001239</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800298</v>
+        <v>124800300</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,21 +1223,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440916</v>
+        <v>440915</v>
       </c>
       <c r="R7" t="n">
-        <v>7001320</v>
+        <v>7001296</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800330</v>
+        <v>124800294</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79851</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,25 +1325,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440646</v>
+        <v>441028</v>
       </c>
       <c r="R8" t="n">
-        <v>7001158</v>
+        <v>7001364</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800327</v>
+        <v>124800299</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440672</v>
+        <v>440915</v>
       </c>
       <c r="R9" t="n">
-        <v>7001361</v>
+        <v>7001377</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800296</v>
+        <v>124740817</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,38 +1541,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440939</v>
+        <v>440684</v>
       </c>
       <c r="R10" t="n">
-        <v>7001309</v>
+        <v>7001254</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,12 +1595,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800311</v>
+        <v>124800322</v>
       </c>
       <c r="B11" t="n">
-        <v>77753</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,21 +1643,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>314</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1675,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440798</v>
+        <v>440696</v>
       </c>
       <c r="R11" t="n">
-        <v>7001239</v>
+        <v>7001259</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,10 +1733,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124801009</v>
+        <v>124800306</v>
       </c>
       <c r="B12" t="n">
-        <v>94769</v>
+        <v>88359</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1749,25 +1745,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2411</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordlig källmossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Philonotis tomentella</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Molendo</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1781,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440900</v>
+        <v>440872</v>
       </c>
       <c r="R12" t="n">
-        <v>7001371</v>
+        <v>7001384</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1839,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800324</v>
+        <v>124800316</v>
       </c>
       <c r="B13" t="n">
-        <v>91361</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,25 +1851,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1881,19 +1877,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440680</v>
+        <v>440773</v>
       </c>
       <c r="R13" t="n">
-        <v>7001258</v>
+        <v>7001489</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,7 +1927,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1953,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800338</v>
+        <v>124800302</v>
       </c>
       <c r="B14" t="n">
-        <v>96776</v>
+        <v>78889</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,25 +1957,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2389</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1997,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440604</v>
+        <v>440910</v>
       </c>
       <c r="R14" t="n">
-        <v>7001240</v>
+        <v>7001371</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800315</v>
+        <v>124800334</v>
       </c>
       <c r="B15" t="n">
-        <v>78889</v>
+        <v>77753</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2075,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>864</v>
+        <v>314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2103,10 +2095,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440782</v>
+        <v>440624</v>
       </c>
       <c r="R15" t="n">
-        <v>7001494</v>
+        <v>7001080</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,10 +2157,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800329</v>
+        <v>124800308</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,21 +2173,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2209,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440658</v>
+        <v>440850</v>
       </c>
       <c r="R16" t="n">
-        <v>7001354</v>
+        <v>7001393</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,7 +2263,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800303</v>
+        <v>124800327</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2315,10 +2307,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440909</v>
+        <v>440672</v>
       </c>
       <c r="R17" t="n">
-        <v>7001374</v>
+        <v>7001361</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,7 +2369,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124740817</v>
+        <v>124800314</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2410,17 +2402,21 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440684</v>
+        <v>440785</v>
       </c>
       <c r="R18" t="n">
-        <v>7001254</v>
+        <v>7001501</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124740889</v>
+        <v>124800319</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>97185</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2491,38 +2487,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>220686</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440684</v>
+        <v>440720</v>
       </c>
       <c r="R19" t="n">
-        <v>7001254</v>
+        <v>7001201</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800332</v>
+        <v>124800315</v>
       </c>
       <c r="B20" t="n">
-        <v>74906</v>
+        <v>78889</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,21 +2597,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440630</v>
+        <v>440782</v>
       </c>
       <c r="R20" t="n">
-        <v>7001086</v>
+        <v>7001494</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800314</v>
+        <v>124740889</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,38 +2703,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440785</v>
+        <v>440684</v>
       </c>
       <c r="R21" t="n">
-        <v>7001501</v>
+        <v>7001254</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,10 +2789,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800333</v>
+        <v>124800296</v>
       </c>
       <c r="B22" t="n">
-        <v>82597</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2809,21 +2805,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2837,10 +2833,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440628</v>
+        <v>440939</v>
       </c>
       <c r="R22" t="n">
-        <v>7001081</v>
+        <v>7001309</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2899,10 +2895,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800306</v>
+        <v>124800304</v>
       </c>
       <c r="B23" t="n">
-        <v>88359</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2915,21 +2911,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2943,10 +2939,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440872</v>
+        <v>440902</v>
       </c>
       <c r="R23" t="n">
-        <v>7001384</v>
+        <v>7001332</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,7 +3001,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800331</v>
+        <v>124800298</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3049,10 +3045,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440637</v>
+        <v>440916</v>
       </c>
       <c r="R24" t="n">
-        <v>7001171</v>
+        <v>7001320</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,10 +3107,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800328</v>
+        <v>124800331</v>
       </c>
       <c r="B25" t="n">
-        <v>95335</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3123,25 +3119,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3155,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440661</v>
+        <v>440637</v>
       </c>
       <c r="R25" t="n">
-        <v>7001244</v>
+        <v>7001171</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3217,10 +3213,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800334</v>
+        <v>124800338</v>
       </c>
       <c r="B26" t="n">
-        <v>77753</v>
+        <v>96776</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3229,25 +3225,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>314</v>
+        <v>2389</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3261,10 +3257,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440624</v>
+        <v>440604</v>
       </c>
       <c r="R26" t="n">
-        <v>7001080</v>
+        <v>7001240</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,10 +3319,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800294</v>
+        <v>124800335</v>
       </c>
       <c r="B27" t="n">
-        <v>79851</v>
+        <v>78889</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3335,25 +3331,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229497</v>
+        <v>864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3367,10 +3363,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441028</v>
+        <v>440621</v>
       </c>
       <c r="R27" t="n">
-        <v>7001364</v>
+        <v>7001181</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800335</v>
+        <v>124800293</v>
       </c>
       <c r="B28" t="n">
-        <v>78889</v>
+        <v>57529</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3445,21 +3441,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3473,10 +3469,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440621</v>
+        <v>441111</v>
       </c>
       <c r="R28" t="n">
-        <v>7001181</v>
+        <v>7001333</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3535,10 +3531,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800326</v>
+        <v>124800305</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3551,21 +3547,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3579,10 +3575,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440672</v>
+        <v>440874</v>
       </c>
       <c r="R29" t="n">
-        <v>7001335</v>
+        <v>7001281</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3641,7 +3637,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800313</v>
+        <v>124800329</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3685,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440791</v>
+        <v>440658</v>
       </c>
       <c r="R30" t="n">
-        <v>7001239</v>
+        <v>7001354</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3747,7 +3743,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800316</v>
+        <v>124800326</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3791,10 +3787,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440773</v>
+        <v>440672</v>
       </c>
       <c r="R31" t="n">
-        <v>7001489</v>
+        <v>7001335</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,10 +3849,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124800309</v>
+        <v>124800324</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>91361</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3865,25 +3861,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3891,16 +3887,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440821</v>
+        <v>440680</v>
       </c>
       <c r="R32" t="n">
-        <v>7001261</v>
+        <v>7001258</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3941,6 +3940,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3959,10 +3959,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124800297</v>
+        <v>124801009</v>
       </c>
       <c r="B33" t="n">
-        <v>91026</v>
+        <v>94769</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3971,25 +3971,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>2411</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Nordlig källmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Philonotis tomentella</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Molendo</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440921</v>
+        <v>440900</v>
       </c>
       <c r="R33" t="n">
-        <v>7001295</v>
+        <v>7001371</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124800307</v>
+        <v>124800321</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4081,21 +4081,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440872</v>
+        <v>440709</v>
       </c>
       <c r="R34" t="n">
-        <v>7001280</v>
+        <v>7001238</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4171,10 +4171,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124800320</v>
+        <v>124800307</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4215,10 +4215,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440720</v>
+        <v>440872</v>
       </c>
       <c r="R35" t="n">
-        <v>7001206</v>
+        <v>7001280</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4277,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124800319</v>
+        <v>124800323</v>
       </c>
       <c r="B36" t="n">
-        <v>97185</v>
+        <v>74901</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4289,25 +4289,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220686</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440720</v>
+        <v>440681</v>
       </c>
       <c r="R36" t="n">
-        <v>7001201</v>
+        <v>7001285</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,10 +4383,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124800308</v>
+        <v>124800330</v>
       </c>
       <c r="B37" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4399,21 +4399,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440850</v>
+        <v>440646</v>
       </c>
       <c r="R37" t="n">
-        <v>7001393</v>
+        <v>7001158</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4489,10 +4489,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124800336</v>
+        <v>124800332</v>
       </c>
       <c r="B38" t="n">
-        <v>91026</v>
+        <v>74906</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4505,21 +4505,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1204</v>
+        <v>1467</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440616</v>
+        <v>440630</v>
       </c>
       <c r="R38" t="n">
-        <v>7001215</v>
+        <v>7001086</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,10 +4595,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124800299</v>
+        <v>124800303</v>
       </c>
       <c r="B39" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4611,21 +4611,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440915</v>
+        <v>440909</v>
       </c>
       <c r="R39" t="n">
-        <v>7001377</v>
+        <v>7001374</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4701,7 +4701,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124800323</v>
+        <v>124800310</v>
       </c>
       <c r="B40" t="n">
         <v>74901</v>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440681</v>
+        <v>440799</v>
       </c>
       <c r="R40" t="n">
-        <v>7001285</v>
+        <v>7001243</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4807,10 +4807,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124800318</v>
+        <v>124800333</v>
       </c>
       <c r="B41" t="n">
-        <v>96354</v>
+        <v>82597</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440721</v>
+        <v>440628</v>
       </c>
       <c r="R41" t="n">
-        <v>7001216</v>
+        <v>7001081</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4913,10 +4913,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124800340</v>
+        <v>124800328</v>
       </c>
       <c r="B42" t="n">
-        <v>74901</v>
+        <v>95335</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4925,25 +4925,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440590</v>
+        <v>440661</v>
       </c>
       <c r="R42" t="n">
-        <v>7001362</v>
+        <v>7001244</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124800322</v>
+        <v>124800311</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>77753</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5035,21 +5035,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5063,10 +5063,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440696</v>
+        <v>440798</v>
       </c>
       <c r="R43" t="n">
-        <v>7001259</v>
+        <v>7001239</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5125,10 +5125,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124800325</v>
+        <v>124800336</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5141,21 +5141,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5169,10 +5169,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440674</v>
+        <v>440616</v>
       </c>
       <c r="R44" t="n">
-        <v>7001385</v>
+        <v>7001215</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5231,10 +5231,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124800300</v>
+        <v>124800295</v>
       </c>
       <c r="B45" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5247,21 +5247,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440915</v>
+        <v>440940</v>
       </c>
       <c r="R45" t="n">
-        <v>7001296</v>
+        <v>7001369</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124800304</v>
+        <v>124800320</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5353,21 +5353,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440902</v>
+        <v>440720</v>
       </c>
       <c r="R46" t="n">
-        <v>7001332</v>
+        <v>7001206</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124800305</v>
+        <v>124800309</v>
       </c>
       <c r="B47" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440874</v>
+        <v>440821</v>
       </c>
       <c r="R47" t="n">
-        <v>7001281</v>
+        <v>7001261</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124800302</v>
+        <v>124800325</v>
       </c>
       <c r="B48" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5565,21 +5565,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440910</v>
+        <v>440674</v>
       </c>
       <c r="R48" t="n">
-        <v>7001371</v>
+        <v>7001385</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5655,10 +5655,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124800321</v>
+        <v>124800340</v>
       </c>
       <c r="B49" t="n">
-        <v>91008</v>
+        <v>74901</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440709</v>
+        <v>440590</v>
       </c>
       <c r="R49" t="n">
-        <v>7001238</v>
+        <v>7001362</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124738082</v>
+        <v>124800318</v>
       </c>
       <c r="B3" t="n">
-        <v>88359</v>
+        <v>96354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440684</v>
+        <v>440721</v>
       </c>
       <c r="R3" t="n">
-        <v>7001254</v>
+        <v>7001216</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,12 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800318</v>
+        <v>124800297</v>
       </c>
       <c r="B4" t="n">
-        <v>96354</v>
+        <v>91026</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -933,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440721</v>
+        <v>440921</v>
       </c>
       <c r="R4" t="n">
-        <v>7001216</v>
+        <v>7001295</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800297</v>
+        <v>124800313</v>
       </c>
       <c r="B5" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1039,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440921</v>
+        <v>440791</v>
       </c>
       <c r="R5" t="n">
-        <v>7001295</v>
+        <v>7001239</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800313</v>
+        <v>124800300</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1121,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1145,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440791</v>
+        <v>440915</v>
       </c>
       <c r="R6" t="n">
-        <v>7001239</v>
+        <v>7001296</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800300</v>
+        <v>124800294</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>79851</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,25 +1223,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1251,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440915</v>
+        <v>441028</v>
       </c>
       <c r="R7" t="n">
-        <v>7001296</v>
+        <v>7001364</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800294</v>
+        <v>124738082</v>
       </c>
       <c r="B8" t="n">
-        <v>79851</v>
+        <v>88359</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,42 +1329,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441028</v>
+        <v>440684</v>
       </c>
       <c r="R8" t="n">
-        <v>7001364</v>
+        <v>7001254</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2687,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124740889</v>
+        <v>124800296</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,34 +2703,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440684</v>
+        <v>440939</v>
       </c>
       <c r="R21" t="n">
-        <v>7001254</v>
+        <v>7001309</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2757,12 +2761,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2789,7 +2793,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800296</v>
+        <v>124800304</v>
       </c>
       <c r="B22" t="n">
         <v>91012</v>
@@ -2833,10 +2837,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440939</v>
+        <v>440902</v>
       </c>
       <c r="R22" t="n">
-        <v>7001309</v>
+        <v>7001332</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,10 +2899,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800304</v>
+        <v>124800298</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2911,21 +2915,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2939,10 +2943,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440902</v>
+        <v>440916</v>
       </c>
       <c r="R23" t="n">
-        <v>7001332</v>
+        <v>7001320</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +3005,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800298</v>
+        <v>124800331</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3045,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440916</v>
+        <v>440637</v>
       </c>
       <c r="R24" t="n">
-        <v>7001320</v>
+        <v>7001171</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3107,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800331</v>
+        <v>124800338</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>96776</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3119,25 +3123,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2389</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3151,10 +3155,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440637</v>
+        <v>440604</v>
       </c>
       <c r="R25" t="n">
-        <v>7001171</v>
+        <v>7001240</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3213,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800338</v>
+        <v>124740889</v>
       </c>
       <c r="B26" t="n">
-        <v>96776</v>
+        <v>91030</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3225,42 +3229,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2389</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440604</v>
+        <v>440684</v>
       </c>
       <c r="R26" t="n">
-        <v>7001240</v>
+        <v>7001254</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3287,12 +3287,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3531,10 +3531,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800305</v>
+        <v>124800329</v>
       </c>
       <c r="B29" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440874</v>
+        <v>440658</v>
       </c>
       <c r="R29" t="n">
-        <v>7001281</v>
+        <v>7001354</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3637,7 +3637,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800329</v>
+        <v>124800326</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440658</v>
+        <v>440672</v>
       </c>
       <c r="R30" t="n">
-        <v>7001354</v>
+        <v>7001335</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3743,10 +3743,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800326</v>
+        <v>124800324</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>91361</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3755,25 +3755,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3781,16 +3781,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440672</v>
+        <v>440680</v>
       </c>
       <c r="R31" t="n">
-        <v>7001335</v>
+        <v>7001258</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3831,6 +3834,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3849,10 +3853,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124800324</v>
+        <v>124800305</v>
       </c>
       <c r="B32" t="n">
-        <v>91361</v>
+        <v>91299</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3861,25 +3865,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3887,19 +3891,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440680</v>
+        <v>440874</v>
       </c>
       <c r="R32" t="n">
-        <v>7001258</v>
+        <v>7001281</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3940,7 +3941,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800318</v>
+        <v>124738082</v>
       </c>
       <c r="B3" t="n">
-        <v>96354</v>
+        <v>88359</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,38 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440721</v>
+        <v>440684</v>
       </c>
       <c r="R3" t="n">
-        <v>7001216</v>
+        <v>7001254</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800297</v>
+        <v>124800318</v>
       </c>
       <c r="B4" t="n">
-        <v>91026</v>
+        <v>96354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440921</v>
+        <v>440721</v>
       </c>
       <c r="R4" t="n">
-        <v>7001295</v>
+        <v>7001216</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800313</v>
+        <v>124800297</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1043,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440791</v>
+        <v>440921</v>
       </c>
       <c r="R5" t="n">
-        <v>7001239</v>
+        <v>7001295</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800300</v>
+        <v>124800313</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1149,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440915</v>
+        <v>440791</v>
       </c>
       <c r="R6" t="n">
-        <v>7001296</v>
+        <v>7001239</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800294</v>
+        <v>124800300</v>
       </c>
       <c r="B7" t="n">
-        <v>79851</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,25 +1219,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1255,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441028</v>
+        <v>440915</v>
       </c>
       <c r="R7" t="n">
-        <v>7001364</v>
+        <v>7001296</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124738082</v>
+        <v>124800294</v>
       </c>
       <c r="B8" t="n">
-        <v>88359</v>
+        <v>79851</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,38 +1325,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440684</v>
+        <v>441028</v>
       </c>
       <c r="R8" t="n">
-        <v>7001254</v>
+        <v>7001364</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -3531,10 +3531,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800329</v>
+        <v>124800305</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440658</v>
+        <v>440874</v>
       </c>
       <c r="R29" t="n">
-        <v>7001354</v>
+        <v>7001281</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3637,7 +3637,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800326</v>
+        <v>124800329</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440672</v>
+        <v>440658</v>
       </c>
       <c r="R30" t="n">
-        <v>7001335</v>
+        <v>7001354</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3743,10 +3743,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800324</v>
+        <v>124800326</v>
       </c>
       <c r="B31" t="n">
-        <v>91361</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3755,25 +3755,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3781,19 +3781,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440680</v>
+        <v>440672</v>
       </c>
       <c r="R31" t="n">
-        <v>7001258</v>
+        <v>7001335</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3834,7 +3831,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3853,10 +3849,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124800305</v>
+        <v>124800324</v>
       </c>
       <c r="B32" t="n">
-        <v>91299</v>
+        <v>91361</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3865,25 +3861,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3891,16 +3887,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440874</v>
+        <v>440680</v>
       </c>
       <c r="R32" t="n">
-        <v>7001281</v>
+        <v>7001258</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3941,6 +3940,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124738082</v>
+        <v>124800311</v>
       </c>
       <c r="B3" t="n">
-        <v>88359</v>
+        <v>77753</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440684</v>
+        <v>440798</v>
       </c>
       <c r="R3" t="n">
-        <v>7001254</v>
+        <v>7001239</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,12 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800318</v>
+        <v>124800296</v>
       </c>
       <c r="B4" t="n">
-        <v>96354</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -933,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440721</v>
+        <v>440939</v>
       </c>
       <c r="R4" t="n">
-        <v>7001216</v>
+        <v>7001309</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800297</v>
+        <v>124800304</v>
       </c>
       <c r="B5" t="n">
-        <v>91026</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1039,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440921</v>
+        <v>440902</v>
       </c>
       <c r="R5" t="n">
-        <v>7001295</v>
+        <v>7001332</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800313</v>
+        <v>124800321</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1121,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1145,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440791</v>
+        <v>440709</v>
       </c>
       <c r="R6" t="n">
-        <v>7001239</v>
+        <v>7001238</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800300</v>
+        <v>124740817</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,38 +1227,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440915</v>
+        <v>440684</v>
       </c>
       <c r="R7" t="n">
-        <v>7001296</v>
+        <v>7001254</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800294</v>
+        <v>124800332</v>
       </c>
       <c r="B8" t="n">
-        <v>79851</v>
+        <v>74906</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,25 +1325,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441028</v>
+        <v>440630</v>
       </c>
       <c r="R8" t="n">
-        <v>7001364</v>
+        <v>7001086</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800299</v>
+        <v>124800305</v>
       </c>
       <c r="B9" t="n">
-        <v>78889</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440915</v>
+        <v>440874</v>
       </c>
       <c r="R9" t="n">
-        <v>7001377</v>
+        <v>7001281</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1525,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124740817</v>
+        <v>124800298</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1558,17 +1558,21 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440684</v>
+        <v>440916</v>
       </c>
       <c r="R10" t="n">
-        <v>7001254</v>
+        <v>7001320</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,12 +1599,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1627,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800322</v>
+        <v>124800300</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1643,21 +1647,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1671,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440696</v>
+        <v>440915</v>
       </c>
       <c r="R11" t="n">
-        <v>7001259</v>
+        <v>7001296</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800306</v>
+        <v>124800323</v>
       </c>
       <c r="B12" t="n">
-        <v>88359</v>
+        <v>74901</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1749,21 +1753,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1777,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440872</v>
+        <v>440681</v>
       </c>
       <c r="R12" t="n">
-        <v>7001384</v>
+        <v>7001285</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800316</v>
+        <v>124800340</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,21 +1859,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1883,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440773</v>
+        <v>440590</v>
       </c>
       <c r="R13" t="n">
-        <v>7001489</v>
+        <v>7001362</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800302</v>
+        <v>124800308</v>
       </c>
       <c r="B14" t="n">
-        <v>78889</v>
+        <v>88359</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1961,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>864</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1989,10 +1993,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440910</v>
+        <v>440850</v>
       </c>
       <c r="R14" t="n">
-        <v>7001371</v>
+        <v>7001393</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800334</v>
+        <v>124800318</v>
       </c>
       <c r="B15" t="n">
-        <v>77753</v>
+        <v>96354</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,21 +2071,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>314</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2095,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440624</v>
+        <v>440721</v>
       </c>
       <c r="R15" t="n">
-        <v>7001080</v>
+        <v>7001216</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800308</v>
+        <v>124800329</v>
       </c>
       <c r="B16" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2173,21 +2177,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2201,10 +2205,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440850</v>
+        <v>440658</v>
       </c>
       <c r="R16" t="n">
-        <v>7001393</v>
+        <v>7001354</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2267,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800327</v>
+        <v>124800314</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2307,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440672</v>
+        <v>440785</v>
       </c>
       <c r="R17" t="n">
-        <v>7001361</v>
+        <v>7001501</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,12 +2341,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2369,10 +2373,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800314</v>
+        <v>124738082</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2385,38 +2389,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440785</v>
+        <v>440684</v>
       </c>
       <c r="R18" t="n">
-        <v>7001501</v>
+        <v>7001254</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2475,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800319</v>
+        <v>124801009</v>
       </c>
       <c r="B19" t="n">
-        <v>97185</v>
+        <v>94769</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2491,21 +2491,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220686</v>
+        <v>2411</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Nordlig källmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Philonotis tomentella</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Molendo</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440720</v>
+        <v>440900</v>
       </c>
       <c r="R19" t="n">
-        <v>7001201</v>
+        <v>7001371</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2581,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800315</v>
+        <v>124800333</v>
       </c>
       <c r="B20" t="n">
-        <v>78889</v>
+        <v>82597</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,21 +2597,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440782</v>
+        <v>440628</v>
       </c>
       <c r="R20" t="n">
-        <v>7001494</v>
+        <v>7001081</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800296</v>
+        <v>124800320</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,21 +2703,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440939</v>
+        <v>440720</v>
       </c>
       <c r="R21" t="n">
-        <v>7001309</v>
+        <v>7001206</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800304</v>
+        <v>124800306</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2809,21 +2809,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440902</v>
+        <v>440872</v>
       </c>
       <c r="R22" t="n">
-        <v>7001332</v>
+        <v>7001384</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800298</v>
+        <v>124800315</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2915,21 +2915,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440916</v>
+        <v>440782</v>
       </c>
       <c r="R23" t="n">
-        <v>7001320</v>
+        <v>7001494</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,10 +3005,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800331</v>
+        <v>124800338</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>96776</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3017,25 +3017,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2389</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440637</v>
+        <v>440604</v>
       </c>
       <c r="R24" t="n">
-        <v>7001171</v>
+        <v>7001240</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800338</v>
+        <v>124800327</v>
       </c>
       <c r="B25" t="n">
-        <v>96776</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3123,25 +3123,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2389</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440604</v>
+        <v>440672</v>
       </c>
       <c r="R25" t="n">
-        <v>7001240</v>
+        <v>7001361</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124740889</v>
+        <v>124800319</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>97185</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3229,38 +3229,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>220686</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440684</v>
+        <v>440720</v>
       </c>
       <c r="R26" t="n">
-        <v>7001254</v>
+        <v>7001201</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3287,12 +3291,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3319,10 +3323,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800335</v>
+        <v>124800331</v>
       </c>
       <c r="B27" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3335,21 +3339,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3363,10 +3367,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440621</v>
+        <v>440637</v>
       </c>
       <c r="R27" t="n">
-        <v>7001181</v>
+        <v>7001171</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,10 +3429,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800293</v>
+        <v>124800302</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
+        <v>78889</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3441,21 +3445,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3469,10 +3473,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441111</v>
+        <v>440910</v>
       </c>
       <c r="R28" t="n">
-        <v>7001333</v>
+        <v>7001371</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,10 +3535,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800305</v>
+        <v>124800336</v>
       </c>
       <c r="B29" t="n">
-        <v>91299</v>
+        <v>91026</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3547,21 +3551,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3575,10 +3579,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440874</v>
+        <v>440616</v>
       </c>
       <c r="R29" t="n">
-        <v>7001281</v>
+        <v>7001215</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3637,7 +3641,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800329</v>
+        <v>124800326</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3681,10 +3685,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440658</v>
+        <v>440672</v>
       </c>
       <c r="R30" t="n">
-        <v>7001354</v>
+        <v>7001335</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3743,10 +3747,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800326</v>
+        <v>124800293</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3759,21 +3763,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3787,10 +3791,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440672</v>
+        <v>441111</v>
       </c>
       <c r="R31" t="n">
-        <v>7001335</v>
+        <v>7001333</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3849,10 +3853,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124800324</v>
+        <v>124800316</v>
       </c>
       <c r="B32" t="n">
-        <v>91361</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3861,25 +3865,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3887,19 +3891,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440680</v>
+        <v>440773</v>
       </c>
       <c r="R32" t="n">
-        <v>7001258</v>
+        <v>7001489</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3940,7 +3941,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3959,10 +3959,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124801009</v>
+        <v>124800330</v>
       </c>
       <c r="B33" t="n">
-        <v>94769</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3971,25 +3971,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2411</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nordlig källmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Philonotis tomentella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Molendo</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440900</v>
+        <v>440646</v>
       </c>
       <c r="R33" t="n">
-        <v>7001371</v>
+        <v>7001158</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124800321</v>
+        <v>124800307</v>
       </c>
       <c r="B34" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4081,21 +4081,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440709</v>
+        <v>440872</v>
       </c>
       <c r="R34" t="n">
-        <v>7001238</v>
+        <v>7001280</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4171,10 +4171,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124800307</v>
+        <v>124800310</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4215,10 +4215,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440872</v>
+        <v>440799</v>
       </c>
       <c r="R35" t="n">
-        <v>7001280</v>
+        <v>7001243</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4277,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124800323</v>
+        <v>124740889</v>
       </c>
       <c r="B36" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4293,38 +4293,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440681</v>
+        <v>440684</v>
       </c>
       <c r="R36" t="n">
-        <v>7001285</v>
+        <v>7001254</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,12 +4347,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4383,7 +4379,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124800330</v>
+        <v>124800303</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4427,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440646</v>
+        <v>440909</v>
       </c>
       <c r="R37" t="n">
-        <v>7001158</v>
+        <v>7001374</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4489,10 +4485,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124800332</v>
+        <v>124800297</v>
       </c>
       <c r="B38" t="n">
-        <v>74906</v>
+        <v>91026</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4505,21 +4501,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4533,10 +4529,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440630</v>
+        <v>440921</v>
       </c>
       <c r="R38" t="n">
-        <v>7001086</v>
+        <v>7001295</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,10 +4591,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124800303</v>
+        <v>124800324</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>91361</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4607,25 +4603,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4633,16 +4629,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440909</v>
+        <v>440680</v>
       </c>
       <c r="R39" t="n">
-        <v>7001374</v>
+        <v>7001258</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4683,6 +4682,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4701,10 +4701,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124800310</v>
+        <v>124800295</v>
       </c>
       <c r="B40" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4717,21 +4717,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440799</v>
+        <v>440940</v>
       </c>
       <c r="R40" t="n">
-        <v>7001243</v>
+        <v>7001369</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4807,10 +4807,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124800333</v>
+        <v>124800313</v>
       </c>
       <c r="B41" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440628</v>
+        <v>440791</v>
       </c>
       <c r="R41" t="n">
-        <v>7001081</v>
+        <v>7001239</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4913,10 +4913,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124800328</v>
+        <v>124800309</v>
       </c>
       <c r="B42" t="n">
-        <v>95335</v>
+        <v>91012</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4925,25 +4925,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440661</v>
+        <v>440821</v>
       </c>
       <c r="R42" t="n">
-        <v>7001244</v>
+        <v>7001261</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124800311</v>
+        <v>124800335</v>
       </c>
       <c r="B43" t="n">
-        <v>77753</v>
+        <v>78889</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5035,21 +5035,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>314</v>
+        <v>864</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5063,10 +5063,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440798</v>
+        <v>440621</v>
       </c>
       <c r="R43" t="n">
-        <v>7001239</v>
+        <v>7001181</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5125,10 +5125,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124800336</v>
+        <v>124800334</v>
       </c>
       <c r="B44" t="n">
-        <v>91026</v>
+        <v>77753</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5141,21 +5141,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1204</v>
+        <v>314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5169,10 +5169,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440616</v>
+        <v>440624</v>
       </c>
       <c r="R44" t="n">
-        <v>7001215</v>
+        <v>7001080</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5231,10 +5231,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124800295</v>
+        <v>124800325</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5247,21 +5247,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440940</v>
+        <v>440674</v>
       </c>
       <c r="R45" t="n">
-        <v>7001369</v>
+        <v>7001385</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124800320</v>
+        <v>124800322</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5353,21 +5353,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440720</v>
+        <v>440696</v>
       </c>
       <c r="R46" t="n">
-        <v>7001206</v>
+        <v>7001259</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124800309</v>
+        <v>124800294</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>79851</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5455,25 +5455,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440821</v>
+        <v>441028</v>
       </c>
       <c r="R47" t="n">
-        <v>7001261</v>
+        <v>7001364</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124800325</v>
+        <v>124800299</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5565,21 +5565,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440674</v>
+        <v>440915</v>
       </c>
       <c r="R48" t="n">
-        <v>7001385</v>
+        <v>7001377</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5655,10 +5655,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124800340</v>
+        <v>124800328</v>
       </c>
       <c r="B49" t="n">
-        <v>74901</v>
+        <v>95335</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5667,25 +5667,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440590</v>
+        <v>440661</v>
       </c>
       <c r="R49" t="n">
-        <v>7001362</v>
+        <v>7001244</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800311</v>
+        <v>124800309</v>
       </c>
       <c r="B3" t="n">
-        <v>77753</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>314</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440798</v>
+        <v>440821</v>
       </c>
       <c r="R3" t="n">
-        <v>7001239</v>
+        <v>7001261</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800304</v>
+        <v>124800295</v>
       </c>
       <c r="B5" t="n">
         <v>91012</v>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440902</v>
+        <v>440940</v>
       </c>
       <c r="R5" t="n">
-        <v>7001332</v>
+        <v>7001369</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800321</v>
+        <v>124801009</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>94769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,25 +1117,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>2411</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Nordlig källmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Philonotis tomentella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Molendo</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440709</v>
+        <v>440900</v>
       </c>
       <c r="R6" t="n">
-        <v>7001238</v>
+        <v>7001371</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124740817</v>
+        <v>124800336</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,34 +1227,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440684</v>
+        <v>440616</v>
       </c>
       <c r="R7" t="n">
-        <v>7001254</v>
+        <v>7001215</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,12 +1285,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800332</v>
+        <v>124800304</v>
       </c>
       <c r="B8" t="n">
-        <v>74906</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1357,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440630</v>
+        <v>440902</v>
       </c>
       <c r="R8" t="n">
-        <v>7001086</v>
+        <v>7001332</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800305</v>
+        <v>124800340</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>74901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1439,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1463,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440874</v>
+        <v>440590</v>
       </c>
       <c r="R9" t="n">
-        <v>7001281</v>
+        <v>7001362</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800298</v>
+        <v>124800334</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>77753</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,21 +1545,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1569,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440916</v>
+        <v>440624</v>
       </c>
       <c r="R10" t="n">
-        <v>7001320</v>
+        <v>7001080</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,10 +1635,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800300</v>
+        <v>124800329</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,21 +1651,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1675,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440915</v>
+        <v>440658</v>
       </c>
       <c r="R11" t="n">
-        <v>7001296</v>
+        <v>7001354</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800323</v>
+        <v>124800313</v>
       </c>
       <c r="B12" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,21 +1757,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1781,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440681</v>
+        <v>440791</v>
       </c>
       <c r="R12" t="n">
-        <v>7001285</v>
+        <v>7001239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800340</v>
+        <v>124740817</v>
       </c>
       <c r="B13" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,38 +1863,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440590</v>
+        <v>440684</v>
       </c>
       <c r="R13" t="n">
-        <v>7001362</v>
+        <v>7001254</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,12 +1917,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800308</v>
+        <v>124738082</v>
       </c>
       <c r="B14" t="n">
         <v>88359</v>
@@ -1982,21 +1982,17 @@
           <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440850</v>
+        <v>440684</v>
       </c>
       <c r="R14" t="n">
-        <v>7001393</v>
+        <v>7001254</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,12 +2019,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2055,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800318</v>
+        <v>124800326</v>
       </c>
       <c r="B15" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2071,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2099,10 +2095,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440721</v>
+        <v>440672</v>
       </c>
       <c r="R15" t="n">
-        <v>7001216</v>
+        <v>7001335</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,10 +2157,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800329</v>
+        <v>124800321</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2177,21 +2173,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2205,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440658</v>
+        <v>440709</v>
       </c>
       <c r="R16" t="n">
-        <v>7001354</v>
+        <v>7001238</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2267,10 +2263,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800314</v>
+        <v>124800322</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2283,21 +2279,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2311,10 +2307,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440785</v>
+        <v>440696</v>
       </c>
       <c r="R17" t="n">
-        <v>7001501</v>
+        <v>7001259</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2341,12 +2337,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2373,10 +2369,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124738082</v>
+        <v>124800319</v>
       </c>
       <c r="B18" t="n">
-        <v>88359</v>
+        <v>97185</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2385,38 +2381,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>220686</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440684</v>
+        <v>440720</v>
       </c>
       <c r="R18" t="n">
-        <v>7001254</v>
+        <v>7001201</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,12 +2443,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2475,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124801009</v>
+        <v>124800328</v>
       </c>
       <c r="B19" t="n">
-        <v>94769</v>
+        <v>95335</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2491,21 +2491,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2411</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordlig källmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Philonotis tomentella</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Molendo</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440900</v>
+        <v>440661</v>
       </c>
       <c r="R19" t="n">
-        <v>7001371</v>
+        <v>7001244</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2581,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800333</v>
+        <v>124800332</v>
       </c>
       <c r="B20" t="n">
-        <v>82597</v>
+        <v>74906</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,21 +2597,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440628</v>
+        <v>440630</v>
       </c>
       <c r="R20" t="n">
-        <v>7001081</v>
+        <v>7001086</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800320</v>
+        <v>124800318</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,21 +2703,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440720</v>
+        <v>440721</v>
       </c>
       <c r="R21" t="n">
-        <v>7001206</v>
+        <v>7001216</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800306</v>
+        <v>124800335</v>
       </c>
       <c r="B22" t="n">
-        <v>88359</v>
+        <v>78889</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2809,21 +2809,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>864</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440872</v>
+        <v>440621</v>
       </c>
       <c r="R22" t="n">
-        <v>7001384</v>
+        <v>7001181</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800315</v>
+        <v>124800327</v>
       </c>
       <c r="B23" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2915,21 +2915,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440782</v>
+        <v>440672</v>
       </c>
       <c r="R23" t="n">
-        <v>7001494</v>
+        <v>7001361</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,10 +3005,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800338</v>
+        <v>124800310</v>
       </c>
       <c r="B24" t="n">
-        <v>96776</v>
+        <v>74901</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3017,25 +3017,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2389</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440604</v>
+        <v>440799</v>
       </c>
       <c r="R24" t="n">
-        <v>7001240</v>
+        <v>7001243</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800327</v>
+        <v>124800308</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3127,21 +3127,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440672</v>
+        <v>440850</v>
       </c>
       <c r="R25" t="n">
-        <v>7001361</v>
+        <v>7001393</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800319</v>
+        <v>124800324</v>
       </c>
       <c r="B26" t="n">
-        <v>97185</v>
+        <v>91361</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3229,25 +3229,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220686</v>
+        <v>2062</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3255,16 +3255,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440720</v>
+        <v>440680</v>
       </c>
       <c r="R26" t="n">
-        <v>7001201</v>
+        <v>7001258</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3305,6 +3308,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3323,10 +3327,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800331</v>
+        <v>124800297</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3339,21 +3343,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3367,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440637</v>
+        <v>440921</v>
       </c>
       <c r="R27" t="n">
-        <v>7001171</v>
+        <v>7001295</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,10 +3433,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800302</v>
+        <v>124800307</v>
       </c>
       <c r="B28" t="n">
-        <v>78889</v>
+        <v>91012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3445,21 +3449,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3473,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440910</v>
+        <v>440872</v>
       </c>
       <c r="R28" t="n">
-        <v>7001371</v>
+        <v>7001280</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3535,10 +3539,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800336</v>
+        <v>124800320</v>
       </c>
       <c r="B29" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3551,21 +3555,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3579,10 +3583,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440616</v>
+        <v>440720</v>
       </c>
       <c r="R29" t="n">
-        <v>7001215</v>
+        <v>7001206</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3641,7 +3645,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800326</v>
+        <v>124800330</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3685,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440672</v>
+        <v>440646</v>
       </c>
       <c r="R30" t="n">
-        <v>7001335</v>
+        <v>7001158</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3747,10 +3751,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800293</v>
+        <v>124740889</v>
       </c>
       <c r="B31" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3763,38 +3767,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441111</v>
+        <v>440684</v>
       </c>
       <c r="R31" t="n">
-        <v>7001333</v>
+        <v>7001254</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3853,10 +3853,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124800316</v>
+        <v>124800311</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>77753</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3869,21 +3869,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440773</v>
+        <v>440798</v>
       </c>
       <c r="R32" t="n">
-        <v>7001489</v>
+        <v>7001239</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3959,10 +3959,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124800330</v>
+        <v>124800305</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3975,21 +3975,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440646</v>
+        <v>440874</v>
       </c>
       <c r="R33" t="n">
-        <v>7001158</v>
+        <v>7001281</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124800307</v>
+        <v>124800333</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>82597</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4081,21 +4081,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440872</v>
+        <v>440628</v>
       </c>
       <c r="R34" t="n">
-        <v>7001280</v>
+        <v>7001081</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4171,10 +4171,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124800310</v>
+        <v>124800325</v>
       </c>
       <c r="B35" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4215,10 +4215,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440799</v>
+        <v>440674</v>
       </c>
       <c r="R35" t="n">
-        <v>7001243</v>
+        <v>7001385</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4277,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124740889</v>
+        <v>124800294</v>
       </c>
       <c r="B36" t="n">
-        <v>91030</v>
+        <v>79851</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4289,38 +4289,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440684</v>
+        <v>441028</v>
       </c>
       <c r="R36" t="n">
-        <v>7001254</v>
+        <v>7001364</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4347,12 +4351,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4379,10 +4383,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124800303</v>
+        <v>124800302</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4395,21 +4399,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4423,10 +4427,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440909</v>
+        <v>440910</v>
       </c>
       <c r="R37" t="n">
-        <v>7001374</v>
+        <v>7001371</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4485,10 +4489,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124800297</v>
+        <v>124800303</v>
       </c>
       <c r="B38" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4501,21 +4505,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4529,10 +4533,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440921</v>
+        <v>440909</v>
       </c>
       <c r="R38" t="n">
-        <v>7001295</v>
+        <v>7001374</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4591,10 +4595,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124800324</v>
+        <v>124800331</v>
       </c>
       <c r="B39" t="n">
-        <v>91361</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4603,25 +4607,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4629,19 +4633,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440680</v>
+        <v>440637</v>
       </c>
       <c r="R39" t="n">
-        <v>7001258</v>
+        <v>7001171</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4682,7 +4683,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4701,10 +4701,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124800295</v>
+        <v>124800299</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>78889</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4717,21 +4717,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440940</v>
+        <v>440915</v>
       </c>
       <c r="R40" t="n">
-        <v>7001369</v>
+        <v>7001377</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4807,10 +4807,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124800313</v>
+        <v>124800306</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440791</v>
+        <v>440872</v>
       </c>
       <c r="R41" t="n">
-        <v>7001239</v>
+        <v>7001384</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4913,10 +4913,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124800309</v>
+        <v>124800316</v>
       </c>
       <c r="B42" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4929,21 +4929,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440821</v>
+        <v>440773</v>
       </c>
       <c r="R42" t="n">
-        <v>7001261</v>
+        <v>7001489</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124800335</v>
+        <v>124800300</v>
       </c>
       <c r="B43" t="n">
-        <v>78889</v>
+        <v>91030</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5035,21 +5035,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5063,10 +5063,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440621</v>
+        <v>440915</v>
       </c>
       <c r="R43" t="n">
-        <v>7001181</v>
+        <v>7001296</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5125,10 +5125,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124800334</v>
+        <v>124800338</v>
       </c>
       <c r="B44" t="n">
-        <v>77753</v>
+        <v>96776</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5137,25 +5137,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>314</v>
+        <v>2389</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5169,10 +5169,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440624</v>
+        <v>440604</v>
       </c>
       <c r="R44" t="n">
-        <v>7001080</v>
+        <v>7001240</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5231,10 +5231,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124800325</v>
+        <v>124800315</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5247,21 +5247,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440674</v>
+        <v>440782</v>
       </c>
       <c r="R45" t="n">
-        <v>7001385</v>
+        <v>7001494</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124800322</v>
+        <v>124800323</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5353,21 +5353,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440696</v>
+        <v>440681</v>
       </c>
       <c r="R46" t="n">
-        <v>7001259</v>
+        <v>7001285</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124800294</v>
+        <v>124800298</v>
       </c>
       <c r="B47" t="n">
-        <v>79851</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5455,25 +5455,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>441028</v>
+        <v>440916</v>
       </c>
       <c r="R47" t="n">
-        <v>7001364</v>
+        <v>7001320</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124800299</v>
+        <v>124800314</v>
       </c>
       <c r="B48" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5565,21 +5565,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440915</v>
+        <v>440785</v>
       </c>
       <c r="R48" t="n">
-        <v>7001377</v>
+        <v>7001501</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5655,10 +5655,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124800328</v>
+        <v>124800293</v>
       </c>
       <c r="B49" t="n">
-        <v>95335</v>
+        <v>57529</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5667,25 +5667,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440661</v>
+        <v>441111</v>
       </c>
       <c r="R49" t="n">
-        <v>7001244</v>
+        <v>7001333</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800309</v>
+        <v>124800320</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440821</v>
+        <v>440720</v>
       </c>
       <c r="R3" t="n">
-        <v>7001261</v>
+        <v>7001206</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800296</v>
+        <v>124800293</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440939</v>
+        <v>441111</v>
       </c>
       <c r="R4" t="n">
-        <v>7001309</v>
+        <v>7001333</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800295</v>
+        <v>124800298</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440940</v>
+        <v>440916</v>
       </c>
       <c r="R5" t="n">
-        <v>7001369</v>
+        <v>7001320</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124801009</v>
+        <v>124800299</v>
       </c>
       <c r="B6" t="n">
-        <v>94769</v>
+        <v>78889</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,25 +1117,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2411</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordlig källmossa</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Philonotis tomentella</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Molendo</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440900</v>
+        <v>440915</v>
       </c>
       <c r="R6" t="n">
-        <v>7001371</v>
+        <v>7001377</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800304</v>
+        <v>124800330</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440902</v>
+        <v>440646</v>
       </c>
       <c r="R8" t="n">
-        <v>7001332</v>
+        <v>7001158</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800340</v>
+        <v>124738082</v>
       </c>
       <c r="B9" t="n">
-        <v>74901</v>
+        <v>88359</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,38 +1439,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440590</v>
+        <v>440684</v>
       </c>
       <c r="R9" t="n">
-        <v>7001362</v>
+        <v>7001254</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,12 +1493,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800334</v>
+        <v>124800318</v>
       </c>
       <c r="B10" t="n">
-        <v>77753</v>
+        <v>96354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,21 +1541,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>314</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1573,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440624</v>
+        <v>440721</v>
       </c>
       <c r="R10" t="n">
-        <v>7001080</v>
+        <v>7001216</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800329</v>
+        <v>124800321</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,21 +1647,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1679,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440658</v>
+        <v>440709</v>
       </c>
       <c r="R11" t="n">
-        <v>7001354</v>
+        <v>7001238</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800313</v>
+        <v>124800319</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>97185</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,25 +1749,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220686</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1785,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440791</v>
+        <v>440720</v>
       </c>
       <c r="R12" t="n">
-        <v>7001239</v>
+        <v>7001201</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124740817</v>
+        <v>124800335</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,34 +1859,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440684</v>
+        <v>440621</v>
       </c>
       <c r="R13" t="n">
-        <v>7001254</v>
+        <v>7001181</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,12 +1917,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124738082</v>
+        <v>124800334</v>
       </c>
       <c r="B14" t="n">
-        <v>88359</v>
+        <v>77753</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,34 +1965,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440684</v>
+        <v>440624</v>
       </c>
       <c r="R14" t="n">
-        <v>7001254</v>
+        <v>7001080</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,12 +2023,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800326</v>
+        <v>124800323</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,21 +2071,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2095,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440672</v>
+        <v>440681</v>
       </c>
       <c r="R15" t="n">
-        <v>7001335</v>
+        <v>7001285</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800321</v>
+        <v>124800333</v>
       </c>
       <c r="B16" t="n">
-        <v>91008</v>
+        <v>82597</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2173,21 +2177,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2201,10 +2205,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440709</v>
+        <v>440628</v>
       </c>
       <c r="R16" t="n">
-        <v>7001238</v>
+        <v>7001081</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,10 +2267,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800322</v>
+        <v>124800303</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2279,21 +2283,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2307,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440696</v>
+        <v>440909</v>
       </c>
       <c r="R17" t="n">
-        <v>7001259</v>
+        <v>7001374</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,10 +2373,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800319</v>
+        <v>124800302</v>
       </c>
       <c r="B18" t="n">
-        <v>97185</v>
+        <v>78889</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2381,25 +2385,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220686</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2413,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440720</v>
+        <v>440910</v>
       </c>
       <c r="R18" t="n">
-        <v>7001201</v>
+        <v>7001371</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2581,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800332</v>
+        <v>124800329</v>
       </c>
       <c r="B20" t="n">
-        <v>74906</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,21 +2601,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2625,10 +2629,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440630</v>
+        <v>440658</v>
       </c>
       <c r="R20" t="n">
-        <v>7001086</v>
+        <v>7001354</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2687,10 +2691,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800318</v>
+        <v>124800326</v>
       </c>
       <c r="B21" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,21 +2707,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2731,10 +2735,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440721</v>
+        <v>440672</v>
       </c>
       <c r="R21" t="n">
-        <v>7001216</v>
+        <v>7001335</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,10 +2797,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800335</v>
+        <v>124800306</v>
       </c>
       <c r="B22" t="n">
-        <v>78889</v>
+        <v>88359</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2809,21 +2813,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>864</v>
+        <v>510</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2837,10 +2841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440621</v>
+        <v>440872</v>
       </c>
       <c r="R22" t="n">
-        <v>7001181</v>
+        <v>7001384</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2899,10 +2903,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800327</v>
+        <v>124800300</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2915,21 +2919,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2943,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440672</v>
+        <v>440915</v>
       </c>
       <c r="R23" t="n">
-        <v>7001361</v>
+        <v>7001296</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,10 +3009,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800310</v>
+        <v>124800316</v>
       </c>
       <c r="B24" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3021,21 +3025,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3049,10 +3053,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440799</v>
+        <v>440773</v>
       </c>
       <c r="R24" t="n">
-        <v>7001243</v>
+        <v>7001489</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,10 +3115,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800308</v>
+        <v>124740817</v>
       </c>
       <c r="B25" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3127,38 +3131,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440850</v>
+        <v>440684</v>
       </c>
       <c r="R25" t="n">
-        <v>7001393</v>
+        <v>7001254</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3185,12 +3185,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3217,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800324</v>
+        <v>124800313</v>
       </c>
       <c r="B26" t="n">
-        <v>91361</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3229,25 +3229,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3255,19 +3255,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440680</v>
+        <v>440791</v>
       </c>
       <c r="R26" t="n">
-        <v>7001258</v>
+        <v>7001239</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3308,7 +3305,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3327,10 +3323,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800297</v>
+        <v>124800310</v>
       </c>
       <c r="B27" t="n">
-        <v>91026</v>
+        <v>74901</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3343,21 +3339,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3371,10 +3367,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440921</v>
+        <v>440799</v>
       </c>
       <c r="R27" t="n">
-        <v>7001295</v>
+        <v>7001243</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3433,7 +3429,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800307</v>
+        <v>124800295</v>
       </c>
       <c r="B28" t="n">
         <v>91012</v>
@@ -3477,10 +3473,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440872</v>
+        <v>440940</v>
       </c>
       <c r="R28" t="n">
-        <v>7001280</v>
+        <v>7001369</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3539,10 +3535,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800320</v>
+        <v>124800304</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3555,21 +3551,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3583,10 +3579,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440720</v>
+        <v>440902</v>
       </c>
       <c r="R29" t="n">
-        <v>7001206</v>
+        <v>7001332</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3645,7 +3641,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800330</v>
+        <v>124800327</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3689,10 +3685,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440646</v>
+        <v>440672</v>
       </c>
       <c r="R30" t="n">
-        <v>7001158</v>
+        <v>7001361</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3751,10 +3747,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124740889</v>
+        <v>124800338</v>
       </c>
       <c r="B31" t="n">
-        <v>91030</v>
+        <v>96776</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3763,38 +3759,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>2389</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Hook.) Gray</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440684</v>
+        <v>440604</v>
       </c>
       <c r="R31" t="n">
-        <v>7001254</v>
+        <v>7001240</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3853,10 +3853,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124800311</v>
+        <v>124740889</v>
       </c>
       <c r="B32" t="n">
-        <v>77753</v>
+        <v>91030</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3869,38 +3869,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>314</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440798</v>
+        <v>440684</v>
       </c>
       <c r="R32" t="n">
-        <v>7001239</v>
+        <v>7001254</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3927,12 +3923,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3959,10 +3955,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124800305</v>
+        <v>124800311</v>
       </c>
       <c r="B33" t="n">
-        <v>91299</v>
+        <v>77753</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3975,21 +3971,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4003,10 +3999,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440874</v>
+        <v>440798</v>
       </c>
       <c r="R33" t="n">
-        <v>7001281</v>
+        <v>7001239</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4065,10 +4061,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124800333</v>
+        <v>124800308</v>
       </c>
       <c r="B34" t="n">
-        <v>82597</v>
+        <v>88359</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4081,21 +4077,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4109,10 +4105,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440628</v>
+        <v>440850</v>
       </c>
       <c r="R34" t="n">
-        <v>7001081</v>
+        <v>7001393</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4171,10 +4167,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124800325</v>
+        <v>124800324</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>91361</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4183,25 +4179,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4209,16 +4205,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440674</v>
+        <v>440680</v>
       </c>
       <c r="R35" t="n">
-        <v>7001385</v>
+        <v>7001258</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4259,6 +4258,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4277,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124800294</v>
+        <v>124801009</v>
       </c>
       <c r="B36" t="n">
-        <v>79851</v>
+        <v>94769</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4293,21 +4293,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>2411</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Nordlig källmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Philonotis tomentella</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Molendo</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>441028</v>
+        <v>440900</v>
       </c>
       <c r="R36" t="n">
-        <v>7001364</v>
+        <v>7001371</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,10 +4383,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124800302</v>
+        <v>124800305</v>
       </c>
       <c r="B37" t="n">
-        <v>78889</v>
+        <v>91299</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4399,21 +4399,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440910</v>
+        <v>440874</v>
       </c>
       <c r="R37" t="n">
-        <v>7001371</v>
+        <v>7001281</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4489,10 +4489,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124800303</v>
+        <v>124800307</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4505,21 +4505,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440909</v>
+        <v>440872</v>
       </c>
       <c r="R38" t="n">
-        <v>7001374</v>
+        <v>7001280</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4595,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124800331</v>
+        <v>124800314</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440637</v>
+        <v>440785</v>
       </c>
       <c r="R39" t="n">
-        <v>7001171</v>
+        <v>7001501</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4669,12 +4669,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4701,10 +4701,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124800299</v>
+        <v>124800294</v>
       </c>
       <c r="B40" t="n">
-        <v>78889</v>
+        <v>79851</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4713,25 +4713,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>864</v>
+        <v>229497</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440915</v>
+        <v>441028</v>
       </c>
       <c r="R40" t="n">
-        <v>7001377</v>
+        <v>7001364</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4807,10 +4807,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124800306</v>
+        <v>124800296</v>
       </c>
       <c r="B41" t="n">
-        <v>88359</v>
+        <v>91012</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440872</v>
+        <v>440939</v>
       </c>
       <c r="R41" t="n">
-        <v>7001384</v>
+        <v>7001309</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4913,7 +4913,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124800316</v>
+        <v>124800331</v>
       </c>
       <c r="B42" t="n">
         <v>78810</v>
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440773</v>
+        <v>440637</v>
       </c>
       <c r="R42" t="n">
-        <v>7001489</v>
+        <v>7001171</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124800300</v>
+        <v>124800325</v>
       </c>
       <c r="B43" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5035,21 +5035,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5063,10 +5063,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440915</v>
+        <v>440674</v>
       </c>
       <c r="R43" t="n">
-        <v>7001296</v>
+        <v>7001385</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5125,10 +5125,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124800338</v>
+        <v>124800340</v>
       </c>
       <c r="B44" t="n">
-        <v>96776</v>
+        <v>74901</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5137,25 +5137,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2389</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5169,10 +5169,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440604</v>
+        <v>440590</v>
       </c>
       <c r="R44" t="n">
-        <v>7001240</v>
+        <v>7001362</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5231,10 +5231,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124800315</v>
+        <v>124800309</v>
       </c>
       <c r="B45" t="n">
-        <v>78889</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5247,21 +5247,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440782</v>
+        <v>440821</v>
       </c>
       <c r="R45" t="n">
-        <v>7001494</v>
+        <v>7001261</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124800323</v>
+        <v>124800297</v>
       </c>
       <c r="B46" t="n">
-        <v>74901</v>
+        <v>91026</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5353,21 +5353,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440681</v>
+        <v>440921</v>
       </c>
       <c r="R46" t="n">
-        <v>7001285</v>
+        <v>7001295</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124800298</v>
+        <v>124800332</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>74906</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440916</v>
+        <v>440630</v>
       </c>
       <c r="R47" t="n">
-        <v>7001320</v>
+        <v>7001086</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124800314</v>
+        <v>124800315</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5565,21 +5565,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440785</v>
+        <v>440782</v>
       </c>
       <c r="R48" t="n">
-        <v>7001501</v>
+        <v>7001494</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5655,10 +5655,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124800293</v>
+        <v>124800322</v>
       </c>
       <c r="B49" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441111</v>
+        <v>440696</v>
       </c>
       <c r="R49" t="n">
-        <v>7001333</v>
+        <v>7001259</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800318</v>
+        <v>124800321</v>
       </c>
       <c r="B10" t="n">
-        <v>96354</v>
+        <v>91008</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,21 +1541,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440721</v>
+        <v>440709</v>
       </c>
       <c r="R10" t="n">
-        <v>7001216</v>
+        <v>7001238</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800321</v>
+        <v>124800318</v>
       </c>
       <c r="B11" t="n">
-        <v>91008</v>
+        <v>96354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,21 +1647,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440709</v>
+        <v>440721</v>
       </c>
       <c r="R11" t="n">
-        <v>7001238</v>
+        <v>7001216</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800333</v>
+        <v>124800302</v>
       </c>
       <c r="B16" t="n">
-        <v>82597</v>
+        <v>78889</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2177,21 +2177,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440628</v>
+        <v>440910</v>
       </c>
       <c r="R16" t="n">
-        <v>7001081</v>
+        <v>7001371</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2267,10 +2267,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800303</v>
+        <v>124800333</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2283,21 +2283,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440909</v>
+        <v>440628</v>
       </c>
       <c r="R17" t="n">
-        <v>7001374</v>
+        <v>7001081</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,10 +2373,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800302</v>
+        <v>124800303</v>
       </c>
       <c r="B18" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2389,21 +2389,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440910</v>
+        <v>440909</v>
       </c>
       <c r="R18" t="n">
-        <v>7001371</v>
+        <v>7001374</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800328</v>
+        <v>124800329</v>
       </c>
       <c r="B19" t="n">
-        <v>95335</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2491,25 +2491,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440661</v>
+        <v>440658</v>
       </c>
       <c r="R19" t="n">
-        <v>7001244</v>
+        <v>7001354</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2585,7 +2585,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800329</v>
+        <v>124800326</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440658</v>
+        <v>440672</v>
       </c>
       <c r="R20" t="n">
-        <v>7001354</v>
+        <v>7001335</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800326</v>
+        <v>124800328</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>95335</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,25 +2703,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440672</v>
+        <v>440661</v>
       </c>
       <c r="R21" t="n">
-        <v>7001335</v>
+        <v>7001244</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2903,10 +2903,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800300</v>
+        <v>124800316</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2919,21 +2919,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440915</v>
+        <v>440773</v>
       </c>
       <c r="R23" t="n">
-        <v>7001296</v>
+        <v>7001489</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3009,10 +3009,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800316</v>
+        <v>124800300</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3025,21 +3025,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440773</v>
+        <v>440915</v>
       </c>
       <c r="R24" t="n">
-        <v>7001489</v>
+        <v>7001296</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800304</v>
+        <v>124800338</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>96776</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3547,25 +3547,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>2389</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440902</v>
+        <v>440604</v>
       </c>
       <c r="R29" t="n">
-        <v>7001332</v>
+        <v>7001240</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3641,10 +3641,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800327</v>
+        <v>124800304</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3657,21 +3657,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440672</v>
+        <v>440902</v>
       </c>
       <c r="R30" t="n">
-        <v>7001361</v>
+        <v>7001332</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800338</v>
+        <v>124800327</v>
       </c>
       <c r="B31" t="n">
-        <v>96776</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3759,25 +3759,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2389</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440604</v>
+        <v>440672</v>
       </c>
       <c r="R31" t="n">
-        <v>7001240</v>
+        <v>7001361</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4277,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124801009</v>
+        <v>124800305</v>
       </c>
       <c r="B36" t="n">
-        <v>94769</v>
+        <v>91299</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4289,25 +4289,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2411</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordlig källmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Philonotis tomentella</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Molendo</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440900</v>
+        <v>440874</v>
       </c>
       <c r="R36" t="n">
-        <v>7001371</v>
+        <v>7001281</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,10 +4383,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124800305</v>
+        <v>124800307</v>
       </c>
       <c r="B37" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4399,21 +4399,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440874</v>
+        <v>440872</v>
       </c>
       <c r="R37" t="n">
-        <v>7001281</v>
+        <v>7001280</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4489,10 +4489,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124800307</v>
+        <v>124800294</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>79851</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4501,25 +4501,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440872</v>
+        <v>441028</v>
       </c>
       <c r="R38" t="n">
-        <v>7001280</v>
+        <v>7001364</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,10 +4595,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124800314</v>
+        <v>124801009</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>94769</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4607,25 +4607,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2411</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig källmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Philonotis tomentella</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Molendo</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440785</v>
+        <v>440900</v>
       </c>
       <c r="R39" t="n">
-        <v>7001501</v>
+        <v>7001371</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4669,12 +4669,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4701,10 +4701,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124800294</v>
+        <v>124800314</v>
       </c>
       <c r="B40" t="n">
-        <v>79851</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4713,25 +4713,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>441028</v>
+        <v>440785</v>
       </c>
       <c r="R40" t="n">
-        <v>7001364</v>
+        <v>7001501</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5231,10 +5231,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124800309</v>
+        <v>124800315</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>78889</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5247,21 +5247,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440821</v>
+        <v>440782</v>
       </c>
       <c r="R45" t="n">
-        <v>7001261</v>
+        <v>7001494</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124800297</v>
+        <v>124800309</v>
       </c>
       <c r="B46" t="n">
-        <v>91026</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5353,21 +5353,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440921</v>
+        <v>440821</v>
       </c>
       <c r="R46" t="n">
-        <v>7001295</v>
+        <v>7001261</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124800332</v>
+        <v>124800297</v>
       </c>
       <c r="B47" t="n">
-        <v>74906</v>
+        <v>91026</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440630</v>
+        <v>440921</v>
       </c>
       <c r="R47" t="n">
-        <v>7001086</v>
+        <v>7001295</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124800315</v>
+        <v>124800332</v>
       </c>
       <c r="B48" t="n">
-        <v>78889</v>
+        <v>74906</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5565,21 +5565,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>864</v>
+        <v>1467</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440782</v>
+        <v>440630</v>
       </c>
       <c r="R48" t="n">
-        <v>7001494</v>
+        <v>7001086</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800320</v>
+        <v>124800316</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440720</v>
+        <v>440773</v>
       </c>
       <c r="R3" t="n">
-        <v>7001206</v>
+        <v>7001489</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800293</v>
+        <v>124800311</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>77753</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441111</v>
+        <v>440798</v>
       </c>
       <c r="R4" t="n">
-        <v>7001333</v>
+        <v>7001239</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800298</v>
+        <v>124800294</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>79851</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1011,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440916</v>
+        <v>441028</v>
       </c>
       <c r="R5" t="n">
-        <v>7001320</v>
+        <v>7001364</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800299</v>
+        <v>124800310</v>
       </c>
       <c r="B6" t="n">
-        <v>78889</v>
+        <v>74901</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,21 +1121,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440915</v>
+        <v>440799</v>
       </c>
       <c r="R6" t="n">
-        <v>7001377</v>
+        <v>7001243</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800336</v>
+        <v>124800313</v>
       </c>
       <c r="B7" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,21 +1227,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440616</v>
+        <v>440791</v>
       </c>
       <c r="R7" t="n">
-        <v>7001215</v>
+        <v>7001239</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800330</v>
+        <v>124800303</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440646</v>
+        <v>440909</v>
       </c>
       <c r="R8" t="n">
-        <v>7001158</v>
+        <v>7001374</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124738082</v>
+        <v>124800300</v>
       </c>
       <c r="B9" t="n">
-        <v>88359</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,34 +1439,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440684</v>
+        <v>440915</v>
       </c>
       <c r="R9" t="n">
-        <v>7001254</v>
+        <v>7001296</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,12 +1497,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1525,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800321</v>
+        <v>124738082</v>
       </c>
       <c r="B10" t="n">
-        <v>91008</v>
+        <v>88359</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,38 +1545,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440709</v>
+        <v>440684</v>
       </c>
       <c r="R10" t="n">
-        <v>7001238</v>
+        <v>7001254</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800318</v>
+        <v>124800324</v>
       </c>
       <c r="B11" t="n">
-        <v>96354</v>
+        <v>91361</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1643,25 +1643,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>2062</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1669,16 +1669,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440721</v>
+        <v>440680</v>
       </c>
       <c r="R11" t="n">
-        <v>7001216</v>
+        <v>7001258</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,6 +1722,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1737,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800319</v>
+        <v>124800321</v>
       </c>
       <c r="B12" t="n">
-        <v>97185</v>
+        <v>91008</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1749,25 +1753,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220686</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1781,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440720</v>
+        <v>440709</v>
       </c>
       <c r="R12" t="n">
-        <v>7001201</v>
+        <v>7001238</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800335</v>
+        <v>124800297</v>
       </c>
       <c r="B13" t="n">
-        <v>78889</v>
+        <v>91026</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1887,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440621</v>
+        <v>440921</v>
       </c>
       <c r="R13" t="n">
-        <v>7001181</v>
+        <v>7001295</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800334</v>
+        <v>124800333</v>
       </c>
       <c r="B14" t="n">
-        <v>77753</v>
+        <v>82597</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1969,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>314</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1993,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440624</v>
+        <v>440628</v>
       </c>
       <c r="R14" t="n">
-        <v>7001080</v>
+        <v>7001081</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,10 +2059,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800323</v>
+        <v>124800327</v>
       </c>
       <c r="B15" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2071,21 +2075,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2099,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440681</v>
+        <v>440672</v>
       </c>
       <c r="R15" t="n">
-        <v>7001285</v>
+        <v>7001361</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,10 +2165,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800302</v>
+        <v>124800309</v>
       </c>
       <c r="B16" t="n">
-        <v>78889</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2177,21 +2181,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2205,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440910</v>
+        <v>440821</v>
       </c>
       <c r="R16" t="n">
-        <v>7001371</v>
+        <v>7001261</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2267,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800333</v>
+        <v>124800331</v>
       </c>
       <c r="B17" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2283,21 +2287,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2311,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440628</v>
+        <v>440637</v>
       </c>
       <c r="R17" t="n">
-        <v>7001081</v>
+        <v>7001171</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800303</v>
+        <v>124800306</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2389,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2417,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440909</v>
+        <v>440872</v>
       </c>
       <c r="R18" t="n">
-        <v>7001374</v>
+        <v>7001384</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800329</v>
+        <v>124800338</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>96776</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2491,25 +2495,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2389</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2523,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440658</v>
+        <v>440604</v>
       </c>
       <c r="R19" t="n">
-        <v>7001354</v>
+        <v>7001240</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2585,10 +2589,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800326</v>
+        <v>124800319</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>97185</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,25 +2601,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220686</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2629,10 +2633,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440672</v>
+        <v>440720</v>
       </c>
       <c r="R20" t="n">
-        <v>7001335</v>
+        <v>7001201</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2691,10 +2695,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800328</v>
+        <v>124800330</v>
       </c>
       <c r="B21" t="n">
-        <v>95335</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,25 +2707,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2735,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440661</v>
+        <v>440646</v>
       </c>
       <c r="R21" t="n">
-        <v>7001244</v>
+        <v>7001158</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,10 +2801,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800306</v>
+        <v>124801009</v>
       </c>
       <c r="B22" t="n">
-        <v>88359</v>
+        <v>94769</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2809,25 +2813,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>2411</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Nordlig källmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Philonotis tomentella</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Molendo</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2841,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440872</v>
+        <v>440900</v>
       </c>
       <c r="R22" t="n">
-        <v>7001384</v>
+        <v>7001371</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2903,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800316</v>
+        <v>124800307</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2919,21 +2923,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2947,10 +2951,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440773</v>
+        <v>440872</v>
       </c>
       <c r="R23" t="n">
-        <v>7001489</v>
+        <v>7001280</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3009,10 +3013,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800300</v>
+        <v>124800334</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>77753</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3025,21 +3029,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3053,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440915</v>
+        <v>440624</v>
       </c>
       <c r="R24" t="n">
-        <v>7001296</v>
+        <v>7001080</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3217,10 +3221,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800313</v>
+        <v>124800293</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3233,21 +3237,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3261,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440791</v>
+        <v>441111</v>
       </c>
       <c r="R26" t="n">
-        <v>7001239</v>
+        <v>7001333</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,10 +3327,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800310</v>
+        <v>124800329</v>
       </c>
       <c r="B27" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3339,21 +3343,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3367,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440799</v>
+        <v>440658</v>
       </c>
       <c r="R27" t="n">
-        <v>7001243</v>
+        <v>7001354</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,10 +3433,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800295</v>
+        <v>124800325</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3445,21 +3449,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3473,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440940</v>
+        <v>440674</v>
       </c>
       <c r="R28" t="n">
-        <v>7001369</v>
+        <v>7001385</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3535,10 +3539,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800338</v>
+        <v>124800322</v>
       </c>
       <c r="B29" t="n">
-        <v>96776</v>
+        <v>91012</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3547,25 +3551,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2389</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3579,10 +3583,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440604</v>
+        <v>440696</v>
       </c>
       <c r="R29" t="n">
-        <v>7001240</v>
+        <v>7001259</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3641,10 +3645,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800304</v>
+        <v>124800332</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>74906</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3657,21 +3661,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3685,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440902</v>
+        <v>440630</v>
       </c>
       <c r="R30" t="n">
-        <v>7001332</v>
+        <v>7001086</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3747,10 +3751,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800327</v>
+        <v>124800335</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3763,21 +3767,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3791,10 +3795,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440672</v>
+        <v>440621</v>
       </c>
       <c r="R31" t="n">
-        <v>7001361</v>
+        <v>7001181</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,10 +3857,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124740889</v>
+        <v>124800314</v>
       </c>
       <c r="B32" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3869,34 +3873,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440684</v>
+        <v>440785</v>
       </c>
       <c r="R32" t="n">
-        <v>7001254</v>
+        <v>7001501</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,10 +3963,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124800311</v>
+        <v>124800299</v>
       </c>
       <c r="B33" t="n">
-        <v>77753</v>
+        <v>78889</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3971,21 +3979,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>314</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3999,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440798</v>
+        <v>440915</v>
       </c>
       <c r="R33" t="n">
-        <v>7001239</v>
+        <v>7001377</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4061,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124800308</v>
+        <v>124800304</v>
       </c>
       <c r="B34" t="n">
-        <v>88359</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4077,21 +4085,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4105,10 +4113,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440850</v>
+        <v>440902</v>
       </c>
       <c r="R34" t="n">
-        <v>7001393</v>
+        <v>7001332</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,10 +4175,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124800324</v>
+        <v>124800305</v>
       </c>
       <c r="B35" t="n">
-        <v>91361</v>
+        <v>91299</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4179,25 +4187,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4205,19 +4213,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440680</v>
+        <v>440874</v>
       </c>
       <c r="R35" t="n">
-        <v>7001258</v>
+        <v>7001281</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4258,7 +4263,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4277,10 +4281,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124800305</v>
+        <v>124800328</v>
       </c>
       <c r="B36" t="n">
-        <v>91299</v>
+        <v>95335</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4289,25 +4293,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4321,10 +4325,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440874</v>
+        <v>440661</v>
       </c>
       <c r="R36" t="n">
-        <v>7001281</v>
+        <v>7001244</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4387,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124800307</v>
+        <v>124800296</v>
       </c>
       <c r="B37" t="n">
         <v>91012</v>
@@ -4427,10 +4431,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440872</v>
+        <v>440939</v>
       </c>
       <c r="R37" t="n">
-        <v>7001280</v>
+        <v>7001309</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4489,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124800294</v>
+        <v>124800323</v>
       </c>
       <c r="B38" t="n">
-        <v>79851</v>
+        <v>74901</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4501,25 +4505,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229497</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4533,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441028</v>
+        <v>440681</v>
       </c>
       <c r="R38" t="n">
-        <v>7001364</v>
+        <v>7001285</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,10 +4599,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124801009</v>
+        <v>124800302</v>
       </c>
       <c r="B39" t="n">
-        <v>94769</v>
+        <v>78889</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4607,25 +4611,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2411</v>
+        <v>864</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nordlig källmossa</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Philonotis tomentella</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Molendo</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4639,7 +4643,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440900</v>
+        <v>440910</v>
       </c>
       <c r="R39" t="n">
         <v>7001371</v>
@@ -4701,10 +4705,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124800314</v>
+        <v>124800315</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4717,21 +4721,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4745,10 +4749,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440785</v>
+        <v>440782</v>
       </c>
       <c r="R40" t="n">
-        <v>7001501</v>
+        <v>7001494</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4775,12 +4779,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4807,10 +4811,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124800296</v>
+        <v>124800308</v>
       </c>
       <c r="B41" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4823,21 +4827,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4851,10 +4855,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440939</v>
+        <v>440850</v>
       </c>
       <c r="R41" t="n">
-        <v>7001309</v>
+        <v>7001393</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4913,10 +4917,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124800331</v>
+        <v>124800340</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4929,21 +4933,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4957,10 +4961,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440637</v>
+        <v>440590</v>
       </c>
       <c r="R42" t="n">
-        <v>7001171</v>
+        <v>7001362</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5019,7 +5023,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124800325</v>
+        <v>124800326</v>
       </c>
       <c r="B43" t="n">
         <v>78810</v>
@@ -5063,10 +5067,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440674</v>
+        <v>440672</v>
       </c>
       <c r="R43" t="n">
-        <v>7001385</v>
+        <v>7001335</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5125,10 +5129,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124800340</v>
+        <v>124800320</v>
       </c>
       <c r="B44" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5141,21 +5145,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5169,10 +5173,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440590</v>
+        <v>440720</v>
       </c>
       <c r="R44" t="n">
-        <v>7001362</v>
+        <v>7001206</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5231,10 +5235,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124800315</v>
+        <v>124800336</v>
       </c>
       <c r="B45" t="n">
-        <v>78889</v>
+        <v>91026</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5247,21 +5251,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5275,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440782</v>
+        <v>440616</v>
       </c>
       <c r="R45" t="n">
-        <v>7001494</v>
+        <v>7001215</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5337,10 +5341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124800309</v>
+        <v>124800318</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>96354</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5353,21 +5357,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5381,10 +5385,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440821</v>
+        <v>440721</v>
       </c>
       <c r="R46" t="n">
-        <v>7001261</v>
+        <v>7001216</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5443,10 +5447,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124800297</v>
+        <v>124740889</v>
       </c>
       <c r="B47" t="n">
-        <v>91026</v>
+        <v>91030</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5459,38 +5463,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440921</v>
+        <v>440684</v>
       </c>
       <c r="R47" t="n">
-        <v>7001295</v>
+        <v>7001254</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5549,10 +5549,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124800332</v>
+        <v>124800295</v>
       </c>
       <c r="B48" t="n">
-        <v>74906</v>
+        <v>91012</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5565,21 +5565,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440630</v>
+        <v>440940</v>
       </c>
       <c r="R48" t="n">
-        <v>7001086</v>
+        <v>7001369</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5655,10 +5655,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124800322</v>
+        <v>124800298</v>
       </c>
       <c r="B49" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440696</v>
+        <v>440916</v>
       </c>
       <c r="R49" t="n">
-        <v>7001259</v>
+        <v>7001320</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -1105,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800310</v>
+        <v>124800303</v>
       </c>
       <c r="B6" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,21 +1121,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440799</v>
+        <v>440909</v>
       </c>
       <c r="R6" t="n">
-        <v>7001243</v>
+        <v>7001374</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800313</v>
+        <v>124800310</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,21 +1227,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440791</v>
+        <v>440799</v>
       </c>
       <c r="R7" t="n">
-        <v>7001239</v>
+        <v>7001243</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800303</v>
+        <v>124800313</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440909</v>
+        <v>440791</v>
       </c>
       <c r="R8" t="n">
-        <v>7001374</v>
+        <v>7001239</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124800323</v>
+        <v>124800302</v>
       </c>
       <c r="B38" t="n">
-        <v>74901</v>
+        <v>78889</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4509,21 +4509,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440681</v>
+        <v>440910</v>
       </c>
       <c r="R38" t="n">
-        <v>7001285</v>
+        <v>7001371</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4599,7 +4599,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124800302</v>
+        <v>124800315</v>
       </c>
       <c r="B39" t="n">
         <v>78889</v>
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440910</v>
+        <v>440782</v>
       </c>
       <c r="R39" t="n">
-        <v>7001371</v>
+        <v>7001494</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4705,10 +4705,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124800315</v>
+        <v>124800323</v>
       </c>
       <c r="B40" t="n">
-        <v>78889</v>
+        <v>74901</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4721,21 +4721,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440782</v>
+        <v>440681</v>
       </c>
       <c r="R40" t="n">
-        <v>7001494</v>
+        <v>7001285</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800316</v>
+        <v>124800309</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440773</v>
+        <v>440821</v>
       </c>
       <c r="R3" t="n">
-        <v>7001489</v>
+        <v>7001261</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800311</v>
+        <v>124800307</v>
       </c>
       <c r="B4" t="n">
-        <v>77753</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>314</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440798</v>
+        <v>440872</v>
       </c>
       <c r="R4" t="n">
-        <v>7001239</v>
+        <v>7001280</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800294</v>
+        <v>124800325</v>
       </c>
       <c r="B5" t="n">
-        <v>79851</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1011,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441028</v>
+        <v>440674</v>
       </c>
       <c r="R5" t="n">
-        <v>7001364</v>
+        <v>7001385</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800303</v>
+        <v>124800321</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,21 +1121,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440909</v>
+        <v>440709</v>
       </c>
       <c r="R6" t="n">
-        <v>7001374</v>
+        <v>7001238</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800310</v>
+        <v>124740889</v>
       </c>
       <c r="B7" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,38 +1227,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440799</v>
+        <v>440684</v>
       </c>
       <c r="R7" t="n">
-        <v>7001243</v>
+        <v>7001254</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,12 +1281,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800313</v>
+        <v>124800300</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1329,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1361,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440791</v>
+        <v>440915</v>
       </c>
       <c r="R8" t="n">
-        <v>7001239</v>
+        <v>7001296</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800300</v>
+        <v>124800320</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1467,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440915</v>
+        <v>440720</v>
       </c>
       <c r="R9" t="n">
-        <v>7001296</v>
+        <v>7001206</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124738082</v>
+        <v>124800295</v>
       </c>
       <c r="B10" t="n">
-        <v>88359</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,34 +1541,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440684</v>
+        <v>440940</v>
       </c>
       <c r="R10" t="n">
-        <v>7001254</v>
+        <v>7001369</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800324</v>
+        <v>124800310</v>
       </c>
       <c r="B11" t="n">
-        <v>91361</v>
+        <v>74901</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1643,25 +1643,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2062</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1669,19 +1669,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440680</v>
+        <v>440799</v>
       </c>
       <c r="R11" t="n">
-        <v>7001258</v>
+        <v>7001243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,7 +1719,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1741,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800321</v>
+        <v>124800314</v>
       </c>
       <c r="B12" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,21 +1753,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1785,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440709</v>
+        <v>440785</v>
       </c>
       <c r="R12" t="n">
-        <v>7001238</v>
+        <v>7001501</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,12 +1811,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800297</v>
+        <v>124800330</v>
       </c>
       <c r="B13" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,21 +1859,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1891,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440921</v>
+        <v>440646</v>
       </c>
       <c r="R13" t="n">
-        <v>7001295</v>
+        <v>7001158</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800333</v>
+        <v>124740817</v>
       </c>
       <c r="B14" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1969,38 +1965,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440628</v>
+        <v>440684</v>
       </c>
       <c r="R14" t="n">
-        <v>7001081</v>
+        <v>7001254</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2027,12 +2019,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2059,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800327</v>
+        <v>124800322</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2075,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2103,10 +2095,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440672</v>
+        <v>440696</v>
       </c>
       <c r="R15" t="n">
-        <v>7001361</v>
+        <v>7001259</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,10 +2157,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800309</v>
+        <v>124800308</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,21 +2173,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2209,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440821</v>
+        <v>440850</v>
       </c>
       <c r="R16" t="n">
-        <v>7001261</v>
+        <v>7001393</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,7 +2263,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800331</v>
+        <v>124800329</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2315,10 +2307,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440637</v>
+        <v>440658</v>
       </c>
       <c r="R17" t="n">
-        <v>7001171</v>
+        <v>7001354</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,10 +2369,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800306</v>
+        <v>124800302</v>
       </c>
       <c r="B18" t="n">
-        <v>88359</v>
+        <v>78889</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,21 +2385,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2421,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440872</v>
+        <v>440910</v>
       </c>
       <c r="R18" t="n">
-        <v>7001384</v>
+        <v>7001371</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800338</v>
+        <v>124800306</v>
       </c>
       <c r="B19" t="n">
-        <v>96776</v>
+        <v>88359</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,25 +2487,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2389</v>
+        <v>510</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2527,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440604</v>
+        <v>440872</v>
       </c>
       <c r="R19" t="n">
-        <v>7001240</v>
+        <v>7001384</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800319</v>
+        <v>124800332</v>
       </c>
       <c r="B20" t="n">
-        <v>97185</v>
+        <v>74906</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2601,25 +2593,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220686</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2633,10 +2625,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440720</v>
+        <v>440630</v>
       </c>
       <c r="R20" t="n">
-        <v>7001201</v>
+        <v>7001086</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800330</v>
+        <v>124800305</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2711,21 +2703,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2739,10 +2731,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440646</v>
+        <v>440874</v>
       </c>
       <c r="R21" t="n">
-        <v>7001158</v>
+        <v>7001281</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2801,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124801009</v>
+        <v>124800340</v>
       </c>
       <c r="B22" t="n">
-        <v>94769</v>
+        <v>74901</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2813,25 +2805,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2411</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordlig källmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Philonotis tomentella</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Molendo</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2845,10 +2837,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440900</v>
+        <v>440590</v>
       </c>
       <c r="R22" t="n">
-        <v>7001371</v>
+        <v>7001362</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,10 +2899,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800307</v>
+        <v>124800335</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>78889</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,21 +2915,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2951,10 +2943,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440872</v>
+        <v>440621</v>
       </c>
       <c r="R23" t="n">
-        <v>7001280</v>
+        <v>7001181</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3013,10 +3005,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800334</v>
+        <v>124800316</v>
       </c>
       <c r="B24" t="n">
-        <v>77753</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3029,21 +3021,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3057,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440624</v>
+        <v>440773</v>
       </c>
       <c r="R24" t="n">
-        <v>7001080</v>
+        <v>7001489</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3119,7 +3111,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124740817</v>
+        <v>124800326</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3152,17 +3144,21 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440684</v>
+        <v>440672</v>
       </c>
       <c r="R25" t="n">
-        <v>7001254</v>
+        <v>7001335</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3189,12 +3185,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3221,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800293</v>
+        <v>124800298</v>
       </c>
       <c r="B26" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3237,21 +3233,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3265,10 +3261,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441111</v>
+        <v>440916</v>
       </c>
       <c r="R26" t="n">
-        <v>7001333</v>
+        <v>7001320</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3327,7 +3323,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800329</v>
+        <v>124800313</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3371,10 +3367,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440658</v>
+        <v>440791</v>
       </c>
       <c r="R27" t="n">
-        <v>7001354</v>
+        <v>7001239</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3433,10 +3429,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800325</v>
+        <v>124800323</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3449,21 +3445,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3477,10 +3473,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440674</v>
+        <v>440681</v>
       </c>
       <c r="R28" t="n">
-        <v>7001385</v>
+        <v>7001285</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3539,10 +3535,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800322</v>
+        <v>124800319</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>97185</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3551,25 +3547,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220686</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3583,10 +3579,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440696</v>
+        <v>440720</v>
       </c>
       <c r="R29" t="n">
-        <v>7001259</v>
+        <v>7001201</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3645,10 +3641,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800332</v>
+        <v>124800303</v>
       </c>
       <c r="B30" t="n">
-        <v>74906</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3661,21 +3657,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3689,10 +3685,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440630</v>
+        <v>440909</v>
       </c>
       <c r="R30" t="n">
-        <v>7001086</v>
+        <v>7001374</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3751,10 +3747,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800335</v>
+        <v>124800311</v>
       </c>
       <c r="B31" t="n">
-        <v>78889</v>
+        <v>77753</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3767,21 +3763,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>864</v>
+        <v>314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3795,10 +3791,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440621</v>
+        <v>440798</v>
       </c>
       <c r="R31" t="n">
-        <v>7001181</v>
+        <v>7001239</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,10 +3853,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124800314</v>
+        <v>124800334</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>77753</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3873,21 +3869,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3901,10 +3897,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440785</v>
+        <v>440624</v>
       </c>
       <c r="R32" t="n">
-        <v>7001501</v>
+        <v>7001080</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3931,12 +3927,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3963,10 +3959,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124800299</v>
+        <v>124800294</v>
       </c>
       <c r="B33" t="n">
-        <v>78889</v>
+        <v>79851</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3975,25 +3971,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>229497</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4007,10 +4003,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440915</v>
+        <v>441028</v>
       </c>
       <c r="R33" t="n">
-        <v>7001377</v>
+        <v>7001364</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4069,10 +4065,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124800304</v>
+        <v>124800318</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>96354</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4085,21 +4081,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4113,10 +4109,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440902</v>
+        <v>440721</v>
       </c>
       <c r="R34" t="n">
-        <v>7001332</v>
+        <v>7001216</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4175,10 +4171,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124800305</v>
+        <v>124801009</v>
       </c>
       <c r="B35" t="n">
-        <v>91299</v>
+        <v>94769</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4187,25 +4183,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>2411</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nordlig källmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Philonotis tomentella</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Molendo</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4219,10 +4215,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440874</v>
+        <v>440900</v>
       </c>
       <c r="R35" t="n">
-        <v>7001281</v>
+        <v>7001371</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4281,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124800328</v>
+        <v>124800333</v>
       </c>
       <c r="B36" t="n">
-        <v>95335</v>
+        <v>82597</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4293,25 +4289,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2809</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4325,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440661</v>
+        <v>440628</v>
       </c>
       <c r="R36" t="n">
-        <v>7001244</v>
+        <v>7001081</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4387,10 +4383,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124800296</v>
+        <v>124800297</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>91026</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4403,21 +4399,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4431,10 +4427,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440939</v>
+        <v>440921</v>
       </c>
       <c r="R37" t="n">
-        <v>7001309</v>
+        <v>7001295</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4493,10 +4489,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124800302</v>
+        <v>124738082</v>
       </c>
       <c r="B38" t="n">
-        <v>78889</v>
+        <v>88359</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4509,38 +4505,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>864</v>
+        <v>510</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440910</v>
+        <v>440684</v>
       </c>
       <c r="R38" t="n">
-        <v>7001371</v>
+        <v>7001254</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4567,12 +4559,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4599,10 +4591,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124800315</v>
+        <v>124800331</v>
       </c>
       <c r="B39" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4615,21 +4607,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4643,10 +4635,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440782</v>
+        <v>440637</v>
       </c>
       <c r="R39" t="n">
-        <v>7001494</v>
+        <v>7001171</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4705,10 +4697,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124800323</v>
+        <v>124800296</v>
       </c>
       <c r="B40" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4721,21 +4713,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4749,10 +4741,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440681</v>
+        <v>440939</v>
       </c>
       <c r="R40" t="n">
-        <v>7001285</v>
+        <v>7001309</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,10 +4803,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124800308</v>
+        <v>124800293</v>
       </c>
       <c r="B41" t="n">
-        <v>88359</v>
+        <v>57529</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4827,21 +4819,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4855,10 +4847,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440850</v>
+        <v>441111</v>
       </c>
       <c r="R41" t="n">
-        <v>7001393</v>
+        <v>7001333</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4917,10 +4909,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124800340</v>
+        <v>124800338</v>
       </c>
       <c r="B42" t="n">
-        <v>74901</v>
+        <v>96776</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4929,25 +4921,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>2389</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4961,10 +4953,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440590</v>
+        <v>440604</v>
       </c>
       <c r="R42" t="n">
-        <v>7001362</v>
+        <v>7001240</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5023,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124800326</v>
+        <v>124800328</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>95335</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5035,25 +5027,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5067,10 +5059,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440672</v>
+        <v>440661</v>
       </c>
       <c r="R43" t="n">
-        <v>7001335</v>
+        <v>7001244</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5129,10 +5121,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124800320</v>
+        <v>124800299</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5145,21 +5137,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5173,10 +5165,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440720</v>
+        <v>440915</v>
       </c>
       <c r="R44" t="n">
-        <v>7001206</v>
+        <v>7001377</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5235,10 +5227,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124800336</v>
+        <v>124800327</v>
       </c>
       <c r="B45" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5251,21 +5243,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5279,10 +5271,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440616</v>
+        <v>440672</v>
       </c>
       <c r="R45" t="n">
-        <v>7001215</v>
+        <v>7001361</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,10 +5333,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124800318</v>
+        <v>124800315</v>
       </c>
       <c r="B46" t="n">
-        <v>96354</v>
+        <v>78889</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5357,21 +5349,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>864</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5385,10 +5377,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440721</v>
+        <v>440782</v>
       </c>
       <c r="R46" t="n">
-        <v>7001216</v>
+        <v>7001494</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5447,10 +5439,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124740889</v>
+        <v>124800304</v>
       </c>
       <c r="B47" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5463,34 +5455,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440684</v>
+        <v>440902</v>
       </c>
       <c r="R47" t="n">
-        <v>7001254</v>
+        <v>7001332</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5517,12 +5513,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5549,10 +5545,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124800295</v>
+        <v>124800336</v>
       </c>
       <c r="B48" t="n">
-        <v>91012</v>
+        <v>91026</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5565,21 +5561,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5593,10 +5589,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440940</v>
+        <v>440616</v>
       </c>
       <c r="R48" t="n">
-        <v>7001369</v>
+        <v>7001215</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5655,10 +5651,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124800298</v>
+        <v>124800324</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>91361</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5667,25 +5663,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5693,16 +5689,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440916</v>
+        <v>440680</v>
       </c>
       <c r="R49" t="n">
-        <v>7001320</v>
+        <v>7001258</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5743,6 +5742,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800309</v>
+        <v>124740889</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>91184</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,38 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440821</v>
+        <v>440684</v>
       </c>
       <c r="R3" t="n">
-        <v>7001261</v>
+        <v>7001254</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800307</v>
+        <v>124800318</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>96522</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440872</v>
+        <v>440721</v>
       </c>
       <c r="R4" t="n">
-        <v>7001280</v>
+        <v>7001216</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800325</v>
+        <v>124800299</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>79026</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1043,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440674</v>
+        <v>440915</v>
       </c>
       <c r="R5" t="n">
-        <v>7001385</v>
+        <v>7001377</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800321</v>
+        <v>124800326</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>78947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1149,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440709</v>
+        <v>440672</v>
       </c>
       <c r="R6" t="n">
-        <v>7001238</v>
+        <v>7001335</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124740889</v>
+        <v>124800297</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>91180</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,34 +1223,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440684</v>
+        <v>440921</v>
       </c>
       <c r="R7" t="n">
-        <v>7001254</v>
+        <v>7001295</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800300</v>
+        <v>124800296</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>91166</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,21 +1329,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440915</v>
+        <v>440939</v>
       </c>
       <c r="R8" t="n">
-        <v>7001296</v>
+        <v>7001309</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800320</v>
+        <v>124800313</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440720</v>
+        <v>440791</v>
       </c>
       <c r="R9" t="n">
-        <v>7001206</v>
+        <v>7001239</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800295</v>
+        <v>124800333</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>82737</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,21 +1541,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440940</v>
+        <v>440628</v>
       </c>
       <c r="R10" t="n">
-        <v>7001369</v>
+        <v>7001081</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800310</v>
+        <v>124800307</v>
       </c>
       <c r="B11" t="n">
-        <v>74901</v>
+        <v>91166</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,21 +1647,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440799</v>
+        <v>440872</v>
       </c>
       <c r="R11" t="n">
-        <v>7001243</v>
+        <v>7001280</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800314</v>
+        <v>124800328</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>95503</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1749,25 +1749,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440785</v>
+        <v>440661</v>
       </c>
       <c r="R12" t="n">
-        <v>7001501</v>
+        <v>7001244</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800330</v>
+        <v>124800338</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>96944</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,25 +1855,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2389</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440646</v>
+        <v>440604</v>
       </c>
       <c r="R13" t="n">
-        <v>7001158</v>
+        <v>7001240</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124740817</v>
+        <v>124800319</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>97353</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1961,38 +1961,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220686</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440684</v>
+        <v>440720</v>
       </c>
       <c r="R14" t="n">
-        <v>7001254</v>
+        <v>7001201</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,12 +2023,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800322</v>
+        <v>124800306</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>88512</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,21 +2071,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2095,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440696</v>
+        <v>440872</v>
       </c>
       <c r="R15" t="n">
-        <v>7001259</v>
+        <v>7001384</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800308</v>
+        <v>124738082</v>
       </c>
       <c r="B16" t="n">
-        <v>88359</v>
+        <v>88512</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2190,21 +2194,17 @@
           <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440850</v>
+        <v>440684</v>
       </c>
       <c r="R16" t="n">
-        <v>7001393</v>
+        <v>7001254</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2231,12 +2231,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,10 +2263,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800329</v>
+        <v>124800311</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>77889</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2279,21 +2279,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440658</v>
+        <v>440798</v>
       </c>
       <c r="R17" t="n">
-        <v>7001354</v>
+        <v>7001239</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,10 +2369,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800302</v>
+        <v>124800298</v>
       </c>
       <c r="B18" t="n">
-        <v>78889</v>
+        <v>78947</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2385,21 +2385,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440910</v>
+        <v>440916</v>
       </c>
       <c r="R18" t="n">
-        <v>7001371</v>
+        <v>7001320</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2475,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800306</v>
+        <v>124800304</v>
       </c>
       <c r="B19" t="n">
-        <v>88359</v>
+        <v>91166</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2491,21 +2491,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440872</v>
+        <v>440902</v>
       </c>
       <c r="R19" t="n">
-        <v>7001384</v>
+        <v>7001332</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2581,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800332</v>
+        <v>124800310</v>
       </c>
       <c r="B20" t="n">
-        <v>74906</v>
+        <v>75025</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,21 +2597,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440630</v>
+        <v>440799</v>
       </c>
       <c r="R20" t="n">
-        <v>7001086</v>
+        <v>7001243</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800305</v>
+        <v>124800315</v>
       </c>
       <c r="B21" t="n">
-        <v>91299</v>
+        <v>79026</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,21 +2703,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440874</v>
+        <v>440782</v>
       </c>
       <c r="R21" t="n">
-        <v>7001281</v>
+        <v>7001494</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800340</v>
+        <v>124800325</v>
       </c>
       <c r="B22" t="n">
-        <v>74901</v>
+        <v>78947</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2809,21 +2809,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440590</v>
+        <v>440674</v>
       </c>
       <c r="R22" t="n">
-        <v>7001362</v>
+        <v>7001385</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800335</v>
+        <v>124801009</v>
       </c>
       <c r="B23" t="n">
-        <v>78889</v>
+        <v>94937</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2911,25 +2911,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>864</v>
+        <v>2411</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Nordlig källmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Philonotis tomentella</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Molendo</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440621</v>
+        <v>440900</v>
       </c>
       <c r="R23" t="n">
-        <v>7001181</v>
+        <v>7001371</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,10 +3005,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800316</v>
+        <v>124800322</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>91166</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3021,21 +3021,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440773</v>
+        <v>440696</v>
       </c>
       <c r="R24" t="n">
-        <v>7001489</v>
+        <v>7001259</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800326</v>
+        <v>124800316</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440672</v>
+        <v>440773</v>
       </c>
       <c r="R25" t="n">
-        <v>7001335</v>
+        <v>7001489</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800298</v>
+        <v>124800303</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440916</v>
+        <v>440909</v>
       </c>
       <c r="R26" t="n">
-        <v>7001320</v>
+        <v>7001374</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,10 +3323,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800313</v>
+        <v>124800320</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440791</v>
+        <v>440720</v>
       </c>
       <c r="R27" t="n">
-        <v>7001239</v>
+        <v>7001206</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800323</v>
+        <v>124800293</v>
       </c>
       <c r="B28" t="n">
-        <v>74901</v>
+        <v>57632</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3445,21 +3445,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440681</v>
+        <v>441111</v>
       </c>
       <c r="R28" t="n">
-        <v>7001285</v>
+        <v>7001333</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800319</v>
+        <v>124800324</v>
       </c>
       <c r="B29" t="n">
-        <v>97185</v>
+        <v>91521</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3547,25 +3547,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220686</v>
+        <v>2062</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3573,16 +3573,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440720</v>
+        <v>440680</v>
       </c>
       <c r="R29" t="n">
-        <v>7001201</v>
+        <v>7001258</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3623,6 +3626,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3641,10 +3645,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800303</v>
+        <v>124800323</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>75025</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3657,21 +3661,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3685,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440909</v>
+        <v>440681</v>
       </c>
       <c r="R30" t="n">
-        <v>7001374</v>
+        <v>7001285</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3747,10 +3751,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800311</v>
+        <v>124800340</v>
       </c>
       <c r="B31" t="n">
-        <v>77753</v>
+        <v>75025</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3763,21 +3767,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>314</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3791,10 +3795,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440798</v>
+        <v>440590</v>
       </c>
       <c r="R31" t="n">
-        <v>7001239</v>
+        <v>7001362</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,10 +3857,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124800334</v>
+        <v>124800331</v>
       </c>
       <c r="B32" t="n">
-        <v>77753</v>
+        <v>78947</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3869,21 +3873,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3897,10 +3901,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440624</v>
+        <v>440637</v>
       </c>
       <c r="R32" t="n">
-        <v>7001080</v>
+        <v>7001171</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3959,10 +3963,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124800294</v>
+        <v>124800308</v>
       </c>
       <c r="B33" t="n">
-        <v>79851</v>
+        <v>88512</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3971,25 +3975,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229497</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4003,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441028</v>
+        <v>440850</v>
       </c>
       <c r="R33" t="n">
-        <v>7001364</v>
+        <v>7001393</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4065,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124800318</v>
+        <v>124800305</v>
       </c>
       <c r="B34" t="n">
-        <v>96354</v>
+        <v>91459</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4081,21 +4085,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4109,10 +4113,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440721</v>
+        <v>440874</v>
       </c>
       <c r="R34" t="n">
-        <v>7001216</v>
+        <v>7001281</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4171,10 +4175,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124801009</v>
+        <v>124800294</v>
       </c>
       <c r="B35" t="n">
-        <v>94769</v>
+        <v>79988</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4187,21 +4191,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2411</v>
+        <v>229497</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nordlig källmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Philonotis tomentella</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Molendo</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4215,10 +4219,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440900</v>
+        <v>441028</v>
       </c>
       <c r="R35" t="n">
-        <v>7001371</v>
+        <v>7001364</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4277,10 +4281,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124800333</v>
+        <v>124800309</v>
       </c>
       <c r="B36" t="n">
-        <v>82597</v>
+        <v>91166</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4293,21 +4297,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4321,10 +4325,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440628</v>
+        <v>440821</v>
       </c>
       <c r="R36" t="n">
-        <v>7001081</v>
+        <v>7001261</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,10 +4387,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124800297</v>
+        <v>124800300</v>
       </c>
       <c r="B37" t="n">
-        <v>91026</v>
+        <v>91184</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4399,21 +4403,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4427,10 +4431,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440921</v>
+        <v>440915</v>
       </c>
       <c r="R37" t="n">
-        <v>7001295</v>
+        <v>7001296</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4489,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124738082</v>
+        <v>124800330</v>
       </c>
       <c r="B38" t="n">
-        <v>88359</v>
+        <v>78947</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4505,34 +4509,38 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440684</v>
+        <v>440646</v>
       </c>
       <c r="R38" t="n">
-        <v>7001254</v>
+        <v>7001158</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4559,12 +4567,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4591,10 +4599,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124800331</v>
+        <v>124800295</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>91166</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4607,21 +4615,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4635,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440637</v>
+        <v>440940</v>
       </c>
       <c r="R39" t="n">
-        <v>7001171</v>
+        <v>7001369</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4697,10 +4705,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124800296</v>
+        <v>124800321</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>91162</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4713,21 +4721,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4741,10 +4749,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440939</v>
+        <v>440709</v>
       </c>
       <c r="R40" t="n">
-        <v>7001309</v>
+        <v>7001238</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4803,10 +4811,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124800293</v>
+        <v>124800335</v>
       </c>
       <c r="B41" t="n">
-        <v>57529</v>
+        <v>79026</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4819,21 +4827,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>864</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4847,10 +4855,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>441111</v>
+        <v>440621</v>
       </c>
       <c r="R41" t="n">
-        <v>7001333</v>
+        <v>7001181</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4909,10 +4917,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124800338</v>
+        <v>124800332</v>
       </c>
       <c r="B42" t="n">
-        <v>96776</v>
+        <v>75030</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4921,25 +4929,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2389</v>
+        <v>1467</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4953,10 +4961,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440604</v>
+        <v>440630</v>
       </c>
       <c r="R42" t="n">
-        <v>7001240</v>
+        <v>7001086</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5015,10 +5023,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124800328</v>
+        <v>124800314</v>
       </c>
       <c r="B43" t="n">
-        <v>95335</v>
+        <v>78947</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5027,25 +5035,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5059,10 +5067,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440661</v>
+        <v>440785</v>
       </c>
       <c r="R43" t="n">
-        <v>7001244</v>
+        <v>7001501</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5089,12 +5097,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5121,10 +5129,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124800299</v>
+        <v>124800334</v>
       </c>
       <c r="B44" t="n">
-        <v>78889</v>
+        <v>77889</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5137,21 +5145,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>864</v>
+        <v>314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5165,10 +5173,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440915</v>
+        <v>440624</v>
       </c>
       <c r="R44" t="n">
-        <v>7001377</v>
+        <v>7001080</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5227,10 +5235,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124800327</v>
+        <v>124800302</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>79026</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5243,21 +5251,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5271,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440672</v>
+        <v>440910</v>
       </c>
       <c r="R45" t="n">
-        <v>7001361</v>
+        <v>7001371</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5333,10 +5341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124800315</v>
+        <v>124740817</v>
       </c>
       <c r="B46" t="n">
-        <v>78889</v>
+        <v>78947</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5349,38 +5357,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440782</v>
+        <v>440684</v>
       </c>
       <c r="R46" t="n">
-        <v>7001494</v>
+        <v>7001254</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5407,12 +5411,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5439,10 +5443,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124800304</v>
+        <v>124800329</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5455,21 +5459,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5483,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440902</v>
+        <v>440658</v>
       </c>
       <c r="R47" t="n">
-        <v>7001332</v>
+        <v>7001354</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5548,7 +5552,7 @@
         <v>124800336</v>
       </c>
       <c r="B48" t="n">
-        <v>91026</v>
+        <v>91180</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5651,10 +5655,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124800324</v>
+        <v>124800327</v>
       </c>
       <c r="B49" t="n">
-        <v>91361</v>
+        <v>78947</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5663,25 +5667,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5689,19 +5693,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440680</v>
+        <v>440672</v>
       </c>
       <c r="R49" t="n">
-        <v>7001258</v>
+        <v>7001361</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5742,7 +5743,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -3645,10 +3645,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800323</v>
+        <v>124800308</v>
       </c>
       <c r="B30" t="n">
-        <v>75025</v>
+        <v>88512</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3661,21 +3661,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440681</v>
+        <v>440850</v>
       </c>
       <c r="R30" t="n">
-        <v>7001285</v>
+        <v>7001393</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3751,7 +3751,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800340</v>
+        <v>124800323</v>
       </c>
       <c r="B31" t="n">
         <v>75025</v>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440590</v>
+        <v>440681</v>
       </c>
       <c r="R31" t="n">
-        <v>7001362</v>
+        <v>7001285</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,10 +3857,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124800331</v>
+        <v>124800340</v>
       </c>
       <c r="B32" t="n">
-        <v>78947</v>
+        <v>75025</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3873,21 +3873,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440637</v>
+        <v>440590</v>
       </c>
       <c r="R32" t="n">
-        <v>7001171</v>
+        <v>7001362</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124800308</v>
+        <v>124800331</v>
       </c>
       <c r="B33" t="n">
-        <v>88512</v>
+        <v>78947</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3979,21 +3979,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440850</v>
+        <v>440637</v>
       </c>
       <c r="R33" t="n">
-        <v>7001393</v>
+        <v>7001171</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124740889</v>
+        <v>124800319</v>
       </c>
       <c r="B3" t="n">
-        <v>91184</v>
+        <v>97353</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440684</v>
+        <v>440720</v>
       </c>
       <c r="R3" t="n">
-        <v>7001254</v>
+        <v>7001201</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,12 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800318</v>
+        <v>124800306</v>
       </c>
       <c r="B4" t="n">
-        <v>96522</v>
+        <v>88512</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -933,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440721</v>
+        <v>440872</v>
       </c>
       <c r="R4" t="n">
-        <v>7001216</v>
+        <v>7001384</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800299</v>
+        <v>124800295</v>
       </c>
       <c r="B5" t="n">
-        <v>79026</v>
+        <v>91166</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1039,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440915</v>
+        <v>440940</v>
       </c>
       <c r="R5" t="n">
-        <v>7001377</v>
+        <v>7001369</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800326</v>
+        <v>124800308</v>
       </c>
       <c r="B6" t="n">
-        <v>78947</v>
+        <v>88512</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1121,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1145,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440672</v>
+        <v>440850</v>
       </c>
       <c r="R6" t="n">
-        <v>7001335</v>
+        <v>7001393</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800297</v>
+        <v>124800333</v>
       </c>
       <c r="B7" t="n">
-        <v>91180</v>
+        <v>82737</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,21 +1227,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1251,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440921</v>
+        <v>440628</v>
       </c>
       <c r="R7" t="n">
-        <v>7001295</v>
+        <v>7001081</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800296</v>
+        <v>124800305</v>
       </c>
       <c r="B8" t="n">
-        <v>91166</v>
+        <v>91459</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1357,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440939</v>
+        <v>440874</v>
       </c>
       <c r="R8" t="n">
-        <v>7001309</v>
+        <v>7001281</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800313</v>
+        <v>124800318</v>
       </c>
       <c r="B9" t="n">
-        <v>78947</v>
+        <v>96522</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1439,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1463,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440791</v>
+        <v>440721</v>
       </c>
       <c r="R9" t="n">
-        <v>7001239</v>
+        <v>7001216</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800333</v>
+        <v>124801009</v>
       </c>
       <c r="B10" t="n">
-        <v>82737</v>
+        <v>94937</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,25 +1541,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>2411</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nordlig källmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Philonotis tomentella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Molendo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1569,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440628</v>
+        <v>440900</v>
       </c>
       <c r="R10" t="n">
-        <v>7001081</v>
+        <v>7001371</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,10 +1635,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800307</v>
+        <v>124800299</v>
       </c>
       <c r="B11" t="n">
-        <v>91166</v>
+        <v>79026</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,21 +1651,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1675,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440872</v>
+        <v>440915</v>
       </c>
       <c r="R11" t="n">
-        <v>7001280</v>
+        <v>7001377</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800328</v>
+        <v>124800334</v>
       </c>
       <c r="B12" t="n">
-        <v>95503</v>
+        <v>77889</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1749,25 +1753,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1781,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440661</v>
+        <v>440624</v>
       </c>
       <c r="R12" t="n">
-        <v>7001244</v>
+        <v>7001080</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800338</v>
+        <v>124800326</v>
       </c>
       <c r="B13" t="n">
-        <v>96944</v>
+        <v>78947</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,25 +1859,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2389</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1887,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440604</v>
+        <v>440672</v>
       </c>
       <c r="R13" t="n">
-        <v>7001240</v>
+        <v>7001335</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800319</v>
+        <v>124800310</v>
       </c>
       <c r="B14" t="n">
-        <v>97353</v>
+        <v>75025</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1961,25 +1965,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220686</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1993,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440720</v>
+        <v>440799</v>
       </c>
       <c r="R14" t="n">
-        <v>7001201</v>
+        <v>7001243</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,10 +2059,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800306</v>
+        <v>124800296</v>
       </c>
       <c r="B15" t="n">
-        <v>88512</v>
+        <v>91166</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2071,21 +2075,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2099,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440872</v>
+        <v>440939</v>
       </c>
       <c r="R15" t="n">
-        <v>7001384</v>
+        <v>7001309</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,10 +2165,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124738082</v>
+        <v>124800322</v>
       </c>
       <c r="B16" t="n">
-        <v>88512</v>
+        <v>91166</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2177,34 +2181,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440684</v>
+        <v>440696</v>
       </c>
       <c r="R16" t="n">
-        <v>7001254</v>
+        <v>7001259</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2231,12 +2239,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800311</v>
+        <v>124800315</v>
       </c>
       <c r="B17" t="n">
-        <v>77889</v>
+        <v>79026</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2279,21 +2287,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>314</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2307,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440798</v>
+        <v>440782</v>
       </c>
       <c r="R17" t="n">
-        <v>7001239</v>
+        <v>7001494</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800298</v>
+        <v>124800324</v>
       </c>
       <c r="B18" t="n">
-        <v>78947</v>
+        <v>91521</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2381,25 +2389,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2407,16 +2415,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440916</v>
+        <v>440680</v>
       </c>
       <c r="R18" t="n">
-        <v>7001320</v>
+        <v>7001258</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,6 +2468,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2475,10 +2487,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800304</v>
+        <v>124800328</v>
       </c>
       <c r="B19" t="n">
-        <v>91166</v>
+        <v>95503</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2487,25 +2499,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2519,10 +2531,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440902</v>
+        <v>440661</v>
       </c>
       <c r="R19" t="n">
-        <v>7001332</v>
+        <v>7001244</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2581,10 +2593,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800310</v>
+        <v>124800330</v>
       </c>
       <c r="B20" t="n">
-        <v>75025</v>
+        <v>78947</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,21 +2609,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2625,10 +2637,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440799</v>
+        <v>440646</v>
       </c>
       <c r="R20" t="n">
-        <v>7001243</v>
+        <v>7001158</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2687,10 +2699,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800315</v>
+        <v>124800293</v>
       </c>
       <c r="B21" t="n">
-        <v>79026</v>
+        <v>57632</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,21 +2715,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2731,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440782</v>
+        <v>441111</v>
       </c>
       <c r="R21" t="n">
-        <v>7001494</v>
+        <v>7001333</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800325</v>
+        <v>124800303</v>
       </c>
       <c r="B22" t="n">
         <v>78947</v>
@@ -2837,10 +2849,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440674</v>
+        <v>440909</v>
       </c>
       <c r="R22" t="n">
-        <v>7001385</v>
+        <v>7001374</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2899,10 +2911,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124801009</v>
+        <v>124800323</v>
       </c>
       <c r="B23" t="n">
-        <v>94937</v>
+        <v>75025</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2911,25 +2923,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2411</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordlig källmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Philonotis tomentella</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Molendo</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2943,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440900</v>
+        <v>440681</v>
       </c>
       <c r="R23" t="n">
-        <v>7001371</v>
+        <v>7001285</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,10 +3017,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800322</v>
+        <v>124800340</v>
       </c>
       <c r="B24" t="n">
-        <v>91166</v>
+        <v>75025</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3021,21 +3033,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3049,10 +3061,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440696</v>
+        <v>440590</v>
       </c>
       <c r="R24" t="n">
-        <v>7001259</v>
+        <v>7001362</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,7 +3123,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800316</v>
+        <v>124800327</v>
       </c>
       <c r="B25" t="n">
         <v>78947</v>
@@ -3155,10 +3167,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440773</v>
+        <v>440672</v>
       </c>
       <c r="R25" t="n">
-        <v>7001489</v>
+        <v>7001361</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3217,7 +3229,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800303</v>
+        <v>124800320</v>
       </c>
       <c r="B26" t="n">
         <v>78947</v>
@@ -3261,10 +3273,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440909</v>
+        <v>440720</v>
       </c>
       <c r="R26" t="n">
-        <v>7001374</v>
+        <v>7001206</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800320</v>
+        <v>124800321</v>
       </c>
       <c r="B27" t="n">
-        <v>78947</v>
+        <v>91162</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3339,21 +3351,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3367,10 +3379,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440720</v>
+        <v>440709</v>
       </c>
       <c r="R27" t="n">
-        <v>7001206</v>
+        <v>7001238</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,10 +3441,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800293</v>
+        <v>124740817</v>
       </c>
       <c r="B28" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3445,38 +3457,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441111</v>
+        <v>440684</v>
       </c>
       <c r="R28" t="n">
-        <v>7001333</v>
+        <v>7001254</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3503,12 +3511,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3535,10 +3543,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800324</v>
+        <v>124800332</v>
       </c>
       <c r="B29" t="n">
-        <v>91521</v>
+        <v>75030</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3547,25 +3555,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2062</v>
+        <v>1467</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3573,19 +3581,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440680</v>
+        <v>440630</v>
       </c>
       <c r="R29" t="n">
-        <v>7001258</v>
+        <v>7001086</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3626,7 +3631,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3645,10 +3649,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800308</v>
+        <v>124800304</v>
       </c>
       <c r="B30" t="n">
-        <v>88512</v>
+        <v>91166</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3661,21 +3665,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3689,10 +3693,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440850</v>
+        <v>440902</v>
       </c>
       <c r="R30" t="n">
-        <v>7001393</v>
+        <v>7001332</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3751,10 +3755,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800323</v>
+        <v>124800300</v>
       </c>
       <c r="B31" t="n">
-        <v>75025</v>
+        <v>91184</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3767,21 +3771,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3795,10 +3799,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440681</v>
+        <v>440915</v>
       </c>
       <c r="R31" t="n">
-        <v>7001285</v>
+        <v>7001296</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,10 +3861,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124800340</v>
+        <v>124800311</v>
       </c>
       <c r="B32" t="n">
-        <v>75025</v>
+        <v>77889</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3873,21 +3877,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3901,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440590</v>
+        <v>440798</v>
       </c>
       <c r="R32" t="n">
-        <v>7001362</v>
+        <v>7001239</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3963,10 +3967,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124800331</v>
+        <v>124800294</v>
       </c>
       <c r="B33" t="n">
-        <v>78947</v>
+        <v>79988</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3975,25 +3979,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4007,10 +4011,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440637</v>
+        <v>441028</v>
       </c>
       <c r="R33" t="n">
-        <v>7001171</v>
+        <v>7001364</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4069,10 +4073,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124800305</v>
+        <v>124738082</v>
       </c>
       <c r="B34" t="n">
-        <v>91459</v>
+        <v>88512</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4085,38 +4089,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440874</v>
+        <v>440684</v>
       </c>
       <c r="R34" t="n">
-        <v>7001281</v>
+        <v>7001254</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4175,10 +4175,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124800294</v>
+        <v>124800302</v>
       </c>
       <c r="B35" t="n">
-        <v>79988</v>
+        <v>79026</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4187,25 +4187,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229497</v>
+        <v>864</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>441028</v>
+        <v>440910</v>
       </c>
       <c r="R35" t="n">
-        <v>7001364</v>
+        <v>7001371</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124800309</v>
+        <v>124800335</v>
       </c>
       <c r="B36" t="n">
-        <v>91166</v>
+        <v>79026</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4297,21 +4297,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440821</v>
+        <v>440621</v>
       </c>
       <c r="R36" t="n">
-        <v>7001261</v>
+        <v>7001181</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4387,7 +4387,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124800300</v>
+        <v>124740889</v>
       </c>
       <c r="B37" t="n">
         <v>91184</v>
@@ -4420,21 +4420,17 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440915</v>
+        <v>440684</v>
       </c>
       <c r="R37" t="n">
-        <v>7001296</v>
+        <v>7001254</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4461,12 +4457,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4493,7 +4489,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124800330</v>
+        <v>124800298</v>
       </c>
       <c r="B38" t="n">
         <v>78947</v>
@@ -4537,10 +4533,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440646</v>
+        <v>440916</v>
       </c>
       <c r="R38" t="n">
-        <v>7001158</v>
+        <v>7001320</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4599,10 +4595,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124800295</v>
+        <v>124800325</v>
       </c>
       <c r="B39" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4615,21 +4611,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4643,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440940</v>
+        <v>440674</v>
       </c>
       <c r="R39" t="n">
-        <v>7001369</v>
+        <v>7001385</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4705,10 +4701,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124800321</v>
+        <v>124800329</v>
       </c>
       <c r="B40" t="n">
-        <v>91162</v>
+        <v>78947</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4721,21 +4717,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4749,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440709</v>
+        <v>440658</v>
       </c>
       <c r="R40" t="n">
-        <v>7001238</v>
+        <v>7001354</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,10 +4807,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124800335</v>
+        <v>124800309</v>
       </c>
       <c r="B41" t="n">
-        <v>79026</v>
+        <v>91166</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4827,21 +4823,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4855,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440621</v>
+        <v>440821</v>
       </c>
       <c r="R41" t="n">
-        <v>7001181</v>
+        <v>7001261</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4917,10 +4913,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124800332</v>
+        <v>124800307</v>
       </c>
       <c r="B42" t="n">
-        <v>75030</v>
+        <v>91166</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4933,21 +4929,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4961,10 +4957,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440630</v>
+        <v>440872</v>
       </c>
       <c r="R42" t="n">
-        <v>7001086</v>
+        <v>7001280</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5023,7 +5019,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124800314</v>
+        <v>124800316</v>
       </c>
       <c r="B43" t="n">
         <v>78947</v>
@@ -5067,10 +5063,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440785</v>
+        <v>440773</v>
       </c>
       <c r="R43" t="n">
-        <v>7001501</v>
+        <v>7001489</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5097,12 +5093,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5129,10 +5125,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124800334</v>
+        <v>124800338</v>
       </c>
       <c r="B44" t="n">
-        <v>77889</v>
+        <v>96944</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5141,25 +5137,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>314</v>
+        <v>2389</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5173,10 +5169,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440624</v>
+        <v>440604</v>
       </c>
       <c r="R44" t="n">
-        <v>7001080</v>
+        <v>7001240</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5235,10 +5231,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124800302</v>
+        <v>124800313</v>
       </c>
       <c r="B45" t="n">
-        <v>79026</v>
+        <v>78947</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5251,21 +5247,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5279,10 +5275,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440910</v>
+        <v>440791</v>
       </c>
       <c r="R45" t="n">
-        <v>7001371</v>
+        <v>7001239</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,7 +5337,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124740817</v>
+        <v>124800314</v>
       </c>
       <c r="B46" t="n">
         <v>78947</v>
@@ -5374,17 +5370,21 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440684</v>
+        <v>440785</v>
       </c>
       <c r="R46" t="n">
-        <v>7001254</v>
+        <v>7001501</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124800329</v>
+        <v>124800297</v>
       </c>
       <c r="B47" t="n">
-        <v>78947</v>
+        <v>91180</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440658</v>
+        <v>440921</v>
       </c>
       <c r="R47" t="n">
-        <v>7001354</v>
+        <v>7001295</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5655,7 +5655,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124800327</v>
+        <v>124800331</v>
       </c>
       <c r="B49" t="n">
         <v>78947</v>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440672</v>
+        <v>440637</v>
       </c>
       <c r="R49" t="n">
-        <v>7001361</v>
+        <v>7001171</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -3755,10 +3755,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800300</v>
+        <v>124800294</v>
       </c>
       <c r="B31" t="n">
-        <v>91184</v>
+        <v>79988</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3767,25 +3767,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440915</v>
+        <v>441028</v>
       </c>
       <c r="R31" t="n">
-        <v>7001296</v>
+        <v>7001364</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124800311</v>
+        <v>124800300</v>
       </c>
       <c r="B32" t="n">
-        <v>77889</v>
+        <v>91184</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3877,21 +3877,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>314</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440798</v>
+        <v>440915</v>
       </c>
       <c r="R32" t="n">
-        <v>7001239</v>
+        <v>7001296</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124800294</v>
+        <v>124800311</v>
       </c>
       <c r="B33" t="n">
-        <v>79988</v>
+        <v>77889</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3979,25 +3979,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229497</v>
+        <v>314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4011,10 +4011,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441028</v>
+        <v>440798</v>
       </c>
       <c r="R33" t="n">
-        <v>7001364</v>
+        <v>7001239</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120752406</v>
+        <v>124800318</v>
       </c>
       <c r="B2" t="n">
-        <v>90731</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>MD6:Åre, SE-JA, SE, Jmt</t>
+          <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440718</v>
+        <v>440721</v>
       </c>
       <c r="R2" t="n">
-        <v>7001489</v>
+        <v>7001216</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:41</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:41</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,49 +764,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800319</v>
+        <v>124800311</v>
       </c>
       <c r="B3" t="n">
-        <v>97353</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440720</v>
+        <v>440798</v>
       </c>
       <c r="R3" t="n">
-        <v>7001201</v>
+        <v>7001239</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800306</v>
+        <v>124800334</v>
       </c>
       <c r="B4" t="n">
-        <v>88512</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440872</v>
+        <v>440624</v>
       </c>
       <c r="R4" t="n">
-        <v>7001384</v>
+        <v>7001080</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800295</v>
+        <v>124738082</v>
       </c>
       <c r="B5" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,38 +989,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440940</v>
+        <v>440684</v>
       </c>
       <c r="R5" t="n">
-        <v>7001369</v>
+        <v>7001254</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,12 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,15 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800308</v>
+        <v>124800306</v>
       </c>
       <c r="B6" t="n">
-        <v>88512</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440850</v>
+        <v>440872</v>
       </c>
       <c r="R6" t="n">
-        <v>7001393</v>
+        <v>7001384</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,15 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800333</v>
+        <v>124800308</v>
       </c>
       <c r="B7" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1255,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440628</v>
+        <v>440850</v>
       </c>
       <c r="R7" t="n">
-        <v>7001081</v>
+        <v>7001393</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,12 +1280,7 @@
         <v>124800305</v>
       </c>
       <c r="B8" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1342,12 +1297,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1423,15 +1378,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800318</v>
+        <v>124800299</v>
       </c>
       <c r="B9" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1439,21 +1389,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1467,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440721</v>
+        <v>440915</v>
       </c>
       <c r="R9" t="n">
-        <v>7001216</v>
+        <v>7001377</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,37 +1479,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124801009</v>
+        <v>124800302</v>
       </c>
       <c r="B10" t="n">
-        <v>94937</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2411</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordlig källmossa</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Philonotis tomentella</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Molendo</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1573,7 +1518,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440900</v>
+        <v>440910</v>
       </c>
       <c r="R10" t="n">
         <v>7001371</v>
@@ -1635,15 +1580,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800299</v>
+        <v>124800315</v>
       </c>
       <c r="B11" t="n">
-        <v>79026</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1679,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440915</v>
+        <v>440782</v>
       </c>
       <c r="R11" t="n">
-        <v>7001377</v>
+        <v>7001494</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,15 +1681,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800334</v>
+        <v>124800335</v>
       </c>
       <c r="B12" t="n">
-        <v>77889</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,21 +1692,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>314</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1785,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440624</v>
+        <v>440621</v>
       </c>
       <c r="R12" t="n">
-        <v>7001080</v>
+        <v>7001181</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,15 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800326</v>
+        <v>124800321</v>
       </c>
       <c r="B13" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1891,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440672</v>
+        <v>440709</v>
       </c>
       <c r="R13" t="n">
-        <v>7001335</v>
+        <v>7001238</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,15 +1883,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800310</v>
+        <v>124800295</v>
       </c>
       <c r="B14" t="n">
-        <v>75025</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,21 +1894,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1997,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440799</v>
+        <v>440940</v>
       </c>
       <c r="R14" t="n">
-        <v>7001243</v>
+        <v>7001369</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2062,12 +1987,7 @@
         <v>124800296</v>
       </c>
       <c r="B15" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,15 +2085,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800322</v>
+        <v>124800304</v>
       </c>
       <c r="B16" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440696</v>
+        <v>440902</v>
       </c>
       <c r="R16" t="n">
-        <v>7001259</v>
+        <v>7001332</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,15 +2186,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800315</v>
+        <v>124800307</v>
       </c>
       <c r="B17" t="n">
-        <v>79026</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,21 +2197,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2315,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440782</v>
+        <v>440872</v>
       </c>
       <c r="R17" t="n">
-        <v>7001494</v>
+        <v>7001280</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,37 +2287,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800324</v>
+        <v>124800309</v>
       </c>
       <c r="B18" t="n">
-        <v>91521</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2415,19 +2320,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440680</v>
+        <v>440821</v>
       </c>
       <c r="R18" t="n">
-        <v>7001258</v>
+        <v>7001261</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2468,7 +2370,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2487,37 +2388,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800328</v>
+        <v>124800322</v>
       </c>
       <c r="B19" t="n">
-        <v>95503</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2531,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440661</v>
+        <v>440696</v>
       </c>
       <c r="R19" t="n">
-        <v>7001244</v>
+        <v>7001259</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2593,37 +2489,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800330</v>
+        <v>124800297</v>
       </c>
       <c r="B20" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2637,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440646</v>
+        <v>440921</v>
       </c>
       <c r="R20" t="n">
-        <v>7001158</v>
+        <v>7001295</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,37 +2590,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800293</v>
+        <v>124800336</v>
       </c>
       <c r="B21" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2743,10 +2629,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441111</v>
+        <v>440616</v>
       </c>
       <c r="R21" t="n">
-        <v>7001333</v>
+        <v>7001215</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,15 +2691,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800303</v>
+        <v>124800333</v>
       </c>
       <c r="B22" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2821,21 +2702,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2849,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440909</v>
+        <v>440628</v>
       </c>
       <c r="R22" t="n">
-        <v>7001374</v>
+        <v>7001081</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2911,15 +2792,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800323</v>
+        <v>124800332</v>
       </c>
       <c r="B23" t="n">
-        <v>75025</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,21 +2803,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2955,10 +2831,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440681</v>
+        <v>440630</v>
       </c>
       <c r="R23" t="n">
-        <v>7001285</v>
+        <v>7001086</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,37 +2893,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800340</v>
+        <v>124800324</v>
       </c>
       <c r="B24" t="n">
-        <v>75025</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>2062</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3055,16 +2926,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440590</v>
+        <v>440680</v>
       </c>
       <c r="R24" t="n">
-        <v>7001362</v>
+        <v>7001258</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3105,6 +2979,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3123,37 +2998,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800327</v>
+        <v>124800338</v>
       </c>
       <c r="B25" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97780</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2389</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3167,10 +3037,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440672</v>
+        <v>440604</v>
       </c>
       <c r="R25" t="n">
-        <v>7001361</v>
+        <v>7001240</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3229,37 +3099,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800320</v>
+        <v>124801009</v>
       </c>
       <c r="B26" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95772</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2411</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig källmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Philonotis tomentella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Molendo</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3273,10 +3138,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440720</v>
+        <v>440900</v>
       </c>
       <c r="R26" t="n">
-        <v>7001206</v>
+        <v>7001371</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3335,37 +3200,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800321</v>
+        <v>124800328</v>
       </c>
       <c r="B27" t="n">
-        <v>91162</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>2809</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3379,10 +3239,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440709</v>
+        <v>440661</v>
       </c>
       <c r="R27" t="n">
-        <v>7001238</v>
+        <v>7001244</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3444,16 +3304,11 @@
         <v>124740817</v>
       </c>
       <c r="B28" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3543,37 +3398,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800332</v>
+        <v>124800298</v>
       </c>
       <c r="B29" t="n">
-        <v>75030</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3587,10 +3437,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440630</v>
+        <v>440916</v>
       </c>
       <c r="R29" t="n">
-        <v>7001086</v>
+        <v>7001320</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3649,37 +3499,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800304</v>
+        <v>124800303</v>
       </c>
       <c r="B30" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3693,10 +3538,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440902</v>
+        <v>440909</v>
       </c>
       <c r="R30" t="n">
-        <v>7001332</v>
+        <v>7001374</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3755,37 +3600,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800294</v>
+        <v>124800313</v>
       </c>
       <c r="B31" t="n">
-        <v>79988</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3799,10 +3639,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441028</v>
+        <v>440791</v>
       </c>
       <c r="R31" t="n">
-        <v>7001364</v>
+        <v>7001239</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3861,37 +3701,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124800300</v>
+        <v>124800314</v>
       </c>
       <c r="B32" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3905,10 +3740,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440915</v>
+        <v>440785</v>
       </c>
       <c r="R32" t="n">
-        <v>7001296</v>
+        <v>7001501</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3935,12 +3770,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,37 +3802,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124800311</v>
+        <v>124800316</v>
       </c>
       <c r="B33" t="n">
-        <v>77889</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4011,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440798</v>
+        <v>440773</v>
       </c>
       <c r="R33" t="n">
-        <v>7001239</v>
+        <v>7001489</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4073,50 +3903,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124738082</v>
+        <v>124800320</v>
       </c>
       <c r="B34" t="n">
-        <v>88512</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440684</v>
+        <v>440720</v>
       </c>
       <c r="R34" t="n">
-        <v>7001254</v>
+        <v>7001206</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4143,12 +3972,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4175,37 +4004,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124800302</v>
+        <v>124800325</v>
       </c>
       <c r="B35" t="n">
-        <v>79026</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4219,10 +4043,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440910</v>
+        <v>440674</v>
       </c>
       <c r="R35" t="n">
-        <v>7001371</v>
+        <v>7001385</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4281,37 +4105,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124800335</v>
+        <v>124800326</v>
       </c>
       <c r="B36" t="n">
-        <v>79026</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4325,10 +4144,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440621</v>
+        <v>440672</v>
       </c>
       <c r="R36" t="n">
-        <v>7001181</v>
+        <v>7001335</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4387,50 +4206,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124740889</v>
+        <v>124800327</v>
       </c>
       <c r="B37" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440684</v>
+        <v>440672</v>
       </c>
       <c r="R37" t="n">
-        <v>7001254</v>
+        <v>7001361</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4457,12 +4275,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4489,19 +4307,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124800298</v>
+        <v>124800329</v>
       </c>
       <c r="B38" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4533,10 +4346,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440916</v>
+        <v>440658</v>
       </c>
       <c r="R38" t="n">
-        <v>7001320</v>
+        <v>7001354</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,19 +4408,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124800325</v>
+        <v>124800330</v>
       </c>
       <c r="B39" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4639,10 +4447,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440674</v>
+        <v>440646</v>
       </c>
       <c r="R39" t="n">
-        <v>7001385</v>
+        <v>7001158</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4701,19 +4509,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124800329</v>
+        <v>124800331</v>
       </c>
       <c r="B40" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4745,10 +4548,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440658</v>
+        <v>440637</v>
       </c>
       <c r="R40" t="n">
-        <v>7001354</v>
+        <v>7001171</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4807,15 +4610,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124800309</v>
+        <v>124800310</v>
       </c>
       <c r="B41" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4823,21 +4621,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4851,10 +4649,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440821</v>
+        <v>440799</v>
       </c>
       <c r="R41" t="n">
-        <v>7001261</v>
+        <v>7001243</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4913,15 +4711,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124800307</v>
+        <v>124800323</v>
       </c>
       <c r="B42" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4929,21 +4722,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4957,10 +4750,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440872</v>
+        <v>440681</v>
       </c>
       <c r="R42" t="n">
-        <v>7001280</v>
+        <v>7001285</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5019,15 +4812,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124800316</v>
+        <v>124800340</v>
       </c>
       <c r="B43" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5035,21 +4823,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5063,10 +4851,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440773</v>
+        <v>440590</v>
       </c>
       <c r="R43" t="n">
-        <v>7001489</v>
+        <v>7001362</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5125,15 +4913,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124800338</v>
+        <v>124800293</v>
       </c>
       <c r="B44" t="n">
-        <v>96944</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5141,21 +4924,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2389</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5169,10 +4952,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440604</v>
+        <v>441111</v>
       </c>
       <c r="R44" t="n">
-        <v>7001240</v>
+        <v>7001333</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5231,37 +5014,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124800313</v>
+        <v>124800319</v>
       </c>
       <c r="B45" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98194</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220686</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5275,10 +5053,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440791</v>
+        <v>440720</v>
       </c>
       <c r="R45" t="n">
-        <v>7001239</v>
+        <v>7001201</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5337,37 +5115,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124800314</v>
+        <v>124800294</v>
       </c>
       <c r="B46" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5381,10 +5154,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440785</v>
+        <v>441028</v>
       </c>
       <c r="R46" t="n">
-        <v>7001501</v>
+        <v>7001364</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5411,12 +5184,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5440,324 +5213,6 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>124800297</v>
-      </c>
-      <c r="B47" t="n">
-        <v>91180</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Västerfjället, Jmt</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>440921</v>
-      </c>
-      <c r="R47" t="n">
-        <v>7001295</v>
-      </c>
-      <c r="S47" t="n">
-        <v>10</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Hallen</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>124800336</v>
-      </c>
-      <c r="B48" t="n">
-        <v>91180</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Västerfjället, Jmt</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>440616</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7001215</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Hallen</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>124800331</v>
-      </c>
-      <c r="B49" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Västerfjället, Jmt</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>440637</v>
-      </c>
-      <c r="R49" t="n">
-        <v>7001171</v>
-      </c>
-      <c r="S49" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Hallen</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15924-2025 artfynd.xlsx
+++ b/artfynd/A 15924-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800318</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800311</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800334</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124738082</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800306</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800308</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800305</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800299</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800302</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1678,6 +1728,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800315</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800335</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1880,6 +1940,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800321</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1981,6 +2046,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800295</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2082,6 +2152,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800296</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2183,6 +2258,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800304</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2284,6 +2364,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800307</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2385,6 +2470,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800309</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2486,6 +2576,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800322</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2587,6 +2682,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800297</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2688,6 +2788,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800336</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2789,6 +2894,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800333</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2890,6 +3000,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800332</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2995,6 +3110,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800324</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3096,6 +3216,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800338</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3197,6 +3322,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124801009</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3298,6 +3428,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800328</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3395,6 +3530,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124740817</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3496,6 +3636,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800298</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3597,6 +3742,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800303</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3698,6 +3848,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800313</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3799,6 +3954,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800314</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3900,6 +4060,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800316</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4001,6 +4166,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800320</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4102,6 +4272,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800325</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4203,6 +4378,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800326</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4304,6 +4484,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800327</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4405,6 +4590,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800329</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4506,6 +4696,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800330</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4607,6 +4802,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800331</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4708,6 +4908,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800310</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4809,6 +5014,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800323</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4910,6 +5120,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800340</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5011,6 +5226,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800293</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5112,6 +5332,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800319</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5213,8 +5438,60 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800294</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>